--- a/data/kbli_populer_riau2.xlsx
+++ b/data/kbli_populer_riau2.xlsx
@@ -9225,7 +9225,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="43" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A43" s="6" t="s">
         <v>1676</v>
       </c>
@@ -15560,7 +15560,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="224" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A224" s="6" t="s">
         <v>1844</v>
       </c>
@@ -30288,7 +30288,7 @@
         <v>1919</v>
       </c>
     </row>
-    <row r="646" spans="1:11" ht="90" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:11" ht="75" x14ac:dyDescent="0.25">
       <c r="A646" s="6" t="s">
         <v>1845</v>
       </c>
@@ -30323,7 +30323,7 @@
         <v>1925</v>
       </c>
     </row>
-    <row r="647" spans="1:11" ht="90" x14ac:dyDescent="0.25">
+    <row r="647" spans="1:11" ht="75" x14ac:dyDescent="0.25">
       <c r="A647" s="6" t="s">
         <v>1845</v>
       </c>
@@ -30883,7 +30883,7 @@
         <v>2002</v>
       </c>
     </row>
-    <row r="663" spans="1:11" ht="64.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="663" spans="1:11" ht="51.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A663" s="6" t="s">
         <v>5</v>
       </c>
@@ -31548,7 +31548,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="682" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="682" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A682" s="6" t="s">
         <v>2022</v>
       </c>
@@ -31583,7 +31583,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="683" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="683" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A683" s="6" t="s">
         <v>2022</v>
       </c>
@@ -32983,7 +32983,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="723" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="723" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A723" s="6" t="s">
         <v>2022</v>
       </c>
@@ -35573,7 +35573,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="797" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="797" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A797" s="6" t="s">
         <v>2023</v>
       </c>
@@ -35713,7 +35713,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="801" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="801" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A801" s="6" t="s">
         <v>2023</v>
       </c>
@@ -35853,7 +35853,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="805" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="805" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A805" s="6" t="s">
         <v>2023</v>
       </c>
@@ -36728,7 +36728,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="830" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="830" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A830" s="6" t="s">
         <v>2023</v>
       </c>
@@ -38513,7 +38513,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="881" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="881" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A881" s="6" t="s">
         <v>2023</v>
       </c>
@@ -38548,7 +38548,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="882" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="882" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A882" s="6" t="s">
         <v>2023</v>
       </c>
@@ -41103,7 +41103,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="955" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="955" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A955" s="6" t="s">
         <v>2024</v>
       </c>
@@ -41313,7 +41313,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="961" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="961" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A961" s="6" t="s">
         <v>2024</v>
       </c>
@@ -41348,7 +41348,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="962" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="962" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A962" s="6" t="s">
         <v>2024</v>
       </c>
@@ -43961,7 +43961,7 @@
         <v>2048</v>
       </c>
     </row>
-    <row r="1037" spans="1:11" ht="75" x14ac:dyDescent="0.25">
+    <row r="1037" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A1037" s="6" t="s">
         <v>16</v>
       </c>
@@ -44057,7 +44057,7 @@
         <v>2060</v>
       </c>
     </row>
-    <row r="1040" spans="1:11" ht="90" x14ac:dyDescent="0.25">
+    <row r="1040" spans="1:11" ht="75" x14ac:dyDescent="0.25">
       <c r="A1040" s="6" t="s">
         <v>16</v>
       </c>
@@ -44220,7 +44220,7 @@
         <v>2075</v>
       </c>
     </row>
-    <row r="1045" spans="1:11" ht="90" x14ac:dyDescent="0.25">
+    <row r="1045" spans="1:11" ht="75" x14ac:dyDescent="0.25">
       <c r="A1045" s="6" t="s">
         <v>16</v>
       </c>
@@ -44459,7 +44459,7 @@
         <v>2098</v>
       </c>
     </row>
-    <row r="1052" spans="1:11" ht="165" x14ac:dyDescent="0.25">
+    <row r="1052" spans="1:11" ht="150" x14ac:dyDescent="0.25">
       <c r="A1052" s="6" t="s">
         <v>16</v>
       </c>
@@ -44599,7 +44599,7 @@
         <v>2111</v>
       </c>
     </row>
-    <row r="1056" spans="1:11" ht="75" x14ac:dyDescent="0.25">
+    <row r="1056" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A1056" s="6" t="s">
         <v>16</v>
       </c>
@@ -44914,7 +44914,7 @@
         <v>2144</v>
       </c>
     </row>
-    <row r="1065" spans="1:11" ht="75" x14ac:dyDescent="0.25">
+    <row r="1065" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A1065" s="6" t="s">
         <v>24</v>
       </c>
@@ -46804,7 +46804,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="1119" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="1119" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A1119" s="6" t="s">
         <v>2266</v>
       </c>
@@ -47259,7 +47259,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="1132" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="1132" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A1132" s="6" t="s">
         <v>2266</v>
       </c>
@@ -49359,7 +49359,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="1192" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+    <row r="1192" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A1192" s="6" t="s">
         <v>2266</v>
       </c>
@@ -53244,7 +53244,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="1303" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+    <row r="1303" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A1303" s="6" t="s">
         <v>2278</v>
       </c>
@@ -53279,7 +53279,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="1304" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+    <row r="1304" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A1304" s="6" t="s">
         <v>2278</v>
       </c>
@@ -55764,7 +55764,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="1375" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+    <row r="1375" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A1375" s="6" t="s">
         <v>41</v>
       </c>
@@ -55869,7 +55869,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="1378" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="1378" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A1378" s="6" t="s">
         <v>41</v>
       </c>
@@ -58214,7 +58214,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="1445" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="1445" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A1445" s="6" t="s">
         <v>81</v>
       </c>
@@ -61294,7 +61294,7 @@
         <v>2288</v>
       </c>
     </row>
-    <row r="1533" spans="1:11" ht="165" x14ac:dyDescent="0.25">
+    <row r="1533" spans="1:11" ht="150" x14ac:dyDescent="0.25">
       <c r="A1533" s="6" t="s">
         <v>2283</v>
       </c>
@@ -61679,7 +61679,7 @@
         <v>2327</v>
       </c>
     </row>
-    <row r="1544" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="1544" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A1544" s="6" t="s">
         <v>2283</v>
       </c>
@@ -61819,7 +61819,7 @@
         <v>2342</v>
       </c>
     </row>
-    <row r="1548" spans="1:11" ht="75" x14ac:dyDescent="0.25">
+    <row r="1548" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A1548" s="6" t="s">
         <v>2283</v>
       </c>
@@ -62064,7 +62064,7 @@
         <v>2368</v>
       </c>
     </row>
-    <row r="1555" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="1555" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A1555" s="6" t="s">
         <v>2283</v>
       </c>
@@ -62169,7 +62169,7 @@
         <v>2381</v>
       </c>
     </row>
-    <row r="1558" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="1558" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A1558" s="6" t="s">
         <v>2376</v>
       </c>

--- a/data/kbli_populer_riau2.xlsx
+++ b/data/kbli_populer_riau2.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4753" uniqueCount="2536">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4761" uniqueCount="2541">
   <si>
     <t>kategori</t>
   </si>
@@ -7135,10 +7135,6 @@
     <t>Biasanya ada yang memiliki etalase, nanti ada yang menitip jualkan kue basah di sana;</t>
   </si>
   <si>
-    <t>perdagangan eceran pakaian, baik terbuat dari tekstil, kulit, maupun kulit buatan, seperti kemeja, celana, jas, mantel, jaket, piyama, kebaya, blus, rok, daster, singlet, kutang/bra, gaun, rok dalam, baju bayi, pakaian tari,  pakaian adat, mukena, dan jubah; Perdagangan eceran pakaian olahraga (bukan konveksi baju olahraga)
-umum yang tidak dirancang khusus untuk olahraga tertentu; Pedagang pakaian di los;</t>
-  </si>
-  <si>
     <t>Depot; Isi ulang; Tirta; Menjual air minum isi ulang;</t>
   </si>
   <si>
@@ -7653,6 +7649,25 @@
   </si>
   <si>
     <t>Jual gorengan (gerobak, keliling, warung non permanen); Food truck; angkringan; siomay gerobak; bakso gerobak; Warung pecel lele; jualan nasi goreng; kedai mie; jual sate; menjual soto; menjual martabak mesir; pedagang cilor; jual telur gulung;  Martabak terang bulan; Martabak bangka; Martabak gerobak (biasanya jualan malam hari); jual lontong; Jual sarapan, nasi uduk, nasi kuning di mobil;</t>
+  </si>
+  <si>
+    <t>perdagangan eceran pakaian, baik terbuat dari tekstil, kulit, maupun kulit buatan, seperti kemeja, celana, jas, mantel, jaket, piyama, kebaya, blus, rok, daster, singlet, kutang/bra, gaun, rok dalam, baju bayi, pakaian tari,  pakaian adat, mukena, dan jubah; Perdagangan eceran pakaian olahraga (bukan konveksi baju olahraga)
+umum yang tidak dirancang khusus untuk olahraga tertentu; Pedagang pakaian di los; baju; baju jadi;</t>
+  </si>
+  <si>
+    <t>jual jilab, jilbab; jual kaos kaki, kaos kaki; menjual selendang, kerudung, sapu tangan, ikat kepala, blangkon, peci, topi, dasi, ikat pinggang, cadar, sarung tangan, kaos kaki, handuk, dan selimut, termasuk juga perdagangan eceran kancing baju, ritsleting, dan benang jahit;</t>
+  </si>
+  <si>
+    <t>Toko hijab/jilbab; Toko Kaos kaki; jual benang jahit, kancing, risleting;</t>
+  </si>
+  <si>
+    <t>Toko sepatu;</t>
+  </si>
+  <si>
+    <t>jual sepatu; jual sendal; sepatu; sendal;</t>
+  </si>
+  <si>
+    <t>Toko kacamata; Optik; Jual Lensa kontak;</t>
   </si>
 </sst>
 </file>
@@ -8222,16 +8237,16 @@
         <v>155</v>
       </c>
       <c r="D2" s="7" t="s">
+        <v>2392</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>2393</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>2394</v>
       </c>
       <c r="F2" s="8" t="s">
         <v>1587</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>2392</v>
+        <v>2391</v>
       </c>
       <c r="I2" t="e">
         <v>#N/A</v>
@@ -8254,16 +8269,16 @@
         <v>156</v>
       </c>
       <c r="D3" s="19" t="s">
-        <v>2396</v>
+        <v>2395</v>
       </c>
       <c r="E3" s="20" t="s">
-        <v>2395</v>
+        <v>2394</v>
       </c>
       <c r="F3" s="8" t="s">
         <v>2280</v>
       </c>
       <c r="H3" s="18" t="s">
-        <v>2373</v>
+        <v>2372</v>
       </c>
       <c r="I3" t="e">
         <v>#N/A</v>
@@ -8286,10 +8301,10 @@
         <v>157</v>
       </c>
       <c r="D4" s="9" t="s">
+        <v>2396</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>2397</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>2398</v>
       </c>
       <c r="F4" s="8" t="s">
         <v>1587</v>
@@ -8298,7 +8313,7 @@
         <v>#N/A</v>
       </c>
       <c r="H4" s="18" t="s">
-        <v>2374</v>
+        <v>2373</v>
       </c>
       <c r="I4" t="e">
         <v>#N/A</v>
@@ -8324,7 +8339,7 @@
         <v>#N/A</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>2415</v>
+        <v>2414</v>
       </c>
       <c r="F5" s="8" t="e">
         <v>#N/A</v>
@@ -8333,7 +8348,7 @@
         <v>#N/A</v>
       </c>
       <c r="H5" s="18" t="s">
-        <v>2375</v>
+        <v>2374</v>
       </c>
       <c r="I5" t="e">
         <v>#N/A</v>
@@ -8359,7 +8374,7 @@
         <v>#N/A</v>
       </c>
       <c r="E6" s="17" t="s">
-        <v>2399</v>
+        <v>2398</v>
       </c>
       <c r="F6" s="8" t="e">
         <v>#N/A</v>
@@ -8368,7 +8383,7 @@
         <v>#N/A</v>
       </c>
       <c r="H6" s="18" t="s">
-        <v>2376</v>
+        <v>2375</v>
       </c>
       <c r="I6" t="e">
         <v>#N/A</v>
@@ -8394,7 +8409,7 @@
         <v>#N/A</v>
       </c>
       <c r="E7" s="17" t="s">
-        <v>2400</v>
+        <v>2399</v>
       </c>
       <c r="F7" s="8" t="e">
         <v>#N/A</v>
@@ -8403,7 +8418,7 @@
         <v>#N/A</v>
       </c>
       <c r="H7" s="18" t="s">
-        <v>2377</v>
+        <v>2376</v>
       </c>
       <c r="I7" t="e">
         <v>#N/A</v>
@@ -8429,7 +8444,7 @@
         <v>#N/A</v>
       </c>
       <c r="E8" s="17" t="s">
-        <v>2401</v>
+        <v>2400</v>
       </c>
       <c r="F8" s="8" t="e">
         <v>#N/A</v>
@@ -8438,7 +8453,7 @@
         <v>#N/A</v>
       </c>
       <c r="H8" s="18" t="s">
-        <v>2378</v>
+        <v>2377</v>
       </c>
       <c r="I8" t="e">
         <v>#N/A</v>
@@ -8464,7 +8479,7 @@
         <v>#N/A</v>
       </c>
       <c r="E9" s="17" t="s">
-        <v>2402</v>
+        <v>2401</v>
       </c>
       <c r="F9" s="8" t="e">
         <v>#N/A</v>
@@ -8473,7 +8488,7 @@
         <v>#N/A</v>
       </c>
       <c r="H9" s="18" t="s">
-        <v>2379</v>
+        <v>2378</v>
       </c>
       <c r="I9" t="e">
         <v>#N/A</v>
@@ -8499,7 +8514,7 @@
         <v>#N/A</v>
       </c>
       <c r="E10" s="17" t="s">
-        <v>2403</v>
+        <v>2402</v>
       </c>
       <c r="F10" s="8" t="e">
         <v>#N/A</v>
@@ -8508,7 +8523,7 @@
         <v>#N/A</v>
       </c>
       <c r="H10" s="18" t="s">
-        <v>2380</v>
+        <v>2379</v>
       </c>
       <c r="I10" t="e">
         <v>#N/A</v>
@@ -8534,7 +8549,7 @@
         <v>#N/A</v>
       </c>
       <c r="E11" s="17" t="s">
-        <v>2404</v>
+        <v>2403</v>
       </c>
       <c r="F11" s="8" t="e">
         <v>#N/A</v>
@@ -8543,7 +8558,7 @@
         <v>#N/A</v>
       </c>
       <c r="H11" s="18" t="s">
-        <v>2381</v>
+        <v>2380</v>
       </c>
       <c r="I11" t="e">
         <v>#N/A</v>
@@ -8569,7 +8584,7 @@
         <v>#N/A</v>
       </c>
       <c r="E12" s="17" t="s">
-        <v>2405</v>
+        <v>2404</v>
       </c>
       <c r="F12" s="8" t="e">
         <v>#N/A</v>
@@ -8578,7 +8593,7 @@
         <v>#N/A</v>
       </c>
       <c r="H12" s="18" t="s">
-        <v>2382</v>
+        <v>2381</v>
       </c>
       <c r="I12" t="e">
         <v>#N/A</v>
@@ -8604,7 +8619,7 @@
         <v>#N/A</v>
       </c>
       <c r="E13" s="17" t="s">
-        <v>2406</v>
+        <v>2405</v>
       </c>
       <c r="F13" s="8" t="e">
         <v>#N/A</v>
@@ -8613,7 +8628,7 @@
         <v>#N/A</v>
       </c>
       <c r="H13" s="18" t="s">
-        <v>2383</v>
+        <v>2382</v>
       </c>
       <c r="I13" t="e">
         <v>#N/A</v>
@@ -8639,7 +8654,7 @@
         <v>#N/A</v>
       </c>
       <c r="E14" s="17" t="s">
-        <v>2407</v>
+        <v>2406</v>
       </c>
       <c r="F14" s="8" t="e">
         <v>#N/A</v>
@@ -8648,7 +8663,7 @@
         <v>#N/A</v>
       </c>
       <c r="H14" s="18" t="s">
-        <v>2384</v>
+        <v>2383</v>
       </c>
       <c r="I14" t="e">
         <v>#N/A</v>
@@ -8674,7 +8689,7 @@
         <v>#N/A</v>
       </c>
       <c r="E15" s="17" t="s">
-        <v>2408</v>
+        <v>2407</v>
       </c>
       <c r="F15" s="8" t="e">
         <v>#N/A</v>
@@ -8683,7 +8698,7 @@
         <v>#N/A</v>
       </c>
       <c r="H15" s="18" t="s">
-        <v>2385</v>
+        <v>2384</v>
       </c>
       <c r="I15" t="e">
         <v>#N/A</v>
@@ -8709,7 +8724,7 @@
         <v>#N/A</v>
       </c>
       <c r="E16" s="17" t="s">
-        <v>2409</v>
+        <v>2408</v>
       </c>
       <c r="F16" s="8" t="e">
         <v>#N/A</v>
@@ -8718,7 +8733,7 @@
         <v>#N/A</v>
       </c>
       <c r="H16" s="18" t="s">
-        <v>2386</v>
+        <v>2385</v>
       </c>
       <c r="I16" t="e">
         <v>#N/A</v>
@@ -8744,7 +8759,7 @@
         <v>#N/A</v>
       </c>
       <c r="E17" s="17" t="s">
-        <v>2410</v>
+        <v>2409</v>
       </c>
       <c r="F17" s="8" t="e">
         <v>#N/A</v>
@@ -8753,7 +8768,7 @@
         <v>#N/A</v>
       </c>
       <c r="H17" s="18" t="s">
-        <v>2387</v>
+        <v>2386</v>
       </c>
       <c r="I17" t="e">
         <v>#N/A</v>
@@ -8779,7 +8794,7 @@
         <v>#N/A</v>
       </c>
       <c r="E18" s="17" t="s">
-        <v>2411</v>
+        <v>2410</v>
       </c>
       <c r="F18" s="8" t="e">
         <v>#N/A</v>
@@ -8788,7 +8803,7 @@
         <v>#N/A</v>
       </c>
       <c r="H18" s="18" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="I18" t="e">
         <v>#N/A</v>
@@ -8814,7 +8829,7 @@
         <v>#N/A</v>
       </c>
       <c r="E19" s="17" t="s">
-        <v>2412</v>
+        <v>2411</v>
       </c>
       <c r="F19" s="8" t="e">
         <v>#N/A</v>
@@ -8823,7 +8838,7 @@
         <v>#N/A</v>
       </c>
       <c r="H19" s="18" t="s">
-        <v>2389</v>
+        <v>2388</v>
       </c>
       <c r="I19" t="e">
         <v>#N/A</v>
@@ -8849,7 +8864,7 @@
         <v>#N/A</v>
       </c>
       <c r="E20" s="17" t="s">
-        <v>2413</v>
+        <v>2412</v>
       </c>
       <c r="F20" s="8" t="e">
         <v>#N/A</v>
@@ -8858,7 +8873,7 @@
         <v>#N/A</v>
       </c>
       <c r="H20" s="18" t="s">
-        <v>2390</v>
+        <v>2389</v>
       </c>
       <c r="I20" t="e">
         <v>#N/A</v>
@@ -8884,7 +8899,7 @@
         <v>#N/A</v>
       </c>
       <c r="E21" s="17" t="s">
-        <v>2414</v>
+        <v>2413</v>
       </c>
       <c r="F21" s="8" t="e">
         <v>#N/A</v>
@@ -8893,7 +8908,7 @@
         <v>#N/A</v>
       </c>
       <c r="H21" s="18" t="s">
-        <v>2391</v>
+        <v>2390</v>
       </c>
       <c r="I21" t="e">
         <v>#N/A</v>
@@ -17141,7 +17156,7 @@
         <v>402</v>
       </c>
       <c r="D257" s="2" t="s">
-        <v>2371</v>
+        <v>2370</v>
       </c>
       <c r="E257" s="2" t="e">
         <v>#N/A</v>
@@ -17529,7 +17544,7 @@
         <v>#N/A</v>
       </c>
       <c r="E268" s="2" t="s">
-        <v>2370</v>
+        <v>2369</v>
       </c>
       <c r="F268" t="e">
         <v>#N/A</v>
@@ -17596,10 +17611,10 @@
         <v>415</v>
       </c>
       <c r="D270" s="2" t="s">
-        <v>2369</v>
+        <v>2368</v>
       </c>
       <c r="E270" s="2" t="s">
-        <v>2368</v>
+        <v>2367</v>
       </c>
       <c r="F270" t="s">
         <v>1587</v>
@@ -20466,10 +20481,10 @@
         <v>497</v>
       </c>
       <c r="D352" s="2" t="s">
+        <v>2485</v>
+      </c>
+      <c r="E352" s="2" t="s">
         <v>2486</v>
-      </c>
-      <c r="E352" s="2" t="s">
-        <v>2487</v>
       </c>
       <c r="F352" t="s">
         <v>1587</v>
@@ -29356,10 +29371,10 @@
         <v>749</v>
       </c>
       <c r="D606" s="2" t="s">
+        <v>2517</v>
+      </c>
+      <c r="E606" s="2" t="s">
         <v>2518</v>
-      </c>
-      <c r="E606" s="2" t="s">
-        <v>2519</v>
       </c>
       <c r="F606" t="s">
         <v>1587</v>
@@ -30554,7 +30569,7 @@
         <v>783</v>
       </c>
       <c r="D641" s="2" t="s">
-        <v>2423</v>
+        <v>2422</v>
       </c>
       <c r="E641" s="2" t="s">
         <v>1850</v>
@@ -30714,7 +30729,7 @@
         <v>788</v>
       </c>
       <c r="D646" s="2" t="s">
-        <v>2491</v>
+        <v>2490</v>
       </c>
       <c r="E646" s="2" t="s">
         <v>1878</v>
@@ -30749,7 +30764,7 @@
         <v>789</v>
       </c>
       <c r="D647" s="2" t="s">
-        <v>2424</v>
+        <v>2423</v>
       </c>
       <c r="E647" s="2" t="s">
         <v>1883</v>
@@ -36839,10 +36854,10 @@
         <v>2361</v>
       </c>
       <c r="D821" s="2" t="s">
-        <v>2470</v>
+        <v>2469</v>
       </c>
       <c r="E821" s="2" t="s">
-        <v>2467</v>
+        <v>2466</v>
       </c>
       <c r="F821" t="s">
         <v>1587</v>
@@ -36874,10 +36889,10 @@
         <v>2329</v>
       </c>
       <c r="D822" s="2" t="s">
-        <v>2469</v>
+        <v>2468</v>
       </c>
       <c r="E822" s="2" t="s">
-        <v>2468</v>
+        <v>2467</v>
       </c>
       <c r="F822" t="s">
         <v>1587</v>
@@ -37574,10 +37589,10 @@
         <v>966</v>
       </c>
       <c r="D842" s="2" t="s">
-        <v>2473</v>
+        <v>2472</v>
       </c>
       <c r="E842" s="2" t="s">
-        <v>2472</v>
+        <v>2471</v>
       </c>
       <c r="F842" t="s">
         <v>105</v>
@@ -37609,10 +37624,10 @@
         <v>967</v>
       </c>
       <c r="D843" s="2" t="s">
-        <v>2475</v>
+        <v>2474</v>
       </c>
       <c r="E843" s="2" t="s">
-        <v>2474</v>
+        <v>2473</v>
       </c>
       <c r="F843" t="s">
         <v>1587</v>
@@ -37679,10 +37694,10 @@
         <v>969</v>
       </c>
       <c r="D845" s="2" t="s">
-        <v>2477</v>
+        <v>2476</v>
       </c>
       <c r="E845" s="2" t="s">
-        <v>2476</v>
+        <v>2475</v>
       </c>
       <c r="F845" t="s">
         <v>1587</v>
@@ -37714,10 +37729,10 @@
         <v>970</v>
       </c>
       <c r="D846" s="2" t="s">
+        <v>2477</v>
+      </c>
+      <c r="E846" s="2" t="s">
         <v>2478</v>
-      </c>
-      <c r="E846" s="2" t="s">
-        <v>2479</v>
       </c>
       <c r="F846" t="s">
         <v>1587</v>
@@ -38312,7 +38327,7 @@
         <v>2356</v>
       </c>
       <c r="E863" s="2" t="s">
-        <v>2527</v>
+        <v>2526</v>
       </c>
       <c r="F863" t="s">
         <v>1587</v>
@@ -38613,7 +38628,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="872" spans="1:11" ht="225" x14ac:dyDescent="0.25">
+    <row r="872" spans="1:11" ht="240" x14ac:dyDescent="0.25">
       <c r="A872" s="4" t="s">
         <v>1979</v>
       </c>
@@ -38624,10 +38639,10 @@
         <v>996</v>
       </c>
       <c r="D872" s="2" t="s">
-        <v>2533</v>
+        <v>2532</v>
       </c>
       <c r="E872" s="2" t="s">
-        <v>2367</v>
+        <v>2535</v>
       </c>
       <c r="F872" t="s">
         <v>1587</v>
@@ -38658,14 +38673,14 @@
       <c r="C873" s="6" t="s">
         <v>997</v>
       </c>
-      <c r="D873" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E873" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F873" t="e">
-        <v>#N/A</v>
+      <c r="D873" s="2" t="s">
+        <v>2538</v>
+      </c>
+      <c r="E873" s="2" t="s">
+        <v>2539</v>
+      </c>
+      <c r="F873" t="s">
+        <v>1587</v>
       </c>
       <c r="G873" t="e">
         <v>#N/A</v>
@@ -38683,7 +38698,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="874" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="874" spans="1:11" ht="150" x14ac:dyDescent="0.25">
       <c r="A874" s="4" t="s">
         <v>1979</v>
       </c>
@@ -38693,14 +38708,14 @@
       <c r="C874" s="6" t="s">
         <v>998</v>
       </c>
-      <c r="D874" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E874" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F874" t="e">
-        <v>#N/A</v>
+      <c r="D874" s="2" t="s">
+        <v>2537</v>
+      </c>
+      <c r="E874" s="2" t="s">
+        <v>2536</v>
+      </c>
+      <c r="F874" t="s">
+        <v>1587</v>
       </c>
       <c r="G874" t="e">
         <v>#N/A</v>
@@ -38872,7 +38887,7 @@
         <v>2357</v>
       </c>
       <c r="E879" s="2" t="s">
-        <v>2528</v>
+        <v>2527</v>
       </c>
       <c r="F879" t="s">
         <v>1587</v>
@@ -39148,14 +39163,14 @@
       <c r="C887" s="6" t="s">
         <v>1011</v>
       </c>
-      <c r="D887" s="2" t="e">
-        <v>#N/A</v>
+      <c r="D887" s="2" t="s">
+        <v>2540</v>
       </c>
       <c r="E887" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="F887" t="e">
-        <v>#N/A</v>
+      <c r="F887" t="s">
+        <v>1587</v>
       </c>
       <c r="G887" t="e">
         <v>#N/A</v>
@@ -39849,7 +39864,7 @@
         <v>1031</v>
       </c>
       <c r="D907" s="2" t="s">
-        <v>2471</v>
+        <v>2470</v>
       </c>
       <c r="E907" s="2" t="s">
         <v>2334</v>
@@ -39986,13 +40001,13 @@
         <v>47781</v>
       </c>
       <c r="C911" s="6" t="s">
+        <v>2482</v>
+      </c>
+      <c r="D911" s="2" t="s">
         <v>2483</v>
       </c>
-      <c r="D911" s="2" t="s">
+      <c r="E911" s="2" t="s">
         <v>2484</v>
-      </c>
-      <c r="E911" s="2" t="s">
-        <v>2485</v>
       </c>
       <c r="F911" t="s">
         <v>1587</v>
@@ -40514,10 +40529,10 @@
         <v>1049</v>
       </c>
       <c r="D926" s="2" t="s">
+        <v>2491</v>
+      </c>
+      <c r="E926" s="2" t="s">
         <v>2492</v>
-      </c>
-      <c r="E926" s="2" t="s">
-        <v>2493</v>
       </c>
       <c r="F926" t="s">
         <v>1587</v>
@@ -40549,10 +40564,10 @@
         <v>1050</v>
       </c>
       <c r="D927" s="2" t="s">
+        <v>2501</v>
+      </c>
+      <c r="E927" s="2" t="s">
         <v>2502</v>
-      </c>
-      <c r="E927" s="2" t="s">
-        <v>2503</v>
       </c>
       <c r="F927" t="s">
         <v>1587</v>
@@ -41284,10 +41299,10 @@
         <v>1071</v>
       </c>
       <c r="D948" s="2" t="s">
-        <v>2498</v>
+        <v>2497</v>
       </c>
       <c r="E948" s="2" t="s">
-        <v>2506</v>
+        <v>2505</v>
       </c>
       <c r="F948" t="s">
         <v>1587</v>
@@ -41319,10 +41334,10 @@
         <v>1072</v>
       </c>
       <c r="D949" s="2" t="s">
+        <v>2498</v>
+      </c>
+      <c r="E949" s="2" t="s">
         <v>2499</v>
-      </c>
-      <c r="E949" s="2" t="s">
-        <v>2500</v>
       </c>
       <c r="F949" t="s">
         <v>1587</v>
@@ -41421,7 +41436,7 @@
         <v>50111</v>
       </c>
       <c r="C952" s="6" t="s">
-        <v>2507</v>
+        <v>2506</v>
       </c>
       <c r="D952" s="2" t="e">
         <v>#N/A</v>
@@ -41526,7 +41541,7 @@
         <v>50114</v>
       </c>
       <c r="C955" s="6" t="s">
-        <v>2508</v>
+        <v>2507</v>
       </c>
       <c r="D955" s="2" t="e">
         <v>#N/A</v>
@@ -41841,7 +41856,7 @@
         <v>50131</v>
       </c>
       <c r="C964" s="6" t="s">
-        <v>2509</v>
+        <v>2508</v>
       </c>
       <c r="D964" s="2" t="e">
         <v>#N/A</v>
@@ -41911,7 +41926,7 @@
         <v>50133</v>
       </c>
       <c r="C966" s="6" t="s">
-        <v>2510</v>
+        <v>2509</v>
       </c>
       <c r="D966" s="2" t="e">
         <v>#N/A</v>
@@ -41946,7 +41961,7 @@
         <v>50134</v>
       </c>
       <c r="C967" s="6" t="s">
-        <v>2511</v>
+        <v>2510</v>
       </c>
       <c r="D967" s="2" t="e">
         <v>#N/A</v>
@@ -42086,7 +42101,7 @@
         <v>50142</v>
       </c>
       <c r="C971" s="6" t="s">
-        <v>2512</v>
+        <v>2511</v>
       </c>
       <c r="D971" s="2" t="e">
         <v>#N/A</v>
@@ -42121,7 +42136,7 @@
         <v>50143</v>
       </c>
       <c r="C972" s="6" t="s">
-        <v>2513</v>
+        <v>2512</v>
       </c>
       <c r="D972" s="2" t="e">
         <v>#N/A</v>
@@ -42156,7 +42171,7 @@
         <v>50144</v>
       </c>
       <c r="C973" s="6" t="s">
-        <v>2514</v>
+        <v>2513</v>
       </c>
       <c r="D973" s="2" t="e">
         <v>#N/A</v>
@@ -42191,7 +42206,7 @@
         <v>50145</v>
       </c>
       <c r="C974" s="6" t="s">
-        <v>2515</v>
+        <v>2514</v>
       </c>
       <c r="D974" s="2" t="e">
         <v>#N/A</v>
@@ -42261,7 +42276,7 @@
         <v>50211</v>
       </c>
       <c r="C976" s="6" t="s">
-        <v>2516</v>
+        <v>2515</v>
       </c>
       <c r="D976" s="2" t="e">
         <v>#N/A</v>
@@ -42296,7 +42311,7 @@
         <v>50212</v>
       </c>
       <c r="C977" s="6" t="s">
-        <v>2517</v>
+        <v>2516</v>
       </c>
       <c r="D977" s="2" t="e">
         <v>#N/A</v>
@@ -44084,10 +44099,10 @@
         <v>15</v>
       </c>
       <c r="D1028" s="2" t="s">
-        <v>2501</v>
+        <v>2500</v>
       </c>
       <c r="E1028" s="2" t="s">
-        <v>2529</v>
+        <v>2528</v>
       </c>
       <c r="F1028" t="s">
         <v>1587</v>
@@ -44390,7 +44405,7 @@
         <v>118</v>
       </c>
       <c r="E1037" s="2" t="s">
-        <v>2420</v>
+        <v>2419</v>
       </c>
       <c r="F1037" t="s">
         <v>105</v>
@@ -44646,10 +44661,10 @@
         <v>1148</v>
       </c>
       <c r="D1045" s="2" t="s">
-        <v>2524</v>
+        <v>2523</v>
       </c>
       <c r="E1045" s="2" t="s">
-        <v>2421</v>
+        <v>2420</v>
       </c>
       <c r="F1045" t="s">
         <v>1587</v>
@@ -44678,7 +44693,7 @@
         <v>1149</v>
       </c>
       <c r="D1046" s="2" t="s">
-        <v>2534</v>
+        <v>2533</v>
       </c>
       <c r="E1046" s="2" t="s">
         <v>2352</v>
@@ -44710,7 +44725,7 @@
         <v>1150</v>
       </c>
       <c r="D1047" s="2" t="s">
-        <v>2535</v>
+        <v>2534</v>
       </c>
       <c r="E1047" s="2" t="s">
         <v>2353</v>
@@ -44780,10 +44795,10 @@
         <v>1152</v>
       </c>
       <c r="D1049" s="2" t="s">
+        <v>2503</v>
+      </c>
+      <c r="E1049" s="2" t="s">
         <v>2504</v>
-      </c>
-      <c r="E1049" s="2" t="s">
-        <v>2505</v>
       </c>
       <c r="F1049" t="s">
         <v>1587</v>
@@ -44920,7 +44935,7 @@
         <v>1156</v>
       </c>
       <c r="D1053" s="2" t="s">
-        <v>2372</v>
+        <v>2371</v>
       </c>
       <c r="E1053" s="2" t="s">
         <v>2339</v>
@@ -45165,10 +45180,10 @@
         <v>1162</v>
       </c>
       <c r="D1060" s="2" t="s">
-        <v>2521</v>
+        <v>2520</v>
       </c>
       <c r="E1060" s="2" t="s">
-        <v>2520</v>
+        <v>2519</v>
       </c>
       <c r="F1060" t="s">
         <v>1826</v>
@@ -45177,7 +45192,7 @@
         <v>2079</v>
       </c>
       <c r="H1060" s="3" t="s">
-        <v>2480</v>
+        <v>2479</v>
       </c>
       <c r="I1060" t="s">
         <v>2082</v>
@@ -45340,10 +45355,10 @@
         <v>2095</v>
       </c>
       <c r="D1065" s="2" t="s">
+        <v>2521</v>
+      </c>
+      <c r="E1065" s="2" t="s">
         <v>2522</v>
-      </c>
-      <c r="E1065" s="2" t="s">
-        <v>2523</v>
       </c>
       <c r="F1065" t="s">
         <v>1587</v>
@@ -45585,7 +45600,7 @@
         <v>1166</v>
       </c>
       <c r="D1072" s="2" t="s">
-        <v>2482</v>
+        <v>2481</v>
       </c>
       <c r="E1072" s="2" t="s">
         <v>2028</v>
@@ -45912,7 +45927,7 @@
         <v>2079</v>
       </c>
       <c r="H1081" s="3" t="s">
-        <v>2481</v>
+        <v>2480</v>
       </c>
       <c r="I1081" t="s">
         <v>2142</v>
@@ -46250,10 +46265,10 @@
         <v>2159</v>
       </c>
       <c r="D1091" s="2" t="s">
+        <v>2488</v>
+      </c>
+      <c r="E1091" s="2" t="s">
         <v>2489</v>
-      </c>
-      <c r="E1091" s="2" t="s">
-        <v>2490</v>
       </c>
       <c r="F1091" t="s">
         <v>1587</v>
@@ -47753,7 +47768,7 @@
         <v>1215</v>
       </c>
       <c r="D1134" s="2" t="s">
-        <v>2425</v>
+        <v>2424</v>
       </c>
       <c r="E1134" s="2" t="s">
         <v>2327</v>
@@ -47861,7 +47876,7 @@
         <v>2322</v>
       </c>
       <c r="E1137" s="2" t="s">
-        <v>2530</v>
+        <v>2529</v>
       </c>
       <c r="F1137" t="s">
         <v>1587</v>
@@ -47998,7 +48013,7 @@
         <v>1222</v>
       </c>
       <c r="D1141" s="2" t="s">
-        <v>2494</v>
+        <v>2493</v>
       </c>
       <c r="E1141" s="2" t="e">
         <v>#N/A</v>
@@ -50028,7 +50043,7 @@
         <v>1279</v>
       </c>
       <c r="D1199" s="2" t="s">
-        <v>2488</v>
+        <v>2487</v>
       </c>
       <c r="E1199" s="2" t="s">
         <v>2316</v>
@@ -50588,10 +50603,10 @@
         <v>1295</v>
       </c>
       <c r="D1215" s="2" t="s">
-        <v>2417</v>
+        <v>2416</v>
       </c>
       <c r="E1215" s="2" t="s">
-        <v>2416</v>
+        <v>2415</v>
       </c>
       <c r="F1215" t="s">
         <v>1587</v>
@@ -50620,13 +50635,13 @@
         <v>68112</v>
       </c>
       <c r="C1216" s="6" t="s">
+        <v>2417</v>
+      </c>
+      <c r="D1216" s="2" t="s">
         <v>2418</v>
       </c>
-      <c r="D1216" s="2" t="s">
-        <v>2419</v>
-      </c>
       <c r="E1216" s="2" t="s">
-        <v>2422</v>
+        <v>2421</v>
       </c>
       <c r="F1216" t="s">
         <v>1587</v>
@@ -57128,7 +57143,7 @@
         <v>69</v>
       </c>
       <c r="D1402" s="2" t="s">
-        <v>2526</v>
+        <v>2525</v>
       </c>
       <c r="E1402" s="2" t="e">
         <v>#N/A</v>
@@ -57968,7 +57983,7 @@
         <v>78</v>
       </c>
       <c r="D1426" s="2" t="s">
-        <v>2525</v>
+        <v>2524</v>
       </c>
       <c r="E1426" s="2" t="e">
         <v>#N/A</v>
@@ -58738,7 +58753,7 @@
         <v>89</v>
       </c>
       <c r="D1448" s="2" t="s">
-        <v>2426</v>
+        <v>2425</v>
       </c>
       <c r="E1448" s="2" t="e">
         <v>#N/A</v>
@@ -59368,10 +59383,10 @@
         <v>90</v>
       </c>
       <c r="D1466" s="2" t="s">
+        <v>2438</v>
+      </c>
+      <c r="E1466" s="2" t="s">
         <v>2439</v>
-      </c>
-      <c r="E1466" s="2" t="s">
-        <v>2440</v>
       </c>
       <c r="F1466" t="s">
         <v>105</v>
@@ -59671,7 +59686,7 @@
         <v>97</v>
       </c>
       <c r="D1475" s="2" t="s">
-        <v>2427</v>
+        <v>2426</v>
       </c>
       <c r="E1475" s="2" t="e">
         <v>#N/A</v>
@@ -59703,10 +59718,10 @@
         <v>98</v>
       </c>
       <c r="D1476" s="2" t="s">
+        <v>2530</v>
+      </c>
+      <c r="E1476" s="2" t="s">
         <v>2531</v>
-      </c>
-      <c r="E1476" s="2" t="s">
-        <v>2532</v>
       </c>
       <c r="F1476" t="s">
         <v>1587</v>
@@ -60998,7 +61013,7 @@
         <v>1526</v>
       </c>
       <c r="D1513" s="2" t="s">
-        <v>2496</v>
+        <v>2495</v>
       </c>
       <c r="E1513" s="2" t="e">
         <v>#N/A</v>
@@ -61243,7 +61258,7 @@
         <v>1533</v>
       </c>
       <c r="D1520" s="2" t="s">
-        <v>2495</v>
+        <v>2494</v>
       </c>
       <c r="E1520" s="2" t="e">
         <v>#N/A</v>
@@ -61628,10 +61643,10 @@
         <v>1544</v>
       </c>
       <c r="D1531" s="2" t="s">
-        <v>2428</v>
+        <v>2427</v>
       </c>
       <c r="E1531" s="2" t="s">
-        <v>2433</v>
+        <v>2432</v>
       </c>
       <c r="F1531" t="s">
         <v>105</v>
@@ -61660,10 +61675,10 @@
         <v>1545</v>
       </c>
       <c r="D1532" s="2" t="s">
-        <v>2435</v>
+        <v>2434</v>
       </c>
       <c r="E1532" s="2" t="s">
-        <v>2434</v>
+        <v>2433</v>
       </c>
       <c r="F1532" t="s">
         <v>105</v>
@@ -61687,7 +61702,7 @@
         <v>1546</v>
       </c>
       <c r="D1533" s="2" t="s">
-        <v>2436</v>
+        <v>2435</v>
       </c>
       <c r="E1533" s="2"/>
       <c r="F1533" t="s">
@@ -61706,10 +61721,10 @@
         <v>1547</v>
       </c>
       <c r="D1534" s="2" t="s">
-        <v>2442</v>
+        <v>2441</v>
       </c>
       <c r="E1534" s="2" t="s">
-        <v>2437</v>
+        <v>2436</v>
       </c>
       <c r="F1534" t="s">
         <v>105</v>
@@ -61727,10 +61742,10 @@
         <v>1548</v>
       </c>
       <c r="D1535" s="2" t="s">
-        <v>2441</v>
+        <v>2440</v>
       </c>
       <c r="E1535" s="2" t="s">
-        <v>2438</v>
+        <v>2437</v>
       </c>
       <c r="F1535" t="s">
         <v>105</v>
@@ -61748,7 +61763,7 @@
         <v>1549</v>
       </c>
       <c r="D1536" s="2" t="s">
-        <v>2429</v>
+        <v>2428</v>
       </c>
       <c r="E1536" s="2" t="s">
         <v>1628</v>
@@ -61781,10 +61796,10 @@
         <v>1550</v>
       </c>
       <c r="D1537" s="2" t="s">
+        <v>2442</v>
+      </c>
+      <c r="E1537" s="2" t="s">
         <v>2443</v>
-      </c>
-      <c r="E1537" s="2" t="s">
-        <v>2444</v>
       </c>
       <c r="F1537" s="2" t="s">
         <v>1587</v>
@@ -61812,10 +61827,10 @@
         <v>1551</v>
       </c>
       <c r="D1538" s="2" t="s">
+        <v>2445</v>
+      </c>
+      <c r="E1538" s="2" t="s">
         <v>2446</v>
-      </c>
-      <c r="E1538" s="2" t="s">
-        <v>2447</v>
       </c>
       <c r="F1538" t="s">
         <v>1587</v>
@@ -61824,7 +61839,7 @@
         <v>2231</v>
       </c>
       <c r="H1538" s="2" t="s">
-        <v>2445</v>
+        <v>2444</v>
       </c>
       <c r="I1538" s="2" t="s">
         <v>2232</v>
@@ -61848,7 +61863,7 @@
         <v>2234</v>
       </c>
       <c r="E1539" s="2" t="s">
-        <v>2448</v>
+        <v>2447</v>
       </c>
       <c r="F1539" t="s">
         <v>1587</v>
@@ -61867,7 +61882,7 @@
         <v>1553</v>
       </c>
       <c r="D1540" s="2" t="s">
-        <v>2449</v>
+        <v>2448</v>
       </c>
       <c r="E1540" s="2" t="s">
         <v>2235</v>
@@ -61900,7 +61915,7 @@
         <v>2239</v>
       </c>
       <c r="E1541" s="2" t="s">
-        <v>2450</v>
+        <v>2449</v>
       </c>
       <c r="F1541" t="s">
         <v>1587</v>
@@ -61930,7 +61945,7 @@
         <v>2241</v>
       </c>
       <c r="E1542" s="2" t="s">
-        <v>2451</v>
+        <v>2450</v>
       </c>
       <c r="F1542" t="s">
         <v>1587</v>
@@ -61957,10 +61972,10 @@
         <v>1555</v>
       </c>
       <c r="D1543" s="2" t="s">
+        <v>2451</v>
+      </c>
+      <c r="E1543" s="2" t="s">
         <v>2452</v>
-      </c>
-      <c r="E1543" s="2" t="s">
-        <v>2453</v>
       </c>
       <c r="F1543" t="s">
         <v>1587</v>
@@ -61992,7 +62007,7 @@
         <v>1556</v>
       </c>
       <c r="D1544" s="2" t="s">
-        <v>2430</v>
+        <v>2429</v>
       </c>
       <c r="E1544" s="2" t="s">
         <v>1629</v>
@@ -62004,7 +62019,7 @@
         <v>2245</v>
       </c>
       <c r="I1544" s="2" t="s">
-        <v>2454</v>
+        <v>2453</v>
       </c>
       <c r="J1544" s="2"/>
       <c r="K1544" s="2" t="s">
@@ -62022,10 +62037,10 @@
         <v>2298</v>
       </c>
       <c r="D1545" s="2" t="s">
-        <v>2456</v>
+        <v>2455</v>
       </c>
       <c r="E1545" s="2" t="s">
-        <v>2455</v>
+        <v>2454</v>
       </c>
       <c r="F1545" t="s">
         <v>1587</v>
@@ -62178,10 +62193,10 @@
         <v>1561</v>
       </c>
       <c r="D1550" s="2" t="s">
-        <v>2458</v>
+        <v>2457</v>
       </c>
       <c r="E1550" s="2" t="s">
-        <v>2457</v>
+        <v>2456</v>
       </c>
       <c r="F1550" s="2" t="s">
         <v>1587</v>
@@ -62199,10 +62214,10 @@
         <v>1562</v>
       </c>
       <c r="D1551" s="2" t="s">
-        <v>2460</v>
+        <v>2459</v>
       </c>
       <c r="E1551" s="2" t="s">
-        <v>2459</v>
+        <v>2458</v>
       </c>
       <c r="F1551" s="2" t="s">
         <v>1587</v>
@@ -62220,10 +62235,10 @@
         <v>1563</v>
       </c>
       <c r="D1552" s="2" t="s">
+        <v>2460</v>
+      </c>
+      <c r="E1552" s="2" t="s">
         <v>2461</v>
-      </c>
-      <c r="E1552" s="2" t="s">
-        <v>2462</v>
       </c>
       <c r="F1552" s="2" t="s">
         <v>1587</v>
@@ -62241,16 +62256,16 @@
         <v>1564</v>
       </c>
       <c r="D1553" s="2" t="s">
-        <v>2431</v>
+        <v>2430</v>
       </c>
       <c r="E1553" s="15" t="s">
-        <v>2463</v>
+        <v>2462</v>
       </c>
       <c r="F1553" t="s">
         <v>1587</v>
       </c>
       <c r="G1553" t="s">
-        <v>2464</v>
+        <v>2463</v>
       </c>
       <c r="K1553"/>
     </row>
@@ -62265,10 +62280,10 @@
         <v>1565</v>
       </c>
       <c r="D1554" s="2" t="s">
-        <v>2465</v>
+        <v>2464</v>
       </c>
       <c r="E1554" s="2" t="s">
-        <v>2432</v>
+        <v>2431</v>
       </c>
       <c r="F1554" s="2" t="s">
         <v>1587</v>
@@ -62302,10 +62317,10 @@
         <v>104</v>
       </c>
       <c r="D1556" s="2" t="s">
-        <v>2497</v>
+        <v>2496</v>
       </c>
       <c r="E1556" s="2" t="s">
-        <v>2466</v>
+        <v>2465</v>
       </c>
       <c r="F1556" s="2" t="s">
         <v>1587</v>

--- a/data/kbli_populer_riau2.xlsx
+++ b/data/kbli_populer_riau2.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4763" uniqueCount="2543">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5024" uniqueCount="2777">
   <si>
     <t>kategori</t>
   </si>
@@ -7204,9 +7204,6 @@
     <t>Kelompok ini mencakup kegiatan pertanian tebu, termasuk di dalamnya kegiatan pengolahan lahan, penanaman, pemeliharaan, pemanenan, dan kegiatan pascapanen yang dilakukan sebagai satu rangkaian kegiatan. Kelompok ini tidak mencakup pertanian bit gula.</t>
   </si>
   <si>
-    <t>Kegiatan pengolahan lahan, penanaman, pemeliharaan, dan juga pemanenan dan pasca panen jika menjadi satu kesatuan kegiatan tanaman jagung. Termasuk kegiatan pembibitan dan pembenihan tanaman jagung. membudidayakan tanaman jagung. luas kurang dari 25 Ha.</t>
-  </si>
-  <si>
     <t>Petani Jagung; mencakup kegiatan penanaman jagung untuk menghasilkan benih berupa biji;</t>
   </si>
   <si>
@@ -7217,9 +7214,6 @@
   </si>
   <si>
     <t>Petani gandum; petani sorgum; gandum hitam; barli;</t>
-  </si>
-  <si>
-    <t>Petani kedelai;</t>
   </si>
   <si>
     <t>kedelai; membudidayakan kedelai; menanam kedelai; kedelai sayur atau edamame tidak termasuk (masuk kbli 01116)</t>
@@ -7624,9 +7618,6 @@
     <t>Menjual pecah belah; menjual peralatan dapur;</t>
   </si>
   <si>
-    <t>Toko kosmetik; menjual bedak; menjual kosmetik;</t>
-  </si>
-  <si>
     <t>kurir; jasa kurir;</t>
   </si>
   <si>
@@ -7658,9 +7649,6 @@
     <t>Toko hijab/jilbab; Toko Kaos kaki; jual benang jahit, kancing, risleting;</t>
   </si>
   <si>
-    <t>Toko sepatu;</t>
-  </si>
-  <si>
     <t>jual sepatu; jual sendal; sepatu; sendal;</t>
   </si>
   <si>
@@ -7674,13 +7662,765 @@
   </si>
   <si>
     <t>Toko tas sekolah; Jual payung eceran;</t>
+  </si>
+  <si>
+    <t>Toko sepatu; Toko sendal;</t>
+  </si>
+  <si>
+    <t>Toko kosmetik; menjual bedak; menjual kosmetik; jual kosmetik; beauty;</t>
+  </si>
+  <si>
+    <t>jual perhiasan; jual emas; toko mas;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">toko mas; </t>
+  </si>
+  <si>
+    <t>Jual seprai; jual bedcover; jual gorden;</t>
+  </si>
+  <si>
+    <t>sprei, seprai, bedcover, selimut, sarung bantal; gorden, horden, hordeng;</t>
+  </si>
+  <si>
+    <t>Jual kacamata, toko kacamata;</t>
+  </si>
+  <si>
+    <t>Toko jam Abbas; Toko jam;</t>
+  </si>
+  <si>
+    <t>jual jam tangan; jual jam dinding; menjual jam;</t>
+  </si>
+  <si>
+    <t>Petani kedelai; Budidaya kedelai; Menanam kedelai; Memproduksi benih kedelai; Penangkaran benih kedelai; Pengolahan lahan kedelai; Pemeliharaan tanaman kedelai; Pemanenan kedelai; Pascapanen kedelai sebagai satu kesatuan kegiatan budidaya;</t>
+  </si>
+  <si>
+    <t>Budidaya kacang tanah; Menanam kacang tanah; Memproduksi benih kacang tanah; Penangkaran benih kacang tanah; Pengolahan lahan kacang tanah; Pemeliharaan tanaman kacang tanah; Pemanenan kacang tanah; Pascapanen kacang tanah sebagai satu kesatuan kegiatan budidaya</t>
+  </si>
+  <si>
+    <t>Budidaya kacang hijau; Menanam kacang hijau; Memproduksi benih kacang hijau; Penangkaran benih kacang hijau; Pengolahan lahan kacang hijau; Pemeliharaan tanaman kacang hijau; Pemanenan kacang hijau; Pascapanen kacang hijau sebagai satu kesatuan kegiatan budidaya</t>
+  </si>
+  <si>
+    <t>Budidaya aneka kacang; Menanam kacang panjang; Menanam buncis; Menanam kacang merah; Menanam kapri; Menanam kecipir; Memproduksi benih aneka kacang; Penangkaran benih aneka kacang; Pengolahan lahan; Pemeliharaan tanaman; Pemanenan; Pascapanen sebagai satu kesatuan kegiatan budidaya</t>
+  </si>
+  <si>
+    <t>Budidaya biji-bijian penghasil minyak makan; Menanam wijen; Menanam bunga matahari; Menanam kanola; Menanam safflower; Memproduksi benih tanaman penghasil minyak makan; Penangkaran benih tanaman penghasil minyak makan; Pengolahan lahan; Pemeliharaan tanaman; Pemanenan; Pascapanen sebagai satu kesatuan kegiatan budidaya</t>
+  </si>
+  <si>
+    <t>Budidaya biji-bijian penghasil minyak selain minyak makan; Menanam biji jarak pohon; Menanam biji kapas; Menanam biji rami; Menanam biji moster; Menanam niger seed; Memproduksi benih tanaman penghasil minyak nonpangan; Penangkaran benih tanaman penghasil minyak nonpangan; Pengolahan lahan; Pemeliharaan tanaman; Pemanenan; Pascapanen sebagai satu kesatuan kegiatan budidaya</t>
+  </si>
+  <si>
+    <t>Budidaya padi hibrida; Pengolahan lahan padi hibrida; Penyemaian padi hibrida; Penanaman padi hibrida; Pemeliharaan tanaman padi hibrida; Pemanenan padi hibrida; Pascapanen padi hibrida sebagai satu kesatuan kegiatan budidaya; Memproduksi benih padi hibrida; Penangkaran benih padi hibrida</t>
+  </si>
+  <si>
+    <t>Budidaya padi inbrida; Pengolahan lahan padi inbrida; Penyemaian padi inbrida; Penanaman padi inbrida; Pemeliharaan tanaman padi inbrida; Pemanenan padi inbrida; Pascapanen padi inbrida sebagai satu kesatuan kegiatan budidaya; Memproduksi benih padi inbrida; Penangkaran benih padi inbrida.</t>
+  </si>
+  <si>
+    <t>Budidaya sayuran daun; Menanam sawi; Menanam kubis; Menanam kembang kol; Menanam brokoli; Menanam selada; Menanam seledri; Menanam daun bawang; Menanam bayam; Menanam kangkung; Menanam asparagus; Pengolahan lahan; Penyemaian; Pemeliharaan tanaman; Pemanenan; Pascapanen sebagai satu kesatuan kegiatan budidaya; Memproduksi benih sayuran daun; Penangkaran benih sayuran daun</t>
+  </si>
+  <si>
+    <t>Budidaya buah semusim; Menanam semangka; Menanam melon; Menanam blewah; Menanam timun suri; Pengolahan lahan; Penyemaian; Pemeliharaan tanaman; Pemanenan; Pascapanen sebagai satu kesatuan kegiatan budidaya; Memproduksi benih buah semusim; Penangkaran benih buah semusim</t>
+  </si>
+  <si>
+    <t>Budidaya sayuran buah; Menanam mentimun; Menanam tomat; Menanam terung; Menanam labu siam; Menanam labu kuning; Menanam gambas (oyong); Menanam belimbing sayur; Pengolahan lahan; Penyemaian; Pemeliharaan tanaman; Pemanenan; Pascapanen sebagai satu kesatuan kegiatan budidaya; Memproduksi benih sayuran buah; Penangkaran benih sayuran buah</t>
+  </si>
+  <si>
+    <t>Budidaya sayuran umbi; Menanam kentang; Menanam wortel; Menanam lobak cina; Menanam rebung; Menanam bawang putih; Menanam bawang bombai; Menanam bawang merah; Menanam bawang perai; Pengolahan lahan; Penyemaian; Pemeliharaan tanaman; Pemanenan; Pascapanen sebagai satu kesatuan kegiatan budidaya; Memproduksi benih sayuran umbi; Penangkaran benih sayuran umbi.</t>
+  </si>
+  <si>
+    <t>Budidaya ubi kayu; Menanam ubi kayu; Menanam singkong; Pengolahan lahan ubi kayu; Penanaman ubi kayu; Pemeliharaan tanaman ubi kayu; Pemanenan ubi kayu; Pascapanen ubi kayu sebagai satu kesatuan kegiatan budidaya; Memproduksi bibit ubi kayu; Penangkaran bibit ubi kayu</t>
+  </si>
+  <si>
+    <t>ESENSIAL</t>
+  </si>
+  <si>
+    <t>Budidaya jamur; Menanam jamur; Budidaya jamur tiram; Budidaya jamur merang; Budidaya jamur kuping; Budidaya jamur shiitake; Budidaya jamur kancing; Pengolahan media tanam jamur; Pemeliharaan jamur; Pemanenan jamur; Pascapanen jamur sebagai satu kesatuan kegiatan budidaya; Memproduksi bibit jamur; Penangkaran bibit jamur</t>
+  </si>
+  <si>
+    <t>Budidaya bit gula; Budidaya stevia; Budidaya sorgum manis; Menanam bit gula; Menanam stevia; Menanam sorgum manis; Pengolahan lahan; Penanaman; Pemeliharaan tanaman; Pemanenan; Pascapanen sebagai satu kesatuan kegiatan budidaya; Memproduksi benih tanaman pemanis; Penangkaran benih tanaman pemanis</t>
+  </si>
+  <si>
+    <t>Budidaya cabai; Menanam cabai; Menanam cabai rawit; Menanam cabai merah; Menanam cabai keriting; Menanam paprika; Pengolahan lahan; Penyemaian; Penanaman; Pemeliharaan tanaman cabai; Pemanenan cabai; Pascapanen cabai sebagai satu kesatuan kegiatan budidaya; Memproduksi benih cabai; Penangkaran benih cabai</t>
+  </si>
+  <si>
+    <t>Budidaya umbi lainnya; Menanam ubi jalar; Menanam talas; Menanam porang; Menanam iles-iles; Menanam ganyong; Menanam gembili; Menanam garut (irut); Pengolahan lahan; Penanaman; Pemeliharaan tanaman; Pemanenan; Pascapanen sebagai satu kesatuan kegiatan budidaya; Memproduksi bibit umbi; Penangkaran bibit umbi.</t>
+  </si>
+  <si>
+    <t>Budidaya tebu; Menanam tebu; Pengolahan lahan tebu; Pembibitan tebu; Perbenihan tebu; Penanaman tebu; Pemeliharaan tanaman tebu; Pemanenan tebu; Pascapanen tebu sebagai satu kesatuan kegiatan budidaya; Memproduksi bibit tebu; Penangkaran bibit tebu</t>
+  </si>
+  <si>
+    <t>Budidaya tembakau; Menanam tembakau; Pengolahan lahan tembakau; Penyemaian tembakau; Pembibitan tembakau; Penanaman tembakau; Pemeliharaan tanaman tembakau; Pemanenan tembakau; Pembersihan daun tembakau; Perajangan tembakau sebagai bagian dari kegiatan budidaya; Pascapanen tembakau sebagai satu kesatuan kegiatan budidaya; Memproduksi benih tembakau; Penangkaran benih tembakau</t>
+  </si>
+  <si>
+    <t>tembakau; membudidayakan; menanam; pengolahan lahan; penyemaian; pemeliharaan; pemanenan; pascapanen; pembersihan tembakau; perajangan tembakau; benih tembakau; biji tembakau</t>
+  </si>
+  <si>
+    <t>SANGAT JARANG DITEMUKAN</t>
+  </si>
+  <si>
+    <t>Budidaya tanaman berserat; Menanam kapuk; Menanam kapas; Menanam rosela; Menanam rami; Menanam yute; Menanam kenaf; Menanam sisal; Menanam agave; Menanam abaka; Pengolahan lahan; Penyemaian; Penanaman; Pemeliharaan tanaman; Pemanenan; Pascapanen sebagai satu kesatuan kegiatan budidaya; Memproduksi benih tanaman berserat; Penangkaran benih tanaman berserat</t>
+  </si>
+  <si>
+    <t>kapas; yute; kenaf; batang lenan; rami; sisal; abaka; agave; bahan baku tekstil; serat alam; menanam; membudidayakan; pengolahan lahan; pemeliharaan; pemanenan; pascapanen; benih tanaman berserat; biji</t>
+  </si>
+  <si>
+    <t>Budidaya tanaman pakan ternak; Menanam rumput gajah; Menanam rumput odot; Menanam rumput raja; Menanam setaria; Menanam alfalfa; Menanam kaliandra; Menanam gamal; Menanam lamtoro; Menanam Indigofera zollingeriana; Pengolahan lahan; Penyemaian; Penanaman; Pemeliharaan tanaman; Pemanenan; Pascapanen sebagai satu kesatuan kegiatan budidaya; Memproduksi benih tanaman pakan ternak; Penangkaran benih tanaman pakan ternak</t>
+  </si>
+  <si>
+    <t>rumput pakan ternak; hijauan pakan ternak; tanaman legum; kacang-kacangan; rumput gajah; rumput raja; rumput odot; rumput setaria; alfalfa; lamtoro; Indigoferea zollingeriana; menanam; membudidayakan; pengolahan lahan; pemeliharaan; pemanenan; pascapanen</t>
+  </si>
+  <si>
+    <t>Pembenihan tanaman pakan ternak; Pembenihan bit pakan (bukan bit gula); Produksi benih rumput gajah; Produksi benih rumput odot; Produksi benih rumput raja; Produksi benih setaria; Produksi benih alfalfa; Produksi benih kaliandra; Produksi benih gamal; Produksi benih lamtoro; Produksi benih Indigofera zollingeriana; Pengolahan lahan; Penanaman; Pemeliharaan tanaman; Pemanenan benih; Pengolahan benih; Penangkaran benih tanaman pakan ternak.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pembenihan; benih biji; tanaman pakan ternak; bit; bukan bit gula; rumput pakan ternak; legum pakan ternak; rumput gajah; rumput raja; rumput odot; rumput setaria; alfalfa; kaliandra; gamal; lamtoro; Indigofera zollingeriana; pengolahan lahan; penanaman; pascapanen
+</t>
+  </si>
+  <si>
+    <t>Budidaya tanaman bunga; Menanam anggrek; Menanam mawar; Menanam melati; Menanam krisan; Menanam anyelir; Menanam gerbera; Menanam gladiol; Menanam sedap malam; Pengolahan lahan; Pembibitan tanaman bunga; Penanaman; Pemeliharaan tanaman bunga; Pemanenan bunga potong; Pascapanen bunga sebagai satu kesatuan kegiatan budidaya; Memproduksi benih tanaman bunga; Penangkaran benih tanaman bunga</t>
+  </si>
+  <si>
+    <t>tanaman bunga; bunga potong; kuncup bunga; anggrek; anyelir; gerbera; hebras; gladiol; krisan; mawar; melati; sedap malam; menanam; membudidayakan; pengolahan lahan; pemeliharaan; pemanenan; pascapanen</t>
+  </si>
+  <si>
+    <t>Pembenihan tanaman bunga; Produksi benih tanaman bunga; Penangkaran benih tanaman bunga; Pembibitan tanaman bunga; Perbanyakan bibit tanaman bunga; Menyeleksi benih tanaman bunga; Pemeliharaan tanaman induk bunga; Pemanenan benih bunga; Pengolahan benih tanaman bunga; Pengemasan benih tanaman bunga; Penyimpanan benih tanaman bunga; Sertifikasi benih tanaman bunga</t>
+  </si>
+  <si>
+    <t>pembenihan; tanaman bunga; benih biji; biji bunga; bahan tanam vegetatif; batang stek; tunas; bibit; perbanyakan tanaman bunga; pengolahan lahan; penanaman; pemeliharaan; pemanenan; pascapanen</t>
+  </si>
+  <si>
+    <t>Budidaya tanaman semusim lainnya; Menanam tanaman semusim lainnya; Pengolahan lahan; Penyemaian; Penanaman; Pemeliharaan tanaman; Pemanenan; Pengolahan pascapanen sebagai satu kesatuan kegiatan budidaya; Memproduksi benih tanaman semusim; Penangkaran benih tanaman semusim</t>
+  </si>
+  <si>
+    <t>tanaman semusim; tanaman semusim lainnya; YTDL; belum terklasifikasi; benih biji; menanam; membudidayakan; pengolahan lahan; pemeliharaan; pemanenan; pascapanen</t>
+  </si>
+  <si>
+    <t>UMUM DITEMUKAN</t>
+  </si>
+  <si>
+    <t>Budidaya buah anggur; Menanam anggur; Pengolahan lahan kebun anggur; Pembibitan tanaman anggur; Perbenihan tanaman anggur; Penanaman anggur; Pemeliharaan tanaman anggur; Pemanenan buah anggur; Pascapanen buah anggur sebagai satu kesatuan kegiatan budidaya; Memproduksi bibit anggur; Penangkaran bibit anggur</t>
+  </si>
+  <si>
+    <t>buah anggur; konsumsi langsung; wine; jus; cuka; kismis; zante currants; sultana; anggur kering; penanaman; pengolahan lahan; pemeliharaan; pemanenan; pascapanen; benih anggur; biji anggur</t>
+  </si>
+  <si>
+    <t>Kegiatan pertanian buah anggur untuk konsumsi langsung atau untuk memproduksi wine, jus, cuka, dan buah yang dikeringkan (seperti kismis, zante currants, sultana). Mencakup pengolahan lahan, penanaman, pemeliharaan, pemanenan, dan pascapanen sebagai satu kesatuan, serta penanaman untuk menghasilkan benih biji. Tidak mencakup pembuatan wine serta pengolahan dan pengawetan anggur.</t>
+  </si>
+  <si>
+    <t>buah tropis; buah subtropis; alpukat; pisang; pisang raja; kurma; buah ara; pepaya; nanas; rambutan; durian; duku; jambu biji; jambu air; lengkeng; nangka; mangga; manggis; sawo; belimbing; salak; sirsak; buah naga; menanam; membudidayakan; pengolahan lahan; pemeliharaan; pemanenan; pascapanen; benih buah; biji buah</t>
+  </si>
+  <si>
+    <t>Kegiatan pertanian buah-buahan tropis dan subtropis, seperti alpukat, pisang dan pisang raja, kurma, buah ara, pepaya, nanas, rambutan, durian, duku, jambu biji, jambu air, lengkeng, nangka, mangga, manggis, sawo, belimbing, salak, sirsak, dan buah naga. Mencakup pengolahan lahan, penanaman, pemeliharaan, pemanenan, dan pascapanen sebagai satu kesatuan, serta penanaman untuk menghasilkan benih berupa biji.</t>
+  </si>
+  <si>
+    <t>buah jeruk; jeruk bali; jeruk lemon; jeruk nipis; limau; jeruk siam; jeruk keprok; jeruk mandarin; tangerine; clementine; menanam; membudidayakan; pengolahan lahan; pemeliharaan; pemanenan; pascapanen; benih jeruk; biji jeruk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kegiatan pertanian buah jeruk, seperti jeruk bali, jeruk lemon, jeruk nipis, limau, jeruk siam, jeruk keprok, jeruk mandarin, tangerine, dan clementine. Mencakup pengolahan lahan, penanaman, pemeliharaan, pemanenan, dan pascapanen sebagai satu kesatuan, serta penanaman untuk menghasilkan benih berupa biji. 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">buah apel; buah batu; pome fruits; stone fruits; aprikot; ceri; persik; nektarin; pir; quince; plum; sloe; markisa; kepel; terong belanda; buah delima; menanam; membudidayakan; pengolahan lahan; pemeliharaan; pemanenan; pascapanen; benih buah; biji buah 
+</t>
+  </si>
+  <si>
+    <t>Kegiatan pertanian buah apel dan buah batu (pome and stone fruits), seperti aprikot, ceri, persik, nektarin, pir, quince, plum, sloe, markisa, kepel, terong belanda, dan buah delima. Mencakup pengolahan lahan, penanaman, pemeliharaan, pemanenan, dan pascapanen sebagai satu kesatuan, serta penanaman untuk menghasilkan benih berupa biji.</t>
+  </si>
+  <si>
+    <t>buah beri; bluberi; kismis; currants; gooseberry; kiwi; rasberi; stroberi; menanam; membudidayakan; pengolahan lahan; pemeliharaan; pemanenan; pascapanen; benih beri; biji beri</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kegiatan pertanian buah beri seperti bluberi, kismis (currants), gooseberry, kiwi, rasberi, dan stroberi. Mencakup pengolahan lahan, penanaman, pemeliharaan, pemanenan, dan pascapanen sebagai satu kesatuan, serta penanaman untuk menghasilkan benih berupa biji. 
+</t>
+  </si>
+  <si>
+    <t>buah biji kacang-kacangan; almon; kacang mete; chestnut; kenari; walnut; kacang hazel; kacang pistasio; menanam; membudidayakan; pengolahan lahan; pemeliharaan; pemanenan; pascapanen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kegiatan pertanian tanaman buah biji kacang-kacangan yang dapat dimakan, seperti almon, kacang mete, chestnut, kenari (walnut), kacang hazel, dan kacang pistasio. Mencakup pengolahan lahan, penanaman, pemeliharaan, pemanenan, dan pascapanen sebagai satu rangkaian kegiatan. 
+</t>
+  </si>
+  <si>
+    <t>sayuran tahunan; kluwih; timbul; sukun; nangka sayur; petai; jengkol; melinjo; menanam; membudidayakan; pengolahan lahan; pemeliharaan; pemanenan; pascapanen; benih sayuran tahunan; biji sayuran tahunan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kegiatan pertanian tanaman sayuran tahunan, seperti kluwih/timbul, sukun, nangka sayur, petai, jengkol, dan melinjo. Mencakup pengolahan lahan, penanaman, pemeliharaan, pemanenan, dan pascapanen sebagai satu rangkaian kegiatan, serta penanaman untuk menghasilkan benih berupa biji. 
+</t>
+  </si>
+  <si>
+    <t>buah semak; tanaman semak; kacang lokus; locust beans; pengolahan lahan; penyemaian; penanaman; pemeliharaan; pemanenan; pascapanen</t>
+  </si>
+  <si>
+    <t>Kegiatan pertanian tanaman semak lainnya, seperti kacang lokus/locust beans, termasuk di dalamnya kegiatan pengolahan lahan, penyemaian, penanaman, pemeliharaan, pemanenan, dan kegiatan pascapanen yang dilakukan sebagai satu rangkaian kegiatan.</t>
+  </si>
+  <si>
+    <t>kelapa; pembibitan kelapa; menanam; membudidayakan; pengolahan lahan; pemeliharaan; pemanenan; pascapanen; benih kelapa; biji kelapa</t>
+  </si>
+  <si>
+    <t>Kegiatan pertanian kelapa, termasuk pengolahan lahan, pembibitan, penanaman, pemeliharaan, pemanenan, dan pascapanen sebagai satu rangkaian kegiatan, serta penanaman untuk menghasilkan benih berupa biji.</t>
+  </si>
+  <si>
+    <t>kelapa sawit; sawit; menanam; membudidayakan; pengolahan lahan; pemeliharaan; pemanenan; pascapanen; benih kelapa sawit; biji kelapa sawit</t>
+  </si>
+  <si>
+    <t>Kegiatan pertanian kelapa sawit, termasuk pengolahan lahan, penanaman, pemeliharaan, pemanenan, dan pascapanen sebagai satu rangkaian kegiatan, serta penanaman untuk menghasilkan benih berupa biji.</t>
+  </si>
+  <si>
+    <t>buah oleagin; zaitun; menanam; membudidayakan; pengolahan lahan; pemeliharaan; pemanenan; pascapanen; benih oleagin; biji oleagin</t>
+  </si>
+  <si>
+    <t>Kegiatan pertanian buah oleagin lainnya, seperti zaitun, termasuk pengolahan lahan, penanaman, pemeliharaan, pemanenan, dan pascapanen sebagai satu rangkaian kegiatan, serta penanaman untuk menghasilkan benih berupa biji.</t>
+  </si>
+  <si>
+    <t>kopi; menanam; membudidayakan; pengolahan lahan; pemeliharaan; pemanenan; pascapanen; biji kopi; benih kopi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kegiatan pertanian kopi, termasuk pengolahan lahan, penanaman, pemeliharaan, pemanenan, dan pascapanen sebagai satu rangkaian kegiatan. 
+</t>
+  </si>
+  <si>
+    <t>teh; menanam; membudidayakan; pengolahan lahan; pemeliharaan; pemanenan; pascapanen; benih teh; biji teh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kegiatan pertanian teh, termasuk pengolahan lahan, penanaman, pemeliharaan, pemanenan, dan pascapanen sebagai satu rangkaian kegiatan, serta penanaman untuk menghasilkan benih berupa biji. 
+</t>
+  </si>
+  <si>
+    <t>kakao; coklat; menanam; membudidayakan; pengolahan lahan; pemeliharaan; pemanenan; pascapanen; benih kakao; biji kakao</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kegiatan pertanian kakao, termasuk pengolahan lahan, penanaman, pemeliharaan, pemanenan, dan pascapanen sebagai satu rangkaian kegiatan, serta penanaman untuk menghasilkan benih berupa biji. 
+</t>
+  </si>
+  <si>
+    <t>bahan minuman; tanaman minuman; menanam; membudidayakan; pengolahan lahan; pemeliharaan; pemanenan; pascapanen</t>
+  </si>
+  <si>
+    <t>Kegiatan pertanian tanaman untuk bahan minuman lainnya, termasuk pengolahan lahan, penanaman, pemeliharaan, pemanenan, dan pascapanen sebagai satu rangkaian kegiatan.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lada; merica; Piper spp; cabai jawa; cabai jamu; menanam; membudidayakan; pengolahan lahan; pemeliharaan; pemanenan; pascapanen 
+</t>
+  </si>
+  <si>
+    <t>Kegiatan pertanian lada atau merica (Piper spp), termasuk pengolahan lahan, penanaman, pemeliharaan, pemanenan, dan pascapanen sebagai satu rangkaian kegiatan. Kelompok ini juga mencakup kegiatan pertanian cabai jawa/cabai jamu.</t>
+  </si>
+  <si>
+    <t>cengkih; cengkeh; menanam; membudidayakan; pengolahan lahan; pemeliharaan; pemanenan; pascapanen; benih cengkih; biji cengkih</t>
+  </si>
+  <si>
+    <t>Kegiatan pertanian cengkih, termasuk pengolahan lahan, penanaman, pemeliharaan, pemanenan, dan pascapanen sebagai satu rangkaian kegiatan, serta penanaman untuk menghasilkan benih berupa biji.</t>
+  </si>
+  <si>
+    <t>pala; menanam; membudidayakan; pengolahan lahan; pemeliharaan; pemanenan; pascapanen; benih pala; biji pala</t>
+  </si>
+  <si>
+    <t>Kegiatan pertanian pala, termasuk pengolahan lahan, penanaman, pemeliharaan, pemanenan, dan pascapanen sebagai satu kesatuan kegiatan, serta penanaman untuk menghasilkan benih berupa biji.</t>
+  </si>
+  <si>
+    <t>tanaman aromatik; tanaman penyegar; serai wangi; nilam; mentol; kenanga; ilang-ilang; gandapura; lawang; gaharu; kayu putih; daun kayu putih; menanam; membudidayakan; pengolahan lahan; penyemaian; pemeliharaan; pemanenan; pascapanen; kawasan hutan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kegiatan pertanian tanaman aromatik/penyegar, seperti serai wangi, nilam, mentol, kenanga, ilang-ilang, gandapura, lawang, dan gaharu, serta pertanian pohon kayu putih untuk menghasilkan daun kayu putih. Mencakup pengolahan lahan, penyemaian, pemeliharaan, pemanenan, dan pascapanen sebagai satu rangkaian kegiatan. Kelompok ini juga mencakup kegiatan yang dilakukan dalam kawasan hutan. 
+</t>
+  </si>
+  <si>
+    <t>tanaman obat; rimpang; biofarmaka; pestisida nabati; jahe; kunyit; temulawak; temugiring; temuireng; temukunci; kencur; lengkuas; lempuyang; dlingo; menanam; membudidayakan; pengolahan lahan; penyemaian; pemeliharaan; pemanenan; pascapanen; benih rimpang; biji rimpang</t>
+  </si>
+  <si>
+    <t>Kegiatan pertanian tanaman obat rimpang (termasuk bahan pestisida nabati), seperti jahe, kunyit, temulawak, temugiring, temuireng, temukunci, kencur, lengkuas, lempuyang, dan dlingo. Mencakup pengolahan lahan, penyemaian, penanaman, pemeliharaan, pemanenan, dan pascapanen sebagai satu rangkaian kegiatan, serta penanaman untuk menghasilkan benih berupa biji.</t>
+  </si>
+  <si>
+    <t>tanaman obat; nonrimpang; pestisida nabati; kapulaga; lidah buaya; sambiloto; mengkudu; pace; mahkota dewa; serai hijau; menanam; membudidayakan; pengolahan lahan; pemeliharaan; pemanenan; pascapanen; benih obat; biji obat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kegiatan pertanian tanaman obat nonrimpang (termasuk bahan pestisida nabati), seperti kapulaga, lidah buaya, sambiloto, mengkudu atau pace, mahkota dewa, dan serai hijau. Mencakup pengolahan lahan, penanaman, pemeliharaan, pemanenan, dan pascapanen sebagai satu rangkaian kegiatan, serta penanaman untuk menghasilkan benih berupa biji. 
+</t>
+  </si>
+  <si>
+    <t>narkotika; tanaman obat terlarang; menanam; membudidayakan; pengolahan lahan; pemeliharaan; pemanenan; pascapanen</t>
+  </si>
+  <si>
+    <t>Kegiatan pertanian narkotika dan tanaman obat terlarang, termasuk pengolahan lahan, penanaman, pemeliharaan, pemanenan, dan pascapanen sebagai satu rangkaian kegiatan.</t>
+  </si>
+  <si>
+    <t>rempah-rempah; aromatik; penyegar; kemiri; vanili; kayu manis; ginseng; kina; adas; pinang; gambir; menanam; membudidayakan; pengolahan lahan; pemeliharaan; pemanenan; pascapanen; benih rempah; biji rempah</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kegiatan pertanian tanaman rempah lainnya, seperti kemiri, vanili, kayu manis, ginseng, kina, adas, pinang, dan gambir. Mencakup pengolahan lahan, penanaman, pemeliharaan, pemanenan, dan pascapanen sebagai satu rangkaian kegiatan, serta penanaman untuk menghasilkan benih berupa biji. 
+</t>
+  </si>
+  <si>
+    <t>karet; getah; damar; pinus; kemenyan; tanaman penghasil getah; menanam; membudidayakan; pengolahan lahan; pemeliharaan; pemanenan; pascapanen; kawasan hutan; benih karet; biji karet</t>
+  </si>
+  <si>
+    <t>Kegiatan pertanian tanaman penghasil getah seperti karet dan tanaman penghasil getah lainnya (misalnya damar, pinus, dan kemenyan). Mencakup pengolahan lahan, penanaman, pemeliharaan, pemanenan, dan pascapanen sebagai satu rangkaian kegiatan. Kelompok ini juga mencakup kegiatan yang dilakukan dalam kawasan hutan, serta penanaman untuk menghasilkan benih berupa biji.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tanaman tahunan; YTDL; cemara; jarak pagar; aren; kaliandra; gamal; bambu; rotan; tanaman anyaman; trubusan; tanaman energi; poplar; dedalu; menanam; membudidayakan; pengolahan lahan; pemeliharaan; pemanenan; pascapanen; kawasan hutan; benih tahunan; biji tahunan 
+</t>
+  </si>
+  <si>
+    <t>Kegiatan pertanian tanaman tahunan lainnya, seperti cemara, tanaman jarak pagar, aren, kaliandra, gamal, tanaman penganyam (bambu dan rotan), serta tanaman berdaur pendek sebagai tanaman energi (poplar dan dedalu). Mencakup pengolahan lahan, penanaman, pemeliharaan, pemanenan, dan pascapanen sebagai satu rangkaian kegiatan, termasuk yang dilakukan dalam kawasan hutan, serta penanaman untuk menghasilkan benih berupa biji.</t>
+  </si>
+  <si>
+    <t>tanaman hias; tanaman hias daun; tanaman hias bunga; bonsai; suplir; kuping gajah; helikonia; pisang-pisangan; dracaena; filodendron; monstera; cordyline; anturium daun; pakis; aglonema; difenbacia; sansifera; lidah mertua; caladium; keladi; palem; anggrek; mawar; adenium; kamboja jepang; anturium bunga; euforbia; ixora; soka; tujuan ornamental; tanah berumput; transplantasi; pengolahan lahan; penanaman; pemeliharaan; pemanenan; pascapanen</t>
+  </si>
+  <si>
+    <t>Kegiatan pertanian atau budi daya tanaman hias daun dan tanaman hias bunga hidup, seperti bonsai, suplir, kuping gajah, helikonia, dracaena, filodendron, monstera, cordyline, anturium daun, pakis, aglonema, difenbacia, sansifera (lidah mertua), caladium (keladi), palem, dan tanaman hias bunga seperti anggrek, mawar, adenium (kamboja jepang), anturium bunga, euforbia, dan ixora (soka). Kelompok ini juga mencakup penanaman tumbuhan untuk tujuan ornamental dan tanah berumput untuk transplantasi. Mencakup pengolahan lahan, penanaman, pemeliharaan, pemanenan, dan pascapanen sebagai satu rangkaian kegiatan.</t>
+  </si>
+  <si>
+    <t>penangkaran; tumbuhan liar; pembiakan vegetatif; batang stek; potongan; bibit; pengembangbiakan tanaman</t>
+  </si>
+  <si>
+    <t>Kegiatan penangkaran tumbuhan liar, termasuk pembiakan secara vegetatif melalui batang stek, potongan, dan bibit untuk kelangsungan pengembangbiakan tanaman.</t>
+  </si>
+  <si>
+    <t>pembiakan; benih; batang stek; potongan; bibit; perbanyakan; okulasi; tanam kembali; umbi-umbian; akar-akaran; pemotongan; cangkokan; spawn jamur; kebun bibit; penyemaian cabai</t>
+  </si>
+  <si>
+    <t>Produksi semua benih tanaman selain yang tercakup pada kelompok 01301 dan 01302 secara vegetatif, termasuk batang stek, potongan, dan bibit untuk perbanyakan tanaman atau pembuatan batang okulasi. Juga mencakup penanaman tumbuhan untuk ditanam kembali, umbi-umbian, akar-akaran, pemotongan, stek, cangkokan, spawn jamur, dan kebun bibit (kecuali kebun bibit hutan). Kegiatan penyemaian cabai termasuk dalam kelompok ini.</t>
+  </si>
+  <si>
+    <t>budi daya sapi; sapi potong; penggemukan sapi; sapi siap potong; pembibitan sapi; bibit sapi; semen sapi; embrio sapi; ternak sapi potong</t>
+  </si>
+  <si>
+    <t>Kegiatan budi daya sapi potong berupa penggemukan untuk menghasilkan sapi siap potong dan kegiatan pembibitan untuk menghasilkan ternak bibit sapi potong, semen, dan embrio.</t>
+  </si>
+  <si>
+    <t>budi daya sapi; sapi perah; penggemukan sapi perah; produksi susu; produksi susu sapi; pembibitan sapi perah; bibit sapi perah; semen sapi; embrio sapi; ternak sapi perah</t>
+  </si>
+  <si>
+    <t>Kegiatan budi daya sapi perah berupa penggemukan, produksi susu, dan kegiatan pembibitan untuk menghasilkan bibit ternak sapi perah, semen, dan embrio.</t>
+  </si>
+  <si>
+    <t>budi daya kerbau; kerbau potong; penggemukan kerbau; kerbau siap potong; pembibitan kerbau; bibit kerbau; semen kerbau; embrio kerbau; ternak kerbau potong</t>
+  </si>
+  <si>
+    <t>Kegiatan budi daya kerbau potong berupa penggemukan untuk menghasilkan kerbau siap potong dan pembibitan untuk menghasilkan bibit ternak kerbau potong, semen, dan embrio.</t>
+  </si>
+  <si>
+    <t>budi daya kerbau; kerbau perah; penggemukan kerbau perah; produksi susu kerbau; pembibitan kerbau perah; bibit kerbau; semen kerbau; embrio kerbau; ternak kerbau perah</t>
+  </si>
+  <si>
+    <t>Kegiatan budi daya kerbau perah berupa penggemukan dan produksi susu, serta kegiatan pembibitan untuk menghasilkan bibit ternak kerbau perah, semen, dan embrio.</t>
+  </si>
+  <si>
+    <t>kuda; kuda potong; kuda perah; kuda pacu; kuda tunggang; kuda tarik; kuda kavaleri; kuda polo; kuda kesayangan; bagal; hinni; budi daya kuda; pembibitan kuda; bibit kuda; semen kuda; embrio kuda; susu kuda</t>
+  </si>
+  <si>
+    <t>Kegiatan budi daya kuda yang menghasilkan kuda, seperti kuda potong, kuda perah, kuda pacu, kuda tunggang, kuda tarik, kuda kavaleri, kuda polo, dan kuda kesayangan, bagal, hinni, dan sejenisnya; serta kegiatan pembibitan untuk menghasilkan bibit, semen, dan embrio. Kelompok ini juga mencakup produksi susu kuda dan sejenisnya. Tidak mencakup pengelolaan kandang kuda untuk balap dan berkuda untuk olahraga.</t>
+  </si>
+  <si>
+    <t>unta; unta potong; unta perah; llama; alpaka; vicunas; guanacos; budi daya unta; pembibitan unta; bibit unta; semen unta; embrio unta; susu unta</t>
+  </si>
+  <si>
+    <t>Kegiatan budi daya untuk menghasilkan unta potong, unta perah, dan hewan sejenisnya seperti llama, alpaka, vicunas, dan guanacos, serta kegiatan pembibitan untuk menghasilkan bibit, semen, dan embrio. Kelompok ini juga mencakup produksi susu dari unta dan hewan sejenisnya.</t>
+  </si>
+  <si>
+    <t>budi daya domba; domba potong; penggemukan domba; domba siap potong; pembibitan domba; bibit domba; semen domba; embrio domba; ternak domba</t>
+  </si>
+  <si>
+    <t>Kegiatan budi daya domba potong berupa penggemukan untuk menghasilkan domba siap potong dan kegiatan pembibitan untuk menghasilkan bibit ternak domba potong, semen, dan embrio.</t>
+  </si>
+  <si>
+    <t>budi daya kambing; kambing potong; penggemukan kambing; kambing siap potong; pembibitan kambing; bibit kambing; semen kambing; embrio kambing; ternak kambing</t>
+  </si>
+  <si>
+    <t>Kegiatan budi daya berupa penggemukan untuk menghasilkan kambing potong dan kegiatan pembibitan untuk menghasilkan bibit ternak kambing potong, semen, dan embrio.</t>
+  </si>
+  <si>
+    <t>budi daya kambing; kambing perah; susu kambing; pembibitan kambing perah; bibit kambing; semen kambing; embrio kambing; ternak kambing perah</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kegiatan budi daya untuk menghasilkan susu dan kegiatan pembibitan untuk menghasilkan bibit ternak kambing perah, semen, dan embrio. 
+</t>
+  </si>
+  <si>
+    <t>budi daya domba; domba perah; susu domba; pembibitan domba perah; bibit domba; semen domba; embrio domba; ternak domba perah</t>
+  </si>
+  <si>
+    <t>Kegiatan budi daya domba perah untuk menghasilkan susu dan kegiatan pembibitan untuk menghasilkan bibit ternak domba perah, semen, dan embrio.</t>
+  </si>
+  <si>
+    <t>bulu domba; wol; raw wool; wol mentah; produksi wol; peternakan domba; domba penghasil wol</t>
+  </si>
+  <si>
+    <t>Kegiatan peternakan yang melakukan produksi bulu domba (wol) mentah.</t>
+  </si>
+  <si>
+    <t>babi; budi daya babi; penggemukan babi; babi siap potong; pembibitan babi; bibit babi; semen babi; embrio babi; ternak babi</t>
+  </si>
+  <si>
+    <t>Kegiatan budi daya babi berupa penggemukan untuk menghasilkan babi siap potong dan kegiatan pembibitan babi untuk menghasilkan bibit ternak babi, semen, dan embrio.</t>
+  </si>
+  <si>
+    <t>budi daya ayam; ayam ras; ayam pedaging; broiler; ayam potong; peternakan ayam ras</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kegiatan budi daya ayam ras untuk menghasilkan ayam pedaging. 
+</t>
+  </si>
+  <si>
+    <t>budi daya ayam; ayam ras; ayam petelur; telur konsumsi; peternakan ayam ras petelur; produksi telur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kegiatan budi daya ayam ras untuk menghasilkan telur konsumsi dan lainnya. 
+</t>
+  </si>
+  <si>
+    <t>pembibitan ayam; ayam lokal; persilangan ayam; bibit ayam; telur tetas; ayam lokal petelur; ayam lokal pedaging; breeding ayam</t>
+  </si>
+  <si>
+    <t>Kegiatan pembibitan ayam lokal dan persilangannya untuk menghasilkan bibit dan telur tetas ayam lokal petelur, pedaging, dan persilangannya.</t>
+  </si>
+  <si>
+    <t>budi daya ayam; ayam lokal; persilangan ayam; ayam dara; pullet; ayam lokal pedaging; ayam siap potong; telur konsumsi; ternak ayam lokal</t>
+  </si>
+  <si>
+    <t>Kegiatan budi daya ayam lokal dan persilangannya untuk menghasilkan ayam dara/pullet, ayam lokal pedaging siap potong, dan telur konsumsi.</t>
+  </si>
+  <si>
+    <t>itik; bebek; budi daya itik; budi daya bebek; itik pedaging; bebek pedaging; itik petelur; bebek petelur; telur konsumsi; telur tetas; pembibitan itik; pembibitan bebek; bibit itik; bibit bebek; ternak itik; ternak bebek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kegiatan budi daya itik dan bebek untuk menghasilkan itik dan bebek pedaging, itik dan bebek petelur, telur konsumsi dan lainnya, serta kegiatan pembibitan untuk menghasilkan telur tetas serta bibit itik dan bebek. 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">burung puyuh; puyuh; budi daya puyuh; puyuh potong; puyuh petelur; telur puyuh; telur konsumsi; pembibitan puyuh; bibit puyuh; telur tetas puyuh; ternak puyuh 
+</t>
+  </si>
+  <si>
+    <t>Kegiatan budi daya burung puyuh untuk menghasilkan burung puyuh potong, burung puyuh petelur, dan telur konsumsi, serta kegiatan pembibitan untuk menghasilkan bibit ternak burung puyuh dan telur tetas.</t>
+  </si>
+  <si>
+    <t>burung merpati; merpati; budi daya merpati; merpati potong; pembibitan merpati; bibit merpati; telur tetas merpati; ternak merpati</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kegiatan budi daya burung merpati untuk menghasilkan burung merpati potong atau lainnya, dan kegiatan pembibitan untuk menghasilkan bibit ternak burung merpati dan telur tetas. 
+</t>
+  </si>
+  <si>
+    <t>pembibitan ayam ras; ayam ras pedaging; ayam ras petelur; telur tetas; ayam bibit; kuri; breeding ayam ras</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kegiatan pembibitan ayam ras pedaging dan ayam ras petelur yang menghasilkan telur tetas, ayam bibit (kuri), dan hasil lainnya. 
+</t>
+  </si>
+  <si>
+    <t>budi daya unggas; unggas lainnya; kalkun; angsa; ayam mutiara; unggas pedaging; unggas petelur; telur konsumsi; pembibitan unggas; bibit unggas; telur tetas</t>
+  </si>
+  <si>
+    <t>Kegiatan budi daya unggas lainnya, seperti kalkun, angsa, dan ayam mutiara untuk menghasilkan unggas pedaging, unggas petelur, dan telur konsumsi, serta kegiatan pembibitan unggas tersebut untuk menghasilkan bibit atau telur tetas.</t>
+  </si>
+  <si>
+    <t>burung unta; budi daya burung unta; burung unta konsumsi; burung unta potong; telur burung unta; pembibitan burung unta; bibit burung unta; telur tetas burung unta; ternak burung unta</t>
+  </si>
+  <si>
+    <t>Kegiatan budi daya burung unta konsumsi untuk menghasilkan burung unta potong, telur dan lainnya, serta kegiatan pembibitan untuk menghasilkan bibit ternak burung unta atau telur tetas.</t>
+  </si>
+  <si>
+    <t>ulat sutra; budi daya ulat sutra; pembibitan ulat sutra; kokon; kepompong; sutra; peternakan ulat sutra</t>
+  </si>
+  <si>
+    <t>Kegiatan budi daya dan pembibitan ulat sutra untuk menghasilkan kokon/kepompong ulat sutra.</t>
+  </si>
+  <si>
+    <t>lebah; budi daya lebah; pembibitan lebah; madu; lilin lebah; propolis; sarang lebah; peternakan lebah; produk lebah</t>
+  </si>
+  <si>
+    <t>Kegiatan budi daya dan pembibitan lebah untuk menghasilkan produk seperti madu, lilin lebah, propolis, dan sarang lebah, serta kegiatan pembibitan lebah.</t>
+  </si>
+  <si>
+    <t>rusa; kijang; budi daya rusa; pembibitan rusa; bibit rusa; daging rusa; kulit rusa; peternakan rusa; ternak rusa</t>
+  </si>
+  <si>
+    <t>Kegiatan budi daya dan pembibitan rusa/kijang untuk menghasilkan bibit, daging, kulit, dan hasil lainnya.</t>
+  </si>
+  <si>
+    <t>kelinci; budi daya kelinci; pembibitan kelinci; daging kelinci; kulit kelinci; peternakan kelinci; ternak kelinci</t>
+  </si>
+  <si>
+    <t>Kegiatan budi daya dan pembibitan kelinci untuk menghasilkan daging, kulit, dan hasil lainnya.</t>
+  </si>
+  <si>
+    <t>cacing; budi daya cacing; pembibitan cacing; bibit cacing; daging cacing; peternakan cacing; vermikultur</t>
+  </si>
+  <si>
+    <t>Kegiatan budi daya dan pembibitan cacing untuk menghasilkan bibit dan daging, dan hasil lainnya.</t>
+  </si>
+  <si>
+    <t>burung walet; walet; budi daya walet; pembibitan walet; sarang burung walet; peternakan walet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kegiatan budi daya dan pembibitan burung walet termasuk kegiatan lainnya untuk menghasilkan burung dan sarang burung walet. Kelompok ini tidak mencakup pengolahan sarang burung walet. 
+</t>
+  </si>
+  <si>
+    <t>penangkaran satwa liar; pembesaran satwa liar; pembiakan satwa liar; mamalia; reptilia; burung; insekta; pelestarian satwa; konservasi ex-situ</t>
+  </si>
+  <si>
+    <t>Kegiatan penangkaran, pembesaran, dan pembiakan satwa liar dari jenis mamalia, reptilia (selain buaya dan aligator), burung, insekta, dan jenis lainnya untuk pelestarian. Kelompok ini tidak mencakup kegiatan penangkaran buaya dan aligator.</t>
+  </si>
+  <si>
+    <t>hewan lainnya; marmut; anjing; kucing; ulat; jangkrik; budi daya hewan; pembibitan hewan; bibit hewan; daging hewan; kulit hewan; peternakan lainnya; ternak lainnya</t>
+  </si>
+  <si>
+    <t>Kegiatan budi daya dan pembibitan hewan lainnya, seperti marmut, anjing, kucing, ulat, dan jangkrik untuk menghasilkan bibit, daging, kulit, dan hasil lainnya.</t>
+  </si>
+  <si>
+    <t>jasa pengolahan lahan; pengolahan lahan pertanian; persiapan penanaman; balas jasa; kontrak; lahan sawah; lahan bukan sawah; jasa pertanian</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kegiatan pengolahan lahan pertanian atas dasar balas jasa atau kontrak dengan tujuan untuk persiapan penanaman, baik di lahan sawah maupun bukan sawah. 
+</t>
+  </si>
+  <si>
+    <t>jasa pemupukan; pemupukan lahan pertanian; balas jasa; kontrak; jasa pertanian</t>
+  </si>
+  <si>
+    <t>Kegiatan pemupukan lahan pertanian atas dasar balas jasa atau kontrak.</t>
+  </si>
+  <si>
+    <t>jasa pemanenan; pemanenan tanaman; panen; balas jasa; kontrak; jasa pertanian</t>
+  </si>
+  <si>
+    <t>Kegiatan pemanenan tanaman atas dasar balas jasa atau kontrak.</t>
+  </si>
+  <si>
+    <t>jasa penyemprotan; jasa penyerbukan; penyemprotan udara; penyerbukan udara; pesawat udara; pesawat khusus; jasa pertanian</t>
+  </si>
+  <si>
+    <t>Kegiatan penyemprotan dan penyerbukan melalui udara dengan pesawat udara khusus berdasarkan keadaan tertentu.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">jasa pengendalian; OPT; organisme pengganggu tumbuhan; pengendalian hama; pengendalian penyakit; pengendalian gulma; balas jasa; kontrak; jasa pertanian 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kegiatan pengendalian hama, penyakit, dan gulma pada tanaman atas dasar balas jasa atau kontrak. 
+</t>
+  </si>
+  <si>
+    <t>jasa penanaman; penanaman benih; benih komoditas pertanian; balas jasa; kontrak; jasa pertanian</t>
+  </si>
+  <si>
+    <t>Kegiatan penanaman benih komoditas pertanian atas dasar balas jasa atau kontrak.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">jasa penunjang pertanian; penyelenggaraan pengairan; penyiraman; penyediaan alat pertanian; operator alat pertanian; pemeliharaan alat pertanian; perawatan alat pertanian; balas jasa; kontrak; jasa pertanian 
+</t>
+  </si>
+  <si>
+    <t>Kegiatan jasa penunjang pertanian lainnya yang belum termasuk dalam kelompok jasa penunjang pertanian di atas, seperti penyelenggaraan pengairan/penyiraman serta penyediaan alat pertanian berikut operatornya, pemeliharaan, dan perawatan alat pertanian atas dasar balas jasa atau kontrak. Kelompok ini tidak mencakup kegiatan penyewaan khusus alat pertanian tanpa operator.</t>
+  </si>
+  <si>
+    <t>jasa perkawinan ternak; inseminasi buatan; transfer embrio; pemeriksaan kebuntingan; bull master; balas jasa; kontrak; jasa peternakan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kegiatan perkawinan ternak atas dasar balas jasa atau kontrak, seperti inseminasi buatan, transfer embrio, pemeriksaan kebuntingan, dan bull master. 
+</t>
+  </si>
+  <si>
+    <t>jasa penetasan telur; penetasan telur; tetas telur; balas jasa; kontrak; jasa peternakan</t>
+  </si>
+  <si>
+    <t>Kegiatan penetasan telur atas dasar balas jasa atau kontrak.</t>
+  </si>
+  <si>
+    <t>jasa penunjang peternakan; pencukuran bulu ternak; pemasangan identitas ternak; pemberian identitas ternak; pembersihan kandang; pencari rumput; pemeliharaan hewan; perawatan hewan; penggembalaan ternak; farrier; tukang tapal kuda; pengebirian hewan; balas jasa; kontrak; jasa peternakan</t>
+  </si>
+  <si>
+    <t>Kegiatan jasa penunjang peternakan lainnya atas dasar balas jasa atau kontrak, seperti pencukuran bulu ternak, pemasangan dan pemberian identitas ternak, pembersihan kandang ternak, termasuk juga usaha pelayanan pencari rumput, pemeliharaan dan perawatan hewan, dan penggembalaan ternak. Kelompok ini juga mencakup kegiatan farrier (tukang tapal kuda) dan pengebirian hewan.</t>
+  </si>
+  <si>
+    <t>jasa pascapanen; penyiapan hasil pertanian; pasar primer; pembersihan; sortasi; pemeringkatan; pengupasan; pengeringan sinar matahari; disinfeksi; pemisahan biji kapas; penyiapan daun tembakau; penyiapan biji cokelat; pemberian lilin buah; pengeringan buah alami; pengeringan sayuran; pengeringan rempah; herba obat; sortasi herba; pemotongan herba; pembusukan serat tekstil; yute; flaks; sabut; pematangan buatan; pematangan pisang; balas jasa; kontrak</t>
+  </si>
+  <si>
+    <t>Kegiatan pascapanen atas dasar balas jasa atau kontrak yang meliputi: penyiapan hasil pertanian untuk pasar primer (pembersihan, sortasi, pemeringkatan, pengupasan, pengeringan sinar matahari, dan disinfeksi); pemisahan biji kapas; penyiapan daun tembakau; penyiapan biji cokelat; pemberian lilin pada buah; pengeringan buah, sayuran, rempah, dan herba obat secara alami; sortasi, pembersihan, dan pemotongan herba obat; pembusukan tanaman serat tekstil (yute, flaks, sabut, dll.) yang tidak terkait dengan aktivitas pertanian; serta pematangan buatan pada buah sebagai jasa (contoh: pematangan pisang). Tidak mencakup penyiapan produk oleh petani (masuk 012/013), kegiatan pascapanen untuk meningkatkan kualitas benih, pembersihan/pengeringan ulang tembakau, pemasaran oleh perdagangan komisi/koperasi (golongan 46), perdagangan besar hasil pertanian, pengolahan biji untuk minyak, atau penelitian rekayasa benih baru.</t>
+  </si>
+  <si>
+    <t>pemilihan benih; pengolahan benih; benih untuk pembiakan; peningkatan kualitas benih; eliminasi material non-benih; benih rusak; benih belum matang; pengeringan benih; pembersihan benih; pemeringkatan; sortasi benih; penyimpanan benih; benih modifikasi; jasa pemuliaan benih</t>
+  </si>
+  <si>
+    <t>Kegiatan pengolahan benih yang ditujukan untuk meningkatkan kualitas perbanyakan benih melalui pengeliminasian material selain benih, benih berukuran terlalu kecil, benih yang rusak secara mekanis atau karena serangga, dan benih yang belum matang, serta mengurangi kelembaban benih agar aman untuk disimpan. Kegiatan ini mencakup pengeringan, pembersihan, pemeringkatan, sortasi, dan lainnya sampai benih dipasarkan. Pemeliharaan benih yang telah dimodifikasi juga termasuk di sini. Kelompok ini tidak mencakup penyiapan produk oleh petani (masuk 012/013), pembersihan dan pengeringan kembali tembakau, pemasaran oleh perdagangan komisi/koperasi (golongan 46), perdagangan besar hasil pertanian dan hewan hidup, penanaman biji, pengolahan biji untuk menghasilkan minyak, atau penelitian untuk mengembangkan/memodifikasi benih dalam bentuk baru.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">perburuan; penangkapan hewan; perangkap; komersial; satwa liar; bulu; kulit reptil; kulit burung; katak; kodok; siput; mamalia laut; duyung; singa laut; anjing laut; rubah; cerpelai; serigala; pengendalian populasi; tanduk mamalia; organ reptil 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kegiatan perburuan dan penangkapan hewan dengan perangkap untuk tujuan komersial; penangkapan satwa liar (mati/hidup) sebagai makanan, untuk diambil bulu/kulitnya, untuk pengendalian populasi, untuk penelitian, kebun binatang, atau hewan kesayangan; produksi kulit bulu, kulit reptil, atau kulit burung dari hasil perburuan/penangkapan; penangkapan katak, kodok, dan siput di alam liar; penangkapan mamalia laut (duyung, singa laut, anjing laut) di daratan; perburuan rubah, cerpelai, dan serigala untuk melindungi ternak; perburuan untuk pengendalian populasi; serta produksi tanduk mamalia dan organ reptil/hewan lainnya dari kegiatan perburuan/penangkapan. Tidak mencakup produksi kulit dari peternakan, pembesaran binatang buruan, pengendalian hama di pertanian, penangkapan paus, produksi kulit dari rumah potong, perburuan untuk olahraga/rekreasi, dan kegiatan organisasi pendukung perburuan/penangkapan. 
+</t>
+  </si>
+  <si>
+    <t>pengelolaan hutan; penanaman; penanaman kembali; reboisasi; konservasi hutan; konservasi lahan kayu; sekuestrasi karbon; penyerapan karbon; penyimpanan karbon; kredit karbon; sertifikat pengurangan emisi; hutan alam; hutan semialami; hutan tanaman; kehutanan</t>
+  </si>
+  <si>
+    <t>Kegiatan pengelolaan hutan, yang meliputi penanaman, penanaman kembali, serta konservasi hutan dan lahan kayu. Kelompok ini juga mencakup kegiatan pengelolaan hutan yang bertujuan untuk penyerapan dan penyimpanan karbon (sekuestrasi karbon) secara alami yang dilakukan di hutan alam, hutan semialami, atau hutan tanaman, serta penjualan kredit karbon atau sertifikat pengurangan emisi sebagai hasil dari kegiatan pengelolaan hutan. Tidak mencakup inventarisasi/pencatatan sekuestrasi karbon oleh pihak ketiga (masuk kategori N).</t>
+  </si>
+  <si>
+    <t>pemanfaatan kayu; kayu hutan; pengelolaan kayu; penanaman; penebangan; kayu bulat; hutan alam; hutan semialami; hutan tanaman; kehutanan</t>
+  </si>
+  <si>
+    <t>Kegiatan pengelolaan kayu di dalam hutan, mulai dari penanaman sampai penebangan dengan hasil produksi berupa kayu bulat. Kegiatan ini dapat dilakukan di dalam hutan alam, hutan semialami, maupun hutan tanaman.</t>
+  </si>
+  <si>
+    <t>pembenihan; pembenihan pohon hutan; pohon hutan; pembibitan kehutanan; bibit pohon hutan; persemaian; kehutanan</t>
+  </si>
+  <si>
+    <t>Kelompok ini mencakup kegiatan pembenihan pohon hutan yang dibesarkan sampai dengan umur tertentu, meliputi kegiatan pengolahan lahan, penyemaian, penanaman, pemeliharaan, pemanenan, dan pascapanen dalam rangka menghasilkan bibit/benih pohon hutan.</t>
+  </si>
+  <si>
+    <t>pemanenan kayu; produksi kayu bulat; penebangan hutan; pit-props; tonggak pagar; tiang listrik; tiang telepon; kayu bulat; kehutanan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kegiatan produksi kayu bulat dari penebangan hutan, baik digunakan dalam industri berbasis produk hutan maupun digunakan dalam bentuk yang tidak diolah, seperti pit-props, tonggak pagar, dan tiang listrik atau telepon. 
+</t>
+  </si>
+  <si>
+    <t>pemungutan kayu; residu hutan; semak belukar; tunggul pohon; serpih kayu; limbah kehutanan; kayu energi; arang tradisional; kehutanan</t>
+  </si>
+  <si>
+    <t>Kegiatan pemungutan kayu hutan dan residu yang dihasilkan dari kegiatan penebangan pohon hutan, misalnya semak belukar, tunggul pohon, serpih kayu, dan limbah kehutanan lainnya untuk energi. Kelompok ini juga mencakup kegiatan produksi arang secara tradisional yang terasosiasi dengan kegiatan kehutanan.</t>
+  </si>
+  <si>
+    <t>hasil hutan bukan kayu; pemungutan liar; jamur; truffles; beri-berian; kacang-kacangan; balata; getah; gabus; lak; damar; resin; balsam; biji pohon ek; kastanya; chestnut; lumut; lumut kerak; sayur rambut; eelgrass; getah karet; getah perca; jelutung; kemenyan; rotan; getah pinus; jernang; kopal; selak; bambu liar; kokon; kepompong ulat sutra; madu; sarang walet; gaharu; cendana; lawang; kayu manis; pandan; kayu putih; rempah liar; pengeringan alami</t>
+  </si>
+  <si>
+    <t>Kegiatan pemungutan hasil hutan bukan kayu yang tumbuh secara liar, misalnya jamur, truffles, beri-berian, kacang-kacangan, balata dan getah lainnya, gabus, lak dan damar/resin, balsam, biji pohon ek, kastanya/horse chestnuts, lumut, dan lumut kerak, serta sayur rambut/eelgrass. Juga mencakup pemungutan getah karet, getah perca, jelutung, kemenyan, rotan, getah pinus, jernang, kopal, selak, bambu liar, kokon/kepompong ulat sutra, damar, madu, sarang burung walet, gaharu, cendana, lawang, kayu manis, pandan, kayu putih, serta pengumpulan rempah liar dan pengeringannya secara alami. Tidak mencakup pertanian produk-produk tersebut (kecuali penanaman pohon gabus, masuk 01), pertanian jamur dan truffles, pertanian buah beri dan aneka kacang, serta pengumpulan kayu bakar.</t>
+  </si>
+  <si>
+    <t>jasa lingkungan hutan; pemanfaatan jasa lingkungan; kondisi lingkungan hutan; potensi ekosistem; fungsi konservasi; fungsi lindung; jasa air hutan; jasa udara hutan; keadaan iklim; fenomena alam; kekhasan jenis; keunikan spesies; hutan alam; hutan semialami; hutan tanaman</t>
+  </si>
+  <si>
+    <t>Kegiatan pemanfaatan jasa/kondisi lingkungan di dalam hutan, mulai dari pemanfaatan kondisi lingkungan berupa pemanfaatan potensi ekosistem (seperti fungsi konservasi dan lindung), pemanfaatan jasa lingkungan hutan (air, udara), keadaan iklim, fenomena alam, kekhasan jenis, dan keunikan spesies. Kegiatan ini dapat dilakukan di dalam hutan alam, hutan semialami, maupun hutan tanaman.</t>
+  </si>
+  <si>
+    <t>jasa penggunaan kawasan hutan; pemanfaatan kawasan hutan; izin penggunaan kawasan hutan; fungsi hutan; peruntukan kawasan hutan; jasa kehutanan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jasa kehutanan bidang penggunaan kawasan hutan tanpa mengubah fungsi dan peruntukan kawasan hutan. 
+</t>
+  </si>
+  <si>
+    <t>jasa kehutanan; inventarisasi hutan; konsultasi manajemen kehutanan; pengevaluasian kayu; pencegahan kebakaran hutan; pengendalian hama hutan; penyewaan perlengkapan kehutanan; penyewaan peralatan kehutanan; operator kehutanan; jasa pemanenan kayu; pengangkutan kayu; kayu dalam hutan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kegiatan jasa kehutanan, seperti inventarisasi hutan, jasa konsultasi manajemen kehutanan, pengevaluasian kayu, pencegahan kebakaran hutan, pengendalian hama hutan, serta penyewaan perlengkapan dan peralatan kehutanan yang disertai dengan operator. Juga mencakup kegiatan jasa pemanenan kayu, seperti pengangkutan kayu di dalam hutan yang terasosiasi dengan kegiatan pemanenan kayu. Tidak mencakup pembenihan tanaman hutan, pengeringan lahan kehutanan, pembersihan lokasi pembangunan, pengelolaan air di kawasan hutan, pengusahaan tenaga panas bumi, kegiatan penangkapan dan penyimpanan karbon, aktivitas taman botani/kebun binatang/cagar alam, serta aktivitas pembangkitan tenaga listrik tenaga surya dan angin di hutan. 
+</t>
+  </si>
+  <si>
+    <t>penangkapan ikan laut; perikanan laut; komersial; samudra; pesisir; ikan bersirip; tuna; cakalang; hiu; pari; krustasea; udang; rajungan; kepiting; moluska; kerang; tiram; cumi-cumi; gurita; siput; coelenterata; ubur-ubur; ekinodermata; teripang; bulu babi; amfibi; kodok; reptilia; buaya; penyu; kura-kura; biawak; ular air; alga; rumput laut; biota air; CITES; paus; dugong; lumba-lumba; ikan napoleon; kuda laut; buaya air asin; karang keras; karang lunak; capungan banggai; mutiara alam; terumbu karang; bunga karang</t>
+  </si>
+  <si>
+    <t>Penangkapan ikan untuk tujuan komersial di samudra dan pesisir, meliputi ikan bersirip (tuna, cakalang, hiu pari), krustasea (udang, rajungan, kepiting), moluska (kerang, tiram, cumi-cumi, gurita, siput), coelenterata (ubur-ubur), ekinodermata (teripang, bulu babi), amfibi (kodok), reptilia (buaya, penyu, kura-kura, biawak, ular air), alga (rumput laut), dan biota air lainnya. Juga mencakup penangkapan biota laut yang dilindungi/dibatasi (CITES), seperti paus, dugong, penyu, lumba-lumba, ikan napoleon, kuda laut, buaya air asin, karang keras/lunak, capungan banggai, serta hiu dan pari. Termasuk pengumpulan biota laut/material laut lainnya seperti mutiara alam, terumbu karang, bunga karang, rumput laut, dan alga. Tidak mencakup penangkapan mamalia laut di darat, pengolahan ikan paus di kapal pabrik, pengolahan ikan di pabrik (kapal/darat), penyewaan kapal pesiar berawak untuk angkutan, jasa patroli perikanan, aktivitas memancing olahraga/rekreasi, dan pengoperasian fasilitas pemancingan olahraga.</t>
+  </si>
+  <si>
+    <t>penangkapan ikan air tawar; perairan air tawar; komersial; krustasea air tawar; udang air tawar; kepiting air tawar; moluska air tawar; kerang; cumi-cumi; amfibi; kodok; reptilia; buaya air tawar; penyu; kura-kura; biawak; ular air; tumbuhan air; biota air tawar; CITES; arwana super red; arwana jardinii; sidat; hiu; pari; pengambilan biota air tawar; pengumpulan material air tawar</t>
+  </si>
+  <si>
+    <t>Penangkapan ikan untuk tujuan komersial di perairan air tawar yang ada di darat; pengambilan krustasea (udang, kepiting), moluska (kerang, cumi-cumi), amfibi (kodok), reptilia (buaya, penyu, kura-kura, biawak, ular air), tumbuhan air, dan biota air tawar lainnya. Juga mencakup penangkapan biota air tawar yang dilindungi/dibatasi (CITES), seperti arwana super red, arwana jardinii, buaya air tawar, sidat, serta hiu dan pari; pengambilan binatang/biota air tawar; dan pengumpulan material air tawar.</t>
+  </si>
+  <si>
+    <t>pembudidayaan ikan air tawar; ikan bersirip; biota air tawar; tidak dilindungi; pendederan; pembesaran; pembiakan; pembenihan; pemanenan; ikan mas; nila; patin; gurami; gabus; toman; mujair; tawes; lele; katak; danau; waduk; sungai; perairan umum air tawar; fasilitas buatan; media air tawar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kegiatan pendederan, pemeliharaan, pembesaran, pembiakan atau pembenihan, serta pemanenan ikan bersirip dan biota air tawar lainnya yang tidak dilindungi sampai umur, bentuk, dan ukuran tertentu untuk dikonsumsi atau sebagai input untuk kegiatan budi daya pembesaran. Jenis biota air tawar yang dibudidayakan, contohnya ikan mas, nila, patin, gurami, gabus, toman, mujair, tawes, lele, dan katak. Kegiatan budi daya dapat dilakukan di perairan umum air tawar di darat, seperti danau, waduk, sungai, genangan air lainnya, dan fasilitas buatan yang menggunakan air tawar sebagai media budi daya. 
+</t>
+  </si>
+  <si>
+    <t>pembudidayaan; ikan hias air laut; tidak dilindungi; kuda laut; ikan badut; clownfish; angel piyama; blue devil; pendederan; pembesaran; pembiakan; pembenihan; pemanenan; muara sungai; laguna; fasilitas buatan; media air laut</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kegiatan pendederan, pemeliharaan, pembesaran, pembiakan atau pembenihan, serta pemanenan ikan hias air laut yang tidak dilindungi, seperti kuda laut, ikan badut/clownfish, angel piyama, dan blue devil. Kegiatan ini dapat dilakukan di laut, muara sungai, laguna, fasilitas buatan, atau tempat lain yang menggunakan air laut sebagai media budi daya. 
+</t>
+  </si>
+  <si>
+    <t>pembudidayaan; tumbuhan air tawar; tidak dilindungi; tanaman hias air tawar; mikroalga; Anubias; java moss; java fern; pembenihan; pemeliharaan; pembesaran; pemanenan; sekuestrasi karbon; penyerapan karbon; penyimpanan karbon; kredit karbon; sertifikat pengurangan emisi; media air tawar</t>
+  </si>
+  <si>
+    <t>Kegiatan pemeliharaan, pembesaran, dan pemanenan tumbuhan air tawar yang tidak dilindungi, termasuk tanaman hias dan mikroalga, seperti Anubias spp., java moss, dan java fern, termasuk pembenihan tumbuhan air tawar. Kelompok ini juga mencakup kegiatan pembudidayaan tumbuhan air tawar yang bertujuan untuk penyerapan dan penyimpanan karbon secara alami, serta penjualan kredit karbon atau sertifikat pengurangan emisi sebagai hasil dari kegiatan budi daya. Kegiatan ini dapat dilakukan di lahan, perairan, dan fasilitas buatan lainnya yang menggunakan air tawar sebagai media budi daya.</t>
+  </si>
+  <si>
+    <t>pengembangbiakan; ikan dilindungi; biota air tawar dilindungi; CITES; ketentuan perundangan; pari air tawar; belida; badar goa; wader goa; selusur maninjau; arwana super red; arwana jardinii; zebra pleco; pari motoro; konservasi ex-situ</t>
+  </si>
+  <si>
+    <t>Kegiatan pengembangbiakan ikan dan biota air tawar yang dilindungi dalam apendiks Convention on International Trade in Endangered Species of Wild Fauna and Flora (CITES) dan/atau berdasarkan ketentuan perundangan yang berlaku, seperti pari air tawar, belida, badar goa (wader goa), selusur maninjau, arwana super red, arwana jardinii, zebra pleco, dan pari motoro.</t>
+  </si>
+  <si>
+    <t>pembudidayaan air payau; ikan bersirip; biota air payau; tidak dilindungi; pendederan; pembesaran; pembiakan; pembenihan; pemanenan; ikan bandeng; patin; nila salin; kakap; kepiting; udang windu; udang vaname; media air payau</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kegiatan pendederan, pembesaran, pembiakan atau pembenihan, dan pemanenan ikan bersirip dan biota air payau lainnya yang tidak dilindungi sampai umur, bentuk, dan ukuran tertentu untuk dikonsumsi atau sebagai input untuk kegiatan budi daya pembesaran. Jenis biota air payau yang dibudidayakan contohnya ikan bandeng, patin, nila salin, kakap, kepiting, udang windu, dan udang vaname. Kegiatan ini dapat dilakukan di lahan, perairan, dan fasilitas buatan lainnya yang menggunakan air payau sebagai media budi daya. 
+</t>
+  </si>
+  <si>
+    <t>pembudidayaan; ikan hias air payau; tidak dilindungi; pendederan; pemeliharaan; pembesaran; pembiakan; pembenihan; pemanenan; media air payau</t>
+  </si>
+  <si>
+    <t>Kegiatan pendederan, pemeliharaan, pembesaran, pembiakan atau pembenihan, dan pemanenan ikan hias air payau yang tidak dilindungi. Kegiatan ini dapat dilakukan di lahan, perairan, dan fasilitas buatan lainnya yang menggunakan air payau sebagai media budi daya.</t>
+  </si>
+  <si>
+    <t>pembudidayaan; tumbuhan air payau; tidak dilindungi; pembesaran; rumput laut; Gracilaria; pembenihan; sekuestrasi karbon; penyerapan karbon; penyimpanan karbon; kredit karbon; sertifikat pengurangan emisi; media air payau</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kegiatan pembesaran tumbuhan air payau yang tidak dilindungi, seperti rumput laut/Gracilaria spp, termasuk pembenihan tumbuhan air payau. Kelompok ini juga mencakup kegiatan pembudidayaan tumbuhan air payau yang bertujuan untuk penyerapan dan penyimpanan karbon secara alami, serta penjualan kredit karbon atau sertifikat pengurangan emisi sebagai hasil dari kegiatan budi daya. Kegiatan ini dapat dilakukan di lahan, perairan, dan fasilitas buatan lainnya yang menggunakan air payau sebagai media budi daya. 
+</t>
+  </si>
+  <si>
+    <t>Kegiatan pendederan, pembesaran, pembiakan atau pembenihan, dan pemanenan ikan bersirip dan biota air payau lainnya yang tidak dilindungi sampai umur, bentuk, dan ukuran tertentu untuk dikonsumsi atau sebagai input untuk kegiatan budi daya pembesaran. Jenis biota air payau yang dibudidayakan contohnya ikan bandeng, patin, nila salin, kakap, kepiting, udang windu, dan udang vaname. Kegiatan ini dapat dilakukan di lahan, perairan, dan fasilitas buatan lainnya yang menggunakan air payau sebagai media budi daya.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kegiatan pendederan, pemeliharaan, pembesaran, pembiakan atau pembenihan, dan pemanenan ikan hias air payau yang tidak dilindungi. Kegiatan ini dapat dilakukan di lahan, perairan, dan fasilitas buatan lainnya yang menggunakan air payau sebagai media budi daya. 
+</t>
+  </si>
+  <si>
+    <t>Kegiatan pembesaran tumbuhan air payau yang tidak dilindungi, seperti rumput laut/Gracilaria spp, termasuk pembenihan tumbuhan air payau. Kelompok ini juga mencakup kegiatan pembudidayaan tumbuhan air payau yang bertujuan untuk penyerapan dan penyimpanan karbon secara alami, serta penjualan kredit karbon atau sertifikat pengurangan emisi sebagai hasil dari kegiatan budi daya. Kegiatan ini dapat dilakukan di lahan, perairan, dan fasilitas buatan lainnya yang menggunakan air payau sebagai media budi daya.</t>
+  </si>
+  <si>
+    <t>pengembangbiakan; biota air payau dilindungi; ikan dilindungi; CITES; ketentuan perundangan; buaya muara; pesut mahakam; dugong; konservasi ex-situ</t>
+  </si>
+  <si>
+    <t>Kegiatan pengembangbiakan ikan dan biota air payau yang dilindungi dalam apendiks Convention on International Trade in Endangered Species of Wild Fauna and Flora (CITES) dan/atau berdasarkan ketentuan perundangan yang berlaku, seperti buaya muara, pesut mahakam, dan dugong.</t>
+  </si>
+  <si>
+    <t>jasa penunjang; penangkapan ikan; pembudidayaan ikan; jasa pemberian pakan; jasa pemanenan; jasa persiapan lelang; jasa sortasi; jasa gradasi; jasa uji mutu; penanganan ikan; pengawetan ikan; pendinginan ikan; perlindungan ikan; predator; pengendalian ikan; pengawasan ikan; fisheries control; fish guard; restorasi ekosistem maritim</t>
+  </si>
+  <si>
+    <t>Jasa penunjang insidental pada kegiatan penangkapan dan pembudidayaan ikan, baik di laut maupun di perairan air tawar, seperti jasa pemberian pakan, jasa pemanenan, jasa persiapan lelang, jasa sortasi dan gradasi, serta jasa uji mutu. Mencakup kegiatan penanganan dan pengawetan ikan hasil penangkapan atau pembudidayaan sebelum dijual, seperti jasa pendinginan ikan untuk mempertahankan kesegarannya; perlindungan ikan dari predator; pengendalian dan pengawasan ikan (fisheries control/fish guard); serta kegiatan restorasi ekosistem maritim. Tidak mencakup pengolahan ikan di kapal pabrik atau pabrik di daratan, distribusi hasil perikanan (masuk golongan 46, 47, 52), kegiatan perikanan untuk olahraga/rekreasi, dan pengoperasian fasilitas pemancingan olahraga.</t>
+  </si>
+  <si>
+    <t>Kegiatan pengolahan lahan, penanaman, pemeliharaan, dan juga pemanenan dan pasca panen jika menjadi satu kesatuan kegiatan tanaman jagung. Termasuk kegiatan pembibitan dan pembenihan tanaman jagung.membudidayakan tanaman jagung; luas kurang dari 25 Ha.</t>
+  </si>
+  <si>
+    <t>Kelompok ini mencakup kegiatan pertanian tanaman tembakau, termasuk di dalamnya kegiatan pengolahan lahan, penyemaian, penanaman, pemeliharaan, pemanenan, dan kegiatan pascapanen yang dilakukan sebagai satu rangkaian kegiatan. Kelompok ini juga mencakup kegiatan pembersihan dan perajangan tembakau yang tidak dapat dipisahkan dari kegiatan pertaniannya. Kelompok ini juga mencakup kegiatan penanaman tanaman tembakau untuk menghasilkan benih berupa biji. Kelompok ini tidak mencakup kegiatan pembuatan produk tembakau.</t>
+  </si>
+  <si>
+    <t>Kelompok ini mencakup pertanian tanaman berserat, seperti kapas, yute, kenaf, batang lenan, rami, sisal, abaka, dan bahan baku tekstil lainnya dari genus Agave. Pertanian tanaman berserat yang dimaksud mencakup kegiatan pengolahan lahan, penanaman, pemeliharaan, pemanenan, dan kegiatan pascapanen yang dilakukan sebagai satu rangkaian kegiatan. Kelompok ini juga mencakup kegiatan penanaman tanaman berserat untuk menghasilkan benih berupa biji.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kelompok ini mencakup kegiatan pertanian tanaman pakan ternak untuk memproduksi hijauan pakan ternak yang meliputi rumput pakan ternak dan tanaman legum/kacang-kacangan, seperti rumput gajah, rumput raja, rumput odot, rumput setaria, alfalfa, lamtoro, dan Indigoferea zollingeriana. Kegiatan pertanian tanaman pakan ternak yang dimaksud mencakup kegiatan pengolahan lahan, penanaman, pemeliharaan, pemanenan, dan kegiatan pascapanen yang dilakukan sebagai satu rangkaian kegiatan. 
+</t>
+  </si>
+  <si>
+    <t>Kegiatan pembenihan tanaman pakan ternak dan bit (bukan bit gula) untuk menghasilkan benih biji, mencakup pengolahan lahan, penanaman, pemeliharaan, pemanenan, dan pascapanen sebagai satu kesatuan. Tanaman meliputi rumput pakan ternak dan legum/kacang-kacangan (rumput gajah, raja, odot, setaria, alfalfa, kaliandra, gamal, lamtoro, Indigofera zollingeriana).</t>
+  </si>
+  <si>
+    <t>Kegiatan pertanian tanaman bunga yang memproduksi bunga potong dan kuncup bunga, seperti anggrek, anyelir, gerbera/hebras, gladiol, krisan, mawar, melati, dan sedap malam. Mencakup pengolahan lahan, penanaman, pemeliharaan, pemanenan, dan pascapanen sebagai satu kesatuan. Tidak mencakup pertanian tanaman bunga hidup (tanaman hias pot).</t>
+  </si>
+  <si>
+    <t>Kegiatan pertanian pembenihan tanaman bunga untuk menghasilkan benih berupa biji. Produksi semua jenis bahan tanam vegetatif (seperti batang stek, tunas, dan bibit untuk perbanyakan tanaman bunga) tidak masuk dalam kelompok ini, melainkan masuk ke subgolongan 0130.</t>
+  </si>
+  <si>
+    <t>Kegiatan pertanian tanaman semusim lainnya yang belum terklasifikasi di tempat lain, serta kegiatan penanaman untuk menghasilkan benih berupa biji. Mencakup pengolahan lahan, penanaman, pemeliharaan, pemanenan, dan pascapanen sebagai satu kesatuan.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -7712,13 +8452,6 @@
     <font>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="10"/>
-      <color rgb="FF0000FF"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -7809,7 +8542,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -7834,20 +8567,8 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -7858,10 +8579,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -7879,6 +8597,28 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -8189,15 +8929,15 @@
   <cols>
     <col min="3" max="3" width="28.42578125" customWidth="1"/>
     <col min="4" max="4" width="28.85546875" style="2" customWidth="1"/>
-    <col min="5" max="5" width="30.140625" style="15" customWidth="1"/>
+    <col min="5" max="5" width="30.140625" style="11" customWidth="1"/>
     <col min="6" max="6" width="17.42578125" customWidth="1"/>
-    <col min="8" max="8" width="33.85546875" style="3" customWidth="1"/>
+    <col min="8" max="8" width="39.5703125" style="3" customWidth="1"/>
     <col min="9" max="9" width="37.28515625" customWidth="1"/>
     <col min="10" max="10" width="32.140625" customWidth="1"/>
     <col min="11" max="11" width="50.140625" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -8232,7 +8972,7 @@
         <v>1633</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" ht="84" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>1634</v>
       </c>
@@ -8243,16 +8983,16 @@
         <v>155</v>
       </c>
       <c r="D2" s="7" t="s">
+        <v>2390</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>2391</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>2392</v>
       </c>
       <c r="F2" s="8" t="s">
         <v>1586</v>
       </c>
-      <c r="H2" s="3" t="s">
-        <v>2390</v>
+      <c r="H2" s="15" t="s">
+        <v>2769</v>
       </c>
       <c r="I2" t="e">
         <v>#N/A</v>
@@ -8264,7 +9004,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" ht="165.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>1634</v>
       </c>
@@ -8274,16 +9014,16 @@
       <c r="C3" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="D3" s="19" t="s">
-        <v>2394</v>
-      </c>
-      <c r="E3" s="20" t="s">
+      <c r="D3" s="14" t="s">
         <v>2393</v>
+      </c>
+      <c r="E3" s="15" t="s">
+        <v>2392</v>
       </c>
       <c r="F3" s="8" t="s">
         <v>2279</v>
       </c>
-      <c r="H3" s="18" t="s">
+      <c r="H3" s="13" t="s">
         <v>2371</v>
       </c>
       <c r="I3" t="e">
@@ -8296,7 +9036,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" ht="128.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>1634</v>
       </c>
@@ -8307,10 +9047,10 @@
         <v>157</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>2395</v>
+        <v>2548</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>2396</v>
+        <v>2394</v>
       </c>
       <c r="F4" s="8" t="s">
         <v>1586</v>
@@ -8318,7 +9058,7 @@
       <c r="G4" t="e">
         <v>#N/A</v>
       </c>
-      <c r="H4" s="18" t="s">
+      <c r="H4" s="13" t="s">
         <v>2372</v>
       </c>
       <c r="I4" t="e">
@@ -8331,7 +9071,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" ht="115.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>1634</v>
       </c>
@@ -8341,19 +9081,19 @@
       <c r="C5" s="6" t="s">
         <v>158</v>
       </c>
-      <c r="D5" s="7" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E5" s="17" t="s">
-        <v>2413</v>
-      </c>
-      <c r="F5" s="8" t="e">
-        <v>#N/A</v>
+      <c r="D5" s="21" t="s">
+        <v>2549</v>
+      </c>
+      <c r="E5" s="13" t="s">
+        <v>2411</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>1586</v>
       </c>
       <c r="G5" t="e">
         <v>#N/A</v>
       </c>
-      <c r="H5" s="18" t="s">
+      <c r="H5" s="13" t="s">
         <v>2373</v>
       </c>
       <c r="I5" t="e">
@@ -8366,7 +9106,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" ht="141" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>1634</v>
       </c>
@@ -8376,19 +9116,19 @@
       <c r="C6" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="D6" s="7" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E6" s="17" t="s">
-        <v>2397</v>
-      </c>
-      <c r="F6" s="8" t="e">
-        <v>#N/A</v>
+      <c r="D6" s="22" t="s">
+        <v>2550</v>
+      </c>
+      <c r="E6" s="13" t="s">
+        <v>2395</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>1586</v>
       </c>
       <c r="G6" t="e">
         <v>#N/A</v>
       </c>
-      <c r="H6" s="18" t="s">
+      <c r="H6" s="13" t="s">
         <v>2374</v>
       </c>
       <c r="I6" t="e">
@@ -8401,7 +9141,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" ht="165.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>1634</v>
       </c>
@@ -8411,19 +9151,19 @@
       <c r="C7" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="D7" s="7" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E7" s="17" t="s">
-        <v>2398</v>
-      </c>
-      <c r="F7" s="8" t="e">
-        <v>#N/A</v>
+      <c r="D7" s="23" t="s">
+        <v>2551</v>
+      </c>
+      <c r="E7" s="13" t="s">
+        <v>2396</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>1586</v>
       </c>
       <c r="G7" t="e">
         <v>#N/A</v>
       </c>
-      <c r="H7" s="18" t="s">
+      <c r="H7" s="13" t="s">
         <v>2375</v>
       </c>
       <c r="I7" t="e">
@@ -8436,7 +9176,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" ht="166.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
         <v>1634</v>
       </c>
@@ -8446,19 +9186,19 @@
       <c r="C8" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="D8" s="7" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E8" s="17" t="s">
-        <v>2399</v>
-      </c>
-      <c r="F8" s="8" t="e">
-        <v>#N/A</v>
+      <c r="D8" s="22" t="s">
+        <v>2552</v>
+      </c>
+      <c r="E8" s="13" t="s">
+        <v>2397</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>1586</v>
       </c>
       <c r="G8" t="e">
         <v>#N/A</v>
       </c>
-      <c r="H8" s="18" t="s">
+      <c r="H8" s="13" t="s">
         <v>2376</v>
       </c>
       <c r="I8" t="e">
@@ -8471,7 +9211,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" ht="179.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>1634</v>
       </c>
@@ -8481,19 +9221,19 @@
       <c r="C9" s="6" t="s">
         <v>162</v>
       </c>
-      <c r="D9" s="7" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E9" s="17" t="s">
-        <v>2400</v>
-      </c>
-      <c r="F9" s="8" t="e">
-        <v>#N/A</v>
+      <c r="D9" s="22" t="s">
+        <v>2553</v>
+      </c>
+      <c r="E9" s="13" t="s">
+        <v>2398</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>1586</v>
       </c>
       <c r="G9" t="e">
         <v>#N/A</v>
       </c>
-      <c r="H9" s="18" t="s">
+      <c r="H9" s="13" t="s">
         <v>2377</v>
       </c>
       <c r="I9" t="e">
@@ -8506,7 +9246,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" ht="285.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>1634</v>
       </c>
@@ -8516,19 +9256,19 @@
       <c r="C10" s="6" t="s">
         <v>163</v>
       </c>
-      <c r="D10" s="7" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E10" s="17" t="s">
-        <v>2401</v>
-      </c>
-      <c r="F10" s="8" t="e">
-        <v>#N/A</v>
+      <c r="D10" s="22" t="s">
+        <v>2554</v>
+      </c>
+      <c r="E10" s="13" t="s">
+        <v>2399</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>105</v>
       </c>
       <c r="G10" t="e">
         <v>#N/A</v>
       </c>
-      <c r="H10" s="18" t="s">
+      <c r="H10" s="13" t="s">
         <v>2378</v>
       </c>
       <c r="I10" t="e">
@@ -8541,7 +9281,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" ht="315.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>1634</v>
       </c>
@@ -8551,19 +9291,19 @@
       <c r="C11" s="6" t="s">
         <v>164</v>
       </c>
-      <c r="D11" s="7" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E11" s="17" t="s">
-        <v>2402</v>
-      </c>
-      <c r="F11" s="8" t="e">
-        <v>#N/A</v>
+      <c r="D11" s="22" t="s">
+        <v>2555</v>
+      </c>
+      <c r="E11" s="13" t="s">
+        <v>2400</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>105</v>
       </c>
       <c r="G11" t="e">
         <v>#N/A</v>
       </c>
-      <c r="H11" s="18" t="s">
+      <c r="H11" s="13" t="s">
         <v>2379</v>
       </c>
       <c r="I11" t="e">
@@ -8576,7 +9316,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" ht="255.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
         <v>1634</v>
       </c>
@@ -8586,19 +9326,19 @@
       <c r="C12" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="D12" s="7" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E12" s="17" t="s">
-        <v>2403</v>
-      </c>
-      <c r="F12" s="8" t="e">
-        <v>#N/A</v>
+      <c r="D12" s="22" t="s">
+        <v>2556</v>
+      </c>
+      <c r="E12" s="15" t="s">
+        <v>2401</v>
+      </c>
+      <c r="F12" s="24" t="s">
+        <v>2582</v>
       </c>
       <c r="G12" t="e">
         <v>#N/A</v>
       </c>
-      <c r="H12" s="18" t="s">
+      <c r="H12" s="13" t="s">
         <v>2380</v>
       </c>
       <c r="I12" t="e">
@@ -8611,7 +9351,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" ht="180.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
         <v>1634</v>
       </c>
@@ -8621,19 +9361,19 @@
       <c r="C13" s="6" t="s">
         <v>166</v>
       </c>
-      <c r="D13" s="7" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E13" s="17" t="s">
-        <v>2404</v>
-      </c>
-      <c r="F13" s="8" t="e">
-        <v>#N/A</v>
+      <c r="D13" s="22" t="s">
+        <v>2557</v>
+      </c>
+      <c r="E13" s="15" t="s">
+        <v>2402</v>
+      </c>
+      <c r="F13" s="24" t="s">
+        <v>2582</v>
       </c>
       <c r="G13" t="e">
         <v>#N/A</v>
       </c>
-      <c r="H13" s="18" t="s">
+      <c r="H13" s="13" t="s">
         <v>2381</v>
       </c>
       <c r="I13" t="e">
@@ -8646,7 +9386,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="120.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" ht="225.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
         <v>1634</v>
       </c>
@@ -8656,19 +9396,19 @@
       <c r="C14" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="D14" s="10" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E14" s="17" t="s">
-        <v>2405</v>
-      </c>
-      <c r="F14" s="8" t="e">
-        <v>#N/A</v>
+      <c r="D14" s="22" t="s">
+        <v>2558</v>
+      </c>
+      <c r="E14" s="15" t="s">
+        <v>2403</v>
+      </c>
+      <c r="F14" s="24" t="s">
+        <v>2582</v>
       </c>
       <c r="G14" t="e">
         <v>#N/A</v>
       </c>
-      <c r="H14" s="18" t="s">
+      <c r="H14" s="13" t="s">
         <v>2382</v>
       </c>
       <c r="I14" t="e">
@@ -8681,7 +9421,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" ht="179.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
         <v>1634</v>
       </c>
@@ -8691,19 +9431,19 @@
       <c r="C15" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="D15" s="11" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E15" s="17" t="s">
-        <v>2406</v>
-      </c>
-      <c r="F15" s="8" t="e">
-        <v>#N/A</v>
+      <c r="D15" s="22" t="s">
+        <v>2559</v>
+      </c>
+      <c r="E15" s="15" t="s">
+        <v>2404</v>
+      </c>
+      <c r="F15" s="24" t="s">
+        <v>2582</v>
       </c>
       <c r="G15" t="e">
         <v>#N/A</v>
       </c>
-      <c r="H15" s="18" t="s">
+      <c r="H15" s="13" t="s">
         <v>2383</v>
       </c>
       <c r="I15" t="e">
@@ -8716,7 +9456,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" ht="141" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
         <v>1634</v>
       </c>
@@ -8726,19 +9466,19 @@
       <c r="C16" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="D16" s="11" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E16" s="17" t="s">
-        <v>2407</v>
-      </c>
-      <c r="F16" s="8" t="e">
-        <v>#N/A</v>
+      <c r="D16" s="22" t="s">
+        <v>2560</v>
+      </c>
+      <c r="E16" s="15" t="s">
+        <v>2405</v>
+      </c>
+      <c r="F16" s="24" t="s">
+        <v>2561</v>
       </c>
       <c r="G16" t="e">
         <v>#N/A</v>
       </c>
-      <c r="H16" s="18" t="s">
+      <c r="H16" s="13" t="s">
         <v>2384</v>
       </c>
       <c r="I16" t="e">
@@ -8751,7 +9491,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="17" spans="1:11" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" ht="166.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
         <v>1634</v>
       </c>
@@ -8761,19 +9501,17 @@
       <c r="C17" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="D17" s="11" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E17" s="17" t="s">
-        <v>2408</v>
-      </c>
-      <c r="F17" s="8" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D17" s="22" t="s">
+        <v>2562</v>
+      </c>
+      <c r="E17" s="15" t="s">
+        <v>2406</v>
+      </c>
+      <c r="F17" s="25"/>
       <c r="G17" t="e">
         <v>#N/A</v>
       </c>
-      <c r="H17" s="18" t="s">
+      <c r="H17" s="13" t="s">
         <v>2385</v>
       </c>
       <c r="I17" t="e">
@@ -8786,7 +9524,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="18" spans="1:11" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11" ht="141" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
         <v>1634</v>
       </c>
@@ -8796,19 +9534,19 @@
       <c r="C18" s="6" t="s">
         <v>171</v>
       </c>
-      <c r="D18" s="11" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E18" s="17" t="s">
-        <v>2409</v>
-      </c>
-      <c r="F18" s="8" t="e">
+      <c r="D18" s="22" t="s">
+        <v>2563</v>
+      </c>
+      <c r="E18" s="15" t="s">
+        <v>2407</v>
+      </c>
+      <c r="F18" s="24" t="e">
         <v>#N/A</v>
       </c>
       <c r="G18" t="e">
         <v>#N/A</v>
       </c>
-      <c r="H18" s="18" t="s">
+      <c r="H18" s="13" t="s">
         <v>2386</v>
       </c>
       <c r="I18" t="e">
@@ -8821,29 +9559,29 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="19" spans="1:11" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11" ht="165.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
         <v>1634</v>
       </c>
-      <c r="B19" s="12" t="s">
+      <c r="B19" s="10" t="s">
         <v>1652</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="D19" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E19" s="17" t="s">
-        <v>2410</v>
-      </c>
-      <c r="F19" s="8" t="e">
-        <v>#N/A</v>
+      <c r="D19" s="22" t="s">
+        <v>2564</v>
+      </c>
+      <c r="E19" s="15" t="s">
+        <v>2408</v>
+      </c>
+      <c r="F19" s="24" t="s">
+        <v>2582</v>
       </c>
       <c r="G19" t="e">
         <v>#N/A</v>
       </c>
-      <c r="H19" s="18" t="s">
+      <c r="H19" s="13" t="s">
         <v>2387</v>
       </c>
       <c r="I19" t="e">
@@ -8856,29 +9594,29 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="20" spans="1:11" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:11" ht="153.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
         <v>1634</v>
       </c>
-      <c r="B20" s="12" t="s">
+      <c r="B20" s="10" t="s">
         <v>1653</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="D20" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E20" s="17" t="s">
-        <v>2411</v>
-      </c>
-      <c r="F20" s="8" t="e">
-        <v>#N/A</v>
+      <c r="D20" s="22" t="s">
+        <v>2565</v>
+      </c>
+      <c r="E20" s="15" t="s">
+        <v>2409</v>
+      </c>
+      <c r="F20" s="24" t="s">
+        <v>2582</v>
       </c>
       <c r="G20" t="e">
         <v>#N/A</v>
       </c>
-      <c r="H20" s="18" t="s">
+      <c r="H20" s="13" t="s">
         <v>2388</v>
       </c>
       <c r="I20" t="e">
@@ -8891,29 +9629,29 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="21" spans="1:11" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:11" ht="128.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
         <v>1634</v>
       </c>
-      <c r="B21" s="12" t="s">
+      <c r="B21" s="10" t="s">
         <v>1654</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="D21" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E21" s="17" t="s">
-        <v>2412</v>
-      </c>
-      <c r="F21" s="8" t="e">
-        <v>#N/A</v>
+      <c r="D21" s="22" t="s">
+        <v>2566</v>
+      </c>
+      <c r="E21" s="15" t="s">
+        <v>2410</v>
+      </c>
+      <c r="F21" s="24" t="s">
+        <v>2582</v>
       </c>
       <c r="G21" t="e">
         <v>#N/A</v>
       </c>
-      <c r="H21" s="18" t="s">
+      <c r="H21" s="13" t="s">
         <v>2389</v>
       </c>
       <c r="I21" t="e">
@@ -8926,30 +9664,30 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" ht="210.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
         <v>1634</v>
       </c>
-      <c r="B22" s="12" t="s">
+      <c r="B22" s="10" t="s">
         <v>1655</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="D22" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E22" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F22" s="8" t="e">
-        <v>#N/A</v>
+      <c r="D22" s="22" t="s">
+        <v>2567</v>
+      </c>
+      <c r="E22" s="15" t="s">
+        <v>2568</v>
+      </c>
+      <c r="F22" s="24" t="s">
+        <v>2569</v>
       </c>
       <c r="G22" t="e">
         <v>#N/A</v>
       </c>
-      <c r="H22" s="3" t="e">
-        <v>#N/A</v>
+      <c r="H22" s="13" t="s">
+        <v>2770</v>
       </c>
       <c r="I22" t="e">
         <v>#N/A</v>
@@ -8961,7 +9699,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="23" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" ht="192" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
         <v>1634</v>
       </c>
@@ -8971,20 +9709,20 @@
       <c r="C23" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="D23" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E23" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F23" s="8" t="e">
+      <c r="D23" s="22" t="s">
+        <v>2570</v>
+      </c>
+      <c r="E23" s="15" t="s">
+        <v>2571</v>
+      </c>
+      <c r="F23" s="24" t="e">
         <v>#N/A</v>
       </c>
       <c r="G23" t="e">
         <v>#N/A</v>
       </c>
-      <c r="H23" s="3" t="e">
-        <v>#N/A</v>
+      <c r="H23" s="13" t="s">
+        <v>2771</v>
       </c>
       <c r="I23" t="e">
         <v>#N/A</v>
@@ -8996,7 +9734,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="24" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" ht="225.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
         <v>1634</v>
       </c>
@@ -9006,20 +9744,20 @@
       <c r="C24" s="6" t="s">
         <v>177</v>
       </c>
-      <c r="D24" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E24" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F24" s="8" t="e">
-        <v>#N/A</v>
+      <c r="D24" s="22" t="s">
+        <v>2572</v>
+      </c>
+      <c r="E24" s="15" t="s">
+        <v>2573</v>
+      </c>
+      <c r="F24" s="24" t="s">
+        <v>2569</v>
       </c>
       <c r="G24" t="e">
         <v>#N/A</v>
       </c>
-      <c r="H24" s="3" t="e">
-        <v>#N/A</v>
+      <c r="H24" s="13" t="s">
+        <v>2772</v>
       </c>
       <c r="I24" t="e">
         <v>#N/A</v>
@@ -9031,7 +9769,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="25" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" ht="204.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
         <v>1634</v>
       </c>
@@ -9041,20 +9779,20 @@
       <c r="C25" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="D25" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E25" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F25" s="8" t="e">
+      <c r="D25" s="22" t="s">
+        <v>2574</v>
+      </c>
+      <c r="E25" s="15" t="s">
+        <v>2575</v>
+      </c>
+      <c r="F25" s="24" t="e">
         <v>#N/A</v>
       </c>
       <c r="G25" t="e">
         <v>#N/A</v>
       </c>
-      <c r="H25" s="3" t="e">
-        <v>#N/A</v>
+      <c r="H25" s="13" t="s">
+        <v>2773</v>
       </c>
       <c r="I25" t="e">
         <v>#N/A</v>
@@ -9066,7 +9804,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="26" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" ht="204.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
         <v>1634</v>
       </c>
@@ -9076,20 +9814,20 @@
       <c r="C26" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="D26" s="14" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E26" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F26" s="8" t="e">
-        <v>#N/A</v>
+      <c r="D26" s="22" t="s">
+        <v>2576</v>
+      </c>
+      <c r="E26" s="15" t="s">
+        <v>2577</v>
+      </c>
+      <c r="F26" s="24" t="s">
+        <v>2582</v>
       </c>
       <c r="G26" t="e">
         <v>#N/A</v>
       </c>
-      <c r="H26" s="3" t="e">
-        <v>#N/A</v>
+      <c r="H26" s="13" t="s">
+        <v>2774</v>
       </c>
       <c r="I26" t="e">
         <v>#N/A</v>
@@ -9101,7 +9839,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="27" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:11" ht="179.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
         <v>1634</v>
       </c>
@@ -9111,20 +9849,20 @@
       <c r="C27" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="D27" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E27" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F27" s="8" t="e">
-        <v>#N/A</v>
+      <c r="D27" s="22" t="s">
+        <v>2578</v>
+      </c>
+      <c r="E27" s="15" t="s">
+        <v>2579</v>
+      </c>
+      <c r="F27" s="24" t="s">
+        <v>2582</v>
       </c>
       <c r="G27" t="e">
         <v>#N/A</v>
       </c>
-      <c r="H27" s="3" t="e">
-        <v>#N/A</v>
+      <c r="H27" s="13" t="s">
+        <v>2775</v>
       </c>
       <c r="I27" t="e">
         <v>#N/A</v>
@@ -9136,7 +9874,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="28" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" ht="141" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
         <v>1634</v>
       </c>
@@ -9146,20 +9884,20 @@
       <c r="C28" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="D28" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E28" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F28" s="8" t="e">
-        <v>#N/A</v>
+      <c r="D28" s="22" t="s">
+        <v>2580</v>
+      </c>
+      <c r="E28" s="15" t="s">
+        <v>2581</v>
+      </c>
+      <c r="F28" s="24" t="s">
+        <v>2569</v>
       </c>
       <c r="G28" t="e">
         <v>#N/A</v>
       </c>
-      <c r="H28" s="3" t="e">
-        <v>#N/A</v>
+      <c r="H28" s="13" t="s">
+        <v>2776</v>
       </c>
       <c r="I28" t="e">
         <v>#N/A</v>
@@ -9171,7 +9909,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" ht="165.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
         <v>1634</v>
       </c>
@@ -9181,20 +9919,20 @@
       <c r="C29" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="D29" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E29" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F29" s="8" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G29" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H29" s="3" t="e">
-        <v>#N/A</v>
+      <c r="D29" s="22" t="s">
+        <v>2583</v>
+      </c>
+      <c r="E29" s="15" t="s">
+        <v>2584</v>
+      </c>
+      <c r="F29" s="24" t="s">
+        <v>2569</v>
+      </c>
+      <c r="G29" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H29" s="13" t="s">
+        <v>2585</v>
       </c>
       <c r="I29" t="e">
         <v>#N/A</v>
@@ -9206,7 +9944,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="30" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11" ht="180.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
         <v>1634</v>
       </c>
@@ -9216,20 +9954,20 @@
       <c r="C30" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="D30" s="14" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E30" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F30" s="8" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G30" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H30" s="3" t="e">
-        <v>#N/A</v>
+      <c r="D30" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E30" s="15" t="s">
+        <v>2586</v>
+      </c>
+      <c r="F30" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G30" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H30" s="13" t="s">
+        <v>2587</v>
       </c>
       <c r="I30" t="e">
         <v>#N/A</v>
@@ -9241,7 +9979,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:11" ht="165.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
         <v>1634</v>
       </c>
@@ -9251,20 +9989,20 @@
       <c r="C31" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="D31" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E31" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F31" s="8" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G31" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H31" s="3" t="e">
-        <v>#N/A</v>
+      <c r="D31" s="22" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E31" s="15" t="s">
+        <v>2588</v>
+      </c>
+      <c r="F31" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G31" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H31" s="13" t="s">
+        <v>2589</v>
       </c>
       <c r="I31" t="e">
         <v>#N/A</v>
@@ -9276,7 +10014,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="32" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11" ht="180.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="4" t="s">
         <v>1634</v>
       </c>
@@ -9286,20 +10024,20 @@
       <c r="C32" s="6" t="s">
         <v>185</v>
       </c>
-      <c r="D32" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E32" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F32" s="8" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G32" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H32" s="3" t="e">
-        <v>#N/A</v>
+      <c r="D32" s="22" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E32" s="15" t="s">
+        <v>2590</v>
+      </c>
+      <c r="F32" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G32" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H32" s="13" t="s">
+        <v>2591</v>
       </c>
       <c r="I32" t="e">
         <v>#N/A</v>
@@ -9311,7 +10049,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:11" ht="150.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
         <v>1634</v>
       </c>
@@ -9321,20 +10059,20 @@
       <c r="C33" s="6" t="s">
         <v>186</v>
       </c>
-      <c r="D33" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E33" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F33" s="8" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G33" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H33" s="3" t="e">
-        <v>#N/A</v>
+      <c r="D33" s="22" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E33" s="15" t="s">
+        <v>2592</v>
+      </c>
+      <c r="F33" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G33" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H33" s="13" t="s">
+        <v>2593</v>
       </c>
       <c r="I33" t="e">
         <v>#N/A</v>
@@ -9346,7 +10084,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="34" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:11" ht="150.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="4" t="s">
         <v>1634</v>
       </c>
@@ -9356,20 +10094,20 @@
       <c r="C34" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="D34" s="14" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E34" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F34" s="8" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G34" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H34" s="3" t="e">
-        <v>#N/A</v>
+      <c r="D34" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E34" s="15" t="s">
+        <v>2594</v>
+      </c>
+      <c r="F34" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G34" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H34" s="13" t="s">
+        <v>2595</v>
       </c>
       <c r="I34" t="e">
         <v>#N/A</v>
@@ -9381,7 +10119,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="35" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:11" ht="150.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
         <v>1634</v>
       </c>
@@ -9391,20 +10129,20 @@
       <c r="C35" s="6" t="s">
         <v>188</v>
       </c>
-      <c r="D35" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E35" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F35" s="8" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G35" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H35" s="3" t="e">
-        <v>#N/A</v>
+      <c r="D35" s="22" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E35" s="15" t="s">
+        <v>2596</v>
+      </c>
+      <c r="F35" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G35" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H35" s="13" t="s">
+        <v>2597</v>
       </c>
       <c r="I35" t="e">
         <v>#N/A</v>
@@ -9416,7 +10154,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="36" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:11" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="4" t="s">
         <v>1634</v>
       </c>
@@ -9426,20 +10164,20 @@
       <c r="C36" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="D36" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E36" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F36" s="8" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G36" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H36" s="3" t="e">
-        <v>#N/A</v>
+      <c r="D36" s="22" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E36" s="15" t="s">
+        <v>2598</v>
+      </c>
+      <c r="F36" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G36" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H36" s="13" t="s">
+        <v>2599</v>
       </c>
       <c r="I36" t="e">
         <v>#N/A</v>
@@ -9451,7 +10189,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:11" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
         <v>1634</v>
       </c>
@@ -9461,20 +10199,20 @@
       <c r="C37" s="6" t="s">
         <v>190</v>
       </c>
-      <c r="D37" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E37" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F37" s="8" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G37" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H37" s="3" t="e">
-        <v>#N/A</v>
+      <c r="D37" s="22" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E37" s="15" t="s">
+        <v>2600</v>
+      </c>
+      <c r="F37" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G37" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H37" s="13" t="s">
+        <v>2601</v>
       </c>
       <c r="I37" t="e">
         <v>#N/A</v>
@@ -9486,7 +10224,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:11" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="s">
         <v>1634</v>
       </c>
@@ -9496,20 +10234,20 @@
       <c r="C38" s="6" t="s">
         <v>191</v>
       </c>
-      <c r="D38" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E38" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F38" s="8" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G38" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H38" s="3" t="e">
-        <v>#N/A</v>
+      <c r="D38" s="22" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E38" s="15" t="s">
+        <v>2602</v>
+      </c>
+      <c r="F38" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G38" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H38" s="13" t="s">
+        <v>2603</v>
       </c>
       <c r="I38" t="e">
         <v>#N/A</v>
@@ -9521,7 +10259,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="39" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:11" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
         <v>1634</v>
       </c>
@@ -9531,20 +10269,20 @@
       <c r="C39" s="6" t="s">
         <v>192</v>
       </c>
-      <c r="D39" s="14" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E39" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F39" s="8" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G39" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H39" s="3" t="e">
-        <v>#N/A</v>
+      <c r="D39" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E39" s="15" t="s">
+        <v>2604</v>
+      </c>
+      <c r="F39" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G39" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H39" s="13" t="s">
+        <v>2605</v>
       </c>
       <c r="I39" t="e">
         <v>#N/A</v>
@@ -9556,7 +10294,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:11" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="4" t="s">
         <v>1634</v>
       </c>
@@ -9566,20 +10304,20 @@
       <c r="C40" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="D40" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E40" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F40" s="8" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G40" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H40" s="3" t="e">
-        <v>#N/A</v>
+      <c r="D40" s="22" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E40" s="15" t="s">
+        <v>2606</v>
+      </c>
+      <c r="F40" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G40" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H40" s="13" t="s">
+        <v>2607</v>
       </c>
       <c r="I40" t="e">
         <v>#N/A</v>
@@ -9591,7 +10329,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:11" ht="120.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="4" t="s">
         <v>1634</v>
       </c>
@@ -9601,20 +10339,20 @@
       <c r="C41" s="6" t="s">
         <v>194</v>
       </c>
-      <c r="D41" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E41" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F41" s="8" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G41" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H41" s="3" t="e">
-        <v>#N/A</v>
+      <c r="D41" s="22" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E41" s="15" t="s">
+        <v>2608</v>
+      </c>
+      <c r="F41" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G41" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H41" s="13" t="s">
+        <v>2609</v>
       </c>
       <c r="I41" t="e">
         <v>#N/A</v>
@@ -9626,7 +10364,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:11" ht="120.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="4" t="s">
         <v>1634</v>
       </c>
@@ -9636,20 +10374,20 @@
       <c r="C42" s="6" t="s">
         <v>195</v>
       </c>
-      <c r="D42" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E42" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F42" s="8" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G42" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H42" s="3" t="e">
-        <v>#N/A</v>
+      <c r="D42" s="22" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E42" s="15" t="s">
+        <v>2610</v>
+      </c>
+      <c r="F42" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G42" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H42" s="13" t="s">
+        <v>2611</v>
       </c>
       <c r="I42" t="e">
         <v>#N/A</v>
@@ -9661,7 +10399,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="43" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:11" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="4" t="s">
         <v>1634</v>
       </c>
@@ -9671,20 +10409,20 @@
       <c r="C43" s="6" t="s">
         <v>196</v>
       </c>
-      <c r="D43" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E43" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F43" s="8" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G43" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H43" s="3" t="e">
-        <v>#N/A</v>
+      <c r="D43" s="22" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E43" s="15" t="s">
+        <v>2612</v>
+      </c>
+      <c r="F43" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G43" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H43" s="13" t="s">
+        <v>2613</v>
       </c>
       <c r="I43" t="e">
         <v>#N/A</v>
@@ -9696,7 +10434,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:11" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="4" t="s">
         <v>1634</v>
       </c>
@@ -9706,20 +10444,20 @@
       <c r="C44" s="6" t="s">
         <v>197</v>
       </c>
-      <c r="D44" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E44" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F44" s="8" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G44" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H44" s="3" t="e">
-        <v>#N/A</v>
+      <c r="D44" s="22" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E44" s="15" t="s">
+        <v>2614</v>
+      </c>
+      <c r="F44" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G44" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H44" s="13" t="s">
+        <v>2615</v>
       </c>
       <c r="I44" t="e">
         <v>#N/A</v>
@@ -9731,7 +10469,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:11" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="4" t="s">
         <v>1634</v>
       </c>
@@ -9741,20 +10479,20 @@
       <c r="C45" s="6" t="s">
         <v>198</v>
       </c>
-      <c r="D45" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E45" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F45" s="8" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G45" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H45" s="3" t="e">
-        <v>#N/A</v>
+      <c r="D45" s="22" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E45" s="15" t="s">
+        <v>2616</v>
+      </c>
+      <c r="F45" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G45" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H45" s="13" t="s">
+        <v>2617</v>
       </c>
       <c r="I45" t="e">
         <v>#N/A</v>
@@ -9766,7 +10504,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:11" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="4" t="s">
         <v>1634</v>
       </c>
@@ -9776,20 +10514,20 @@
       <c r="C46" s="6" t="s">
         <v>199</v>
       </c>
-      <c r="D46" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E46" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F46" s="8" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G46" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H46" s="3" t="e">
-        <v>#N/A</v>
+      <c r="D46" s="22" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E46" s="15" t="s">
+        <v>2618</v>
+      </c>
+      <c r="F46" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G46" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H46" s="13" t="s">
+        <v>2619</v>
       </c>
       <c r="I46" t="e">
         <v>#N/A</v>
@@ -9801,7 +10539,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="47" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:11" ht="210.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="4" t="s">
         <v>1634</v>
       </c>
@@ -9811,20 +10549,20 @@
       <c r="C47" s="6" t="s">
         <v>200</v>
       </c>
-      <c r="D47" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E47" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F47" s="8" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G47" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H47" s="3" t="e">
-        <v>#N/A</v>
+      <c r="D47" s="22" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E47" s="15" t="s">
+        <v>2620</v>
+      </c>
+      <c r="F47" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G47" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H47" s="13" t="s">
+        <v>2621</v>
       </c>
       <c r="I47" t="e">
         <v>#N/A</v>
@@ -9836,7 +10574,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="48" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:11" ht="165.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="4" t="s">
         <v>1634</v>
       </c>
@@ -9846,20 +10584,20 @@
       <c r="C48" s="6" t="s">
         <v>201</v>
       </c>
-      <c r="D48" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E48" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F48" s="8" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G48" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H48" s="3" t="e">
-        <v>#N/A</v>
+      <c r="D48" s="22" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E48" s="15" t="s">
+        <v>2622</v>
+      </c>
+      <c r="F48" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G48" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H48" s="13" t="s">
+        <v>2623</v>
       </c>
       <c r="I48" t="e">
         <v>#N/A</v>
@@ -9871,7 +10609,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="49" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:11" ht="180.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="4" t="s">
         <v>1634</v>
       </c>
@@ -9881,20 +10619,20 @@
       <c r="C49" s="6" t="s">
         <v>202</v>
       </c>
-      <c r="D49" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E49" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F49" s="8" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G49" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H49" s="3" t="e">
-        <v>#N/A</v>
+      <c r="D49" s="22" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E49" s="15" t="s">
+        <v>2624</v>
+      </c>
+      <c r="F49" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G49" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H49" s="13" t="s">
+        <v>2625</v>
       </c>
       <c r="I49" t="e">
         <v>#N/A</v>
@@ -9906,7 +10644,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="50" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:11" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="4" t="s">
         <v>1634</v>
       </c>
@@ -9916,20 +10654,20 @@
       <c r="C50" s="6" t="s">
         <v>203</v>
       </c>
-      <c r="D50" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E50" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F50" s="8" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G50" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H50" s="3" t="e">
-        <v>#N/A</v>
+      <c r="D50" s="22" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E50" s="15" t="s">
+        <v>2626</v>
+      </c>
+      <c r="F50" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G50" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H50" s="13" t="s">
+        <v>2627</v>
       </c>
       <c r="I50" t="e">
         <v>#N/A</v>
@@ -9941,7 +10679,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="51" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:11" ht="150.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="4" t="s">
         <v>1634</v>
       </c>
@@ -9951,20 +10689,20 @@
       <c r="C51" s="6" t="s">
         <v>204</v>
       </c>
-      <c r="D51" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E51" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F51" s="8" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G51" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H51" s="3" t="e">
-        <v>#N/A</v>
+      <c r="D51" s="22" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E51" s="15" t="s">
+        <v>2628</v>
+      </c>
+      <c r="F51" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G51" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H51" s="13" t="s">
+        <v>2629</v>
       </c>
       <c r="I51" t="e">
         <v>#N/A</v>
@@ -9976,7 +10714,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="52" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:11" ht="150.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="4" t="s">
         <v>1634</v>
       </c>
@@ -9986,20 +10724,20 @@
       <c r="C52" s="6" t="s">
         <v>205</v>
       </c>
-      <c r="D52" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E52" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F52" s="8" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G52" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H52" s="3" t="e">
-        <v>#N/A</v>
+      <c r="D52" s="22" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E52" s="15" t="s">
+        <v>2630</v>
+      </c>
+      <c r="F52" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G52" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H52" s="13" t="s">
+        <v>2631</v>
       </c>
       <c r="I52" t="e">
         <v>#N/A</v>
@@ -10011,7 +10749,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="53" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:11" ht="180.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="4" t="s">
         <v>1634</v>
       </c>
@@ -10021,20 +10759,20 @@
       <c r="C53" s="6" t="s">
         <v>206</v>
       </c>
-      <c r="D53" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E53" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F53" s="8" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G53" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H53" s="3" t="e">
-        <v>#N/A</v>
+      <c r="D53" s="22" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E53" s="15" t="s">
+        <v>2632</v>
+      </c>
+      <c r="F53" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G53" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H53" s="13" t="s">
+        <v>2633</v>
       </c>
       <c r="I53" t="e">
         <v>#N/A</v>
@@ -10046,7 +10784,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:11" ht="255.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" s="4" t="s">
         <v>1634</v>
       </c>
@@ -10056,20 +10794,20 @@
       <c r="C54" s="6" t="s">
         <v>207</v>
       </c>
-      <c r="D54" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E54" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F54" s="8" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G54" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H54" s="3" t="e">
-        <v>#N/A</v>
+      <c r="D54" s="22" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E54" s="15" t="s">
+        <v>2634</v>
+      </c>
+      <c r="F54" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G54" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H54" s="13" t="s">
+        <v>2635</v>
       </c>
       <c r="I54" t="e">
         <v>#N/A</v>
@@ -10081,7 +10819,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="55" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:11" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A55" s="4" t="s">
         <v>1634</v>
       </c>
@@ -10091,20 +10829,20 @@
       <c r="C55" s="6" t="s">
         <v>208</v>
       </c>
-      <c r="D55" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E55" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F55" s="8" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G55" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H55" s="3" t="e">
-        <v>#N/A</v>
+      <c r="D55" s="22" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E55" s="15" t="s">
+        <v>2636</v>
+      </c>
+      <c r="F55" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G55" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H55" s="13" t="s">
+        <v>2637</v>
       </c>
       <c r="I55" t="e">
         <v>#N/A</v>
@@ -10116,7 +10854,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="56" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:11" ht="180.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A56" s="4" t="s">
         <v>1634</v>
       </c>
@@ -10126,20 +10864,20 @@
       <c r="C56" s="6" t="s">
         <v>209</v>
       </c>
-      <c r="D56" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E56" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F56" s="8" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G56" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H56" s="3" t="e">
-        <v>#N/A</v>
+      <c r="D56" s="22" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E56" s="15" t="s">
+        <v>2638</v>
+      </c>
+      <c r="F56" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G56" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H56" s="13" t="s">
+        <v>2639</v>
       </c>
       <c r="I56" t="e">
         <v>#N/A</v>
@@ -10151,7 +10889,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="57" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:11" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A57" s="4" t="s">
         <v>1634</v>
       </c>
@@ -10161,20 +10899,20 @@
       <c r="C57" s="6" t="s">
         <v>210</v>
       </c>
-      <c r="D57" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E57" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F57" s="8" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G57" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H57" s="3" t="e">
-        <v>#N/A</v>
+      <c r="D57" s="22" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E57" s="15" t="s">
+        <v>2640</v>
+      </c>
+      <c r="F57" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G57" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H57" s="13" t="s">
+        <v>2641</v>
       </c>
       <c r="I57" t="e">
         <v>#N/A</v>
@@ -10186,7 +10924,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="58" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:11" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A58" s="4" t="s">
         <v>1634</v>
       </c>
@@ -10196,20 +10934,20 @@
       <c r="C58" s="6" t="s">
         <v>211</v>
       </c>
-      <c r="D58" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E58" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F58" s="8" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G58" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H58" s="3" t="e">
-        <v>#N/A</v>
+      <c r="D58" s="22" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E58" s="15" t="s">
+        <v>2642</v>
+      </c>
+      <c r="F58" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G58" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H58" s="13" t="s">
+        <v>2643</v>
       </c>
       <c r="I58" t="e">
         <v>#N/A</v>
@@ -10221,7 +10959,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="59" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:11" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A59" s="4" t="s">
         <v>1634</v>
       </c>
@@ -10231,20 +10969,20 @@
       <c r="C59" s="6" t="s">
         <v>212</v>
       </c>
-      <c r="D59" s="14" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E59" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F59" s="8" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G59" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H59" s="3" t="e">
-        <v>#N/A</v>
+      <c r="D59" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E59" s="15" t="s">
+        <v>2644</v>
+      </c>
+      <c r="F59" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G59" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H59" s="13" t="s">
+        <v>2645</v>
       </c>
       <c r="I59" t="e">
         <v>#N/A</v>
@@ -10256,7 +10994,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="60" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:11" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A60" s="4" t="s">
         <v>1634</v>
       </c>
@@ -10266,20 +11004,20 @@
       <c r="C60" s="6" t="s">
         <v>213</v>
       </c>
-      <c r="D60" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E60" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F60" s="8" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G60" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H60" s="3" t="e">
-        <v>#N/A</v>
+      <c r="D60" s="22" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E60" s="15" t="s">
+        <v>2646</v>
+      </c>
+      <c r="F60" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G60" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H60" s="13" t="s">
+        <v>2647</v>
       </c>
       <c r="I60" t="e">
         <v>#N/A</v>
@@ -10291,7 +11029,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="61" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:11" ht="165.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A61" s="4" t="s">
         <v>1634</v>
       </c>
@@ -10301,20 +11039,20 @@
       <c r="C61" s="6" t="s">
         <v>214</v>
       </c>
-      <c r="D61" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E61" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F61" s="8" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G61" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H61" s="3" t="e">
-        <v>#N/A</v>
+      <c r="D61" s="22" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E61" s="27" t="s">
+        <v>2648</v>
+      </c>
+      <c r="F61" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G61" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H61" s="13" t="s">
+        <v>2649</v>
       </c>
       <c r="I61" t="e">
         <v>#N/A</v>
@@ -10326,7 +11064,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="62" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:11" ht="120.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A62" s="4" t="s">
         <v>1634</v>
       </c>
@@ -10336,20 +11074,20 @@
       <c r="C62" s="6" t="s">
         <v>215</v>
       </c>
-      <c r="D62" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E62" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F62" s="8" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G62" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H62" s="3" t="e">
-        <v>#N/A</v>
+      <c r="D62" s="22" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E62" s="15" t="s">
+        <v>2650</v>
+      </c>
+      <c r="F62" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G62" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H62" s="13" t="s">
+        <v>2651</v>
       </c>
       <c r="I62" t="e">
         <v>#N/A</v>
@@ -10361,7 +11099,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="63" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:11" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A63" s="4" t="s">
         <v>1634</v>
       </c>
@@ -10371,20 +11109,20 @@
       <c r="C63" s="6" t="s">
         <v>216</v>
       </c>
-      <c r="D63" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E63" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F63" s="8" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G63" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H63" s="3" t="e">
-        <v>#N/A</v>
+      <c r="D63" s="22" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E63" s="15" t="s">
+        <v>2652</v>
+      </c>
+      <c r="F63" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G63" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H63" s="13" t="s">
+        <v>2653</v>
       </c>
       <c r="I63" t="e">
         <v>#N/A</v>
@@ -10396,7 +11134,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="64" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:11" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A64" s="4" t="s">
         <v>1634</v>
       </c>
@@ -10406,20 +11144,20 @@
       <c r="C64" s="6" t="s">
         <v>217</v>
       </c>
-      <c r="D64" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E64" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F64" s="8" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G64" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H64" s="3" t="e">
-        <v>#N/A</v>
+      <c r="D64" s="22" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E64" s="15" t="s">
+        <v>2654</v>
+      </c>
+      <c r="F64" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G64" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H64" s="13" t="s">
+        <v>2655</v>
       </c>
       <c r="I64" t="e">
         <v>#N/A</v>
@@ -10431,7 +11169,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="65" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:11" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A65" s="4" t="s">
         <v>1634</v>
       </c>
@@ -10441,20 +11179,20 @@
       <c r="C65" s="6" t="s">
         <v>218</v>
       </c>
-      <c r="D65" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E65" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F65" s="8" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G65" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H65" s="3" t="e">
-        <v>#N/A</v>
+      <c r="D65" s="22" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E65" s="15" t="s">
+        <v>2656</v>
+      </c>
+      <c r="F65" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G65" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H65" s="13" t="s">
+        <v>2657</v>
       </c>
       <c r="I65" t="e">
         <v>#N/A</v>
@@ -10466,7 +11204,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="66" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:11" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A66" s="4" t="s">
         <v>1634</v>
       </c>
@@ -10476,20 +11214,20 @@
       <c r="C66" s="6" t="s">
         <v>219</v>
       </c>
-      <c r="D66" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E66" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F66" s="8" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G66" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H66" s="3" t="e">
-        <v>#N/A</v>
+      <c r="D66" s="22" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E66" s="15" t="s">
+        <v>2658</v>
+      </c>
+      <c r="F66" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G66" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H66" s="13" t="s">
+        <v>2659</v>
       </c>
       <c r="I66" t="e">
         <v>#N/A</v>
@@ -10501,7 +11239,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="67" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:11" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A67" s="4" t="s">
         <v>1634</v>
       </c>
@@ -10511,20 +11249,20 @@
       <c r="C67" s="6" t="s">
         <v>220</v>
       </c>
-      <c r="D67" s="7" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E67" s="21" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F67" s="8" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G67" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H67" s="3" t="e">
-        <v>#N/A</v>
+      <c r="D67" s="21" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E67" s="15" t="s">
+        <v>2660</v>
+      </c>
+      <c r="F67" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G67" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H67" s="13" t="s">
+        <v>2661</v>
       </c>
       <c r="I67" t="e">
         <v>#N/A</v>
@@ -10536,7 +11274,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:11" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A68" s="4" t="s">
         <v>1634</v>
       </c>
@@ -10546,20 +11284,20 @@
       <c r="C68" s="6" t="s">
         <v>221</v>
       </c>
-      <c r="D68" s="7" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E68" s="21" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F68" s="8" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G68" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H68" s="3" t="e">
-        <v>#N/A</v>
+      <c r="D68" s="21" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E68" s="15" t="s">
+        <v>2662</v>
+      </c>
+      <c r="F68" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G68" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H68" s="13" t="s">
+        <v>2663</v>
       </c>
       <c r="I68" t="e">
         <v>#N/A</v>
@@ -10571,7 +11309,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="69" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:11" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A69" s="4" t="s">
         <v>1634</v>
       </c>
@@ -10581,20 +11319,20 @@
       <c r="C69" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="D69" s="7" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E69" s="21" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F69" s="8" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G69" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H69" s="3" t="e">
-        <v>#N/A</v>
+      <c r="D69" s="21" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E69" s="15" t="s">
+        <v>2664</v>
+      </c>
+      <c r="F69" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G69" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H69" s="13" t="s">
+        <v>2665</v>
       </c>
       <c r="I69" t="e">
         <v>#N/A</v>
@@ -10606,7 +11344,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="70" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:11" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A70" s="4" t="s">
         <v>1634</v>
       </c>
@@ -10616,20 +11354,20 @@
       <c r="C70" s="6" t="s">
         <v>223</v>
       </c>
-      <c r="D70" s="9" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E70" s="21" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F70" s="8" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G70" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H70" s="3" t="e">
-        <v>#N/A</v>
+      <c r="D70" s="28" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E70" s="15" t="s">
+        <v>2666</v>
+      </c>
+      <c r="F70" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G70" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H70" s="13" t="s">
+        <v>2667</v>
       </c>
       <c r="I70" t="e">
         <v>#N/A</v>
@@ -10641,7 +11379,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="71" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:11" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A71" s="4" t="s">
         <v>1634</v>
       </c>
@@ -10651,20 +11389,20 @@
       <c r="C71" s="6" t="s">
         <v>224</v>
       </c>
-      <c r="D71" s="9" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E71" s="21" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F71" s="8" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G71" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H71" s="3" t="e">
-        <v>#N/A</v>
+      <c r="D71" s="28" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E71" s="15" t="s">
+        <v>2668</v>
+      </c>
+      <c r="F71" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G71" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H71" s="13" t="s">
+        <v>2669</v>
       </c>
       <c r="I71" t="e">
         <v>#N/A</v>
@@ -10676,7 +11414,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="72" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:11" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A72" s="4" t="s">
         <v>1634</v>
       </c>
@@ -10686,20 +11424,20 @@
       <c r="C72" s="6" t="s">
         <v>225</v>
       </c>
-      <c r="D72" s="9" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E72" s="21" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F72" s="8" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G72" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H72" s="3" t="e">
-        <v>#N/A</v>
+      <c r="D72" s="28" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E72" s="15" t="s">
+        <v>2670</v>
+      </c>
+      <c r="F72" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G72" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H72" s="13" t="s">
+        <v>2671</v>
       </c>
       <c r="I72" t="e">
         <v>#N/A</v>
@@ -10711,7 +11449,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="73" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:11" ht="120.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A73" s="4" t="s">
         <v>1634</v>
       </c>
@@ -10721,20 +11459,20 @@
       <c r="C73" s="6" t="s">
         <v>226</v>
       </c>
-      <c r="D73" s="11" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E73" s="21" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F73" s="8" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G73" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H73" s="3" t="e">
-        <v>#N/A</v>
+      <c r="D73" s="28" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E73" s="15" t="s">
+        <v>2672</v>
+      </c>
+      <c r="F73" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G73" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H73" s="13" t="s">
+        <v>2673</v>
       </c>
       <c r="I73" t="e">
         <v>#N/A</v>
@@ -10746,7 +11484,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="74" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:11" ht="120.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A74" s="4" t="s">
         <v>1634</v>
       </c>
@@ -10756,20 +11494,20 @@
       <c r="C74" s="6" t="s">
         <v>227</v>
       </c>
-      <c r="D74" s="11" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E74" s="21" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F74" s="8" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G74" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H74" s="3" t="e">
-        <v>#N/A</v>
+      <c r="D74" s="28" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E74" s="15" t="s">
+        <v>2674</v>
+      </c>
+      <c r="F74" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G74" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H74" s="13" t="s">
+        <v>2675</v>
       </c>
       <c r="I74" t="e">
         <v>#N/A</v>
@@ -10781,7 +11519,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="75" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:11" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A75" s="4" t="s">
         <v>1634</v>
       </c>
@@ -10791,20 +11529,20 @@
       <c r="C75" s="6" t="s">
         <v>228</v>
       </c>
-      <c r="D75" s="11" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E75" s="21" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F75" s="8" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G75" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H75" s="3" t="e">
-        <v>#N/A</v>
+      <c r="D75" s="28" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E75" s="15" t="s">
+        <v>2676</v>
+      </c>
+      <c r="F75" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G75" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H75" s="13" t="s">
+        <v>2677</v>
       </c>
       <c r="I75" t="e">
         <v>#N/A</v>
@@ -10816,7 +11554,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:11" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A76" s="4" t="s">
         <v>1634</v>
       </c>
@@ -10826,20 +11564,20 @@
       <c r="C76" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="D76" s="11" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E76" s="21" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F76" s="8" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G76" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H76" s="3" t="e">
-        <v>#N/A</v>
+      <c r="D76" s="28" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E76" s="15" t="s">
+        <v>2678</v>
+      </c>
+      <c r="F76" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G76" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H76" s="13" t="s">
+        <v>2679</v>
       </c>
       <c r="I76" t="e">
         <v>#N/A</v>
@@ -10851,7 +11589,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="77" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:11" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A77" s="4" t="s">
         <v>1634</v>
       </c>
@@ -10861,20 +11599,20 @@
       <c r="C77" s="6" t="s">
         <v>230</v>
       </c>
-      <c r="D77" s="11" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E77" s="21" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F77" s="8" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G77" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H77" s="3" t="e">
-        <v>#N/A</v>
+      <c r="D77" s="28" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E77" s="15" t="s">
+        <v>2680</v>
+      </c>
+      <c r="F77" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G77" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H77" s="13" t="s">
+        <v>2681</v>
       </c>
       <c r="I77" t="e">
         <v>#N/A</v>
@@ -10886,7 +11624,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="78" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:11" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A78" s="4" t="s">
         <v>1634</v>
       </c>
@@ -10896,20 +11634,20 @@
       <c r="C78" s="6" t="s">
         <v>231</v>
       </c>
-      <c r="D78" s="11" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E78" s="21" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F78" s="8" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G78" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H78" s="3" t="e">
-        <v>#N/A</v>
+      <c r="D78" s="28" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E78" s="15" t="s">
+        <v>2682</v>
+      </c>
+      <c r="F78" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G78" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H78" s="13" t="s">
+        <v>2683</v>
       </c>
       <c r="I78" t="e">
         <v>#N/A</v>
@@ -10921,7 +11659,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="79" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:11" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A79" s="4" t="s">
         <v>1634</v>
       </c>
@@ -10931,20 +11669,20 @@
       <c r="C79" s="6" t="s">
         <v>232</v>
       </c>
-      <c r="D79" s="11" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E79" s="21" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F79" s="8" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G79" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H79" s="3" t="e">
-        <v>#N/A</v>
+      <c r="D79" s="28" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E79" s="15" t="s">
+        <v>2684</v>
+      </c>
+      <c r="F79" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G79" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H79" s="13" t="s">
+        <v>2685</v>
       </c>
       <c r="I79" t="e">
         <v>#N/A</v>
@@ -10956,7 +11694,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="80" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:11" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A80" s="4" t="s">
         <v>1634</v>
       </c>
@@ -10966,20 +11704,20 @@
       <c r="C80" s="6" t="s">
         <v>233</v>
       </c>
-      <c r="D80" s="11" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E80" s="8" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F80" s="8" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G80" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H80" s="3" t="e">
-        <v>#N/A</v>
+      <c r="D80" s="28" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E80" s="22" t="s">
+        <v>2686</v>
+      </c>
+      <c r="F80" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G80" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H80" s="13" t="s">
+        <v>2687</v>
       </c>
       <c r="I80" t="e">
         <v>#N/A</v>
@@ -10991,7 +11729,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="81" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:11" ht="51.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A81" s="4" t="s">
         <v>1634</v>
       </c>
@@ -11001,20 +11739,20 @@
       <c r="C81" s="6" t="s">
         <v>234</v>
       </c>
-      <c r="D81" s="11" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E81" s="8" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F81" s="8" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G81" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H81" s="3" t="e">
-        <v>#N/A</v>
+      <c r="D81" s="28" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E81" s="22" t="s">
+        <v>2688</v>
+      </c>
+      <c r="F81" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G81" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H81" s="13" t="s">
+        <v>2689</v>
       </c>
       <c r="I81" t="e">
         <v>#N/A</v>
@@ -11026,7 +11764,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="82" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:11" ht="51.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A82" s="4" t="s">
         <v>1634</v>
       </c>
@@ -11036,20 +11774,20 @@
       <c r="C82" s="6" t="s">
         <v>235</v>
       </c>
-      <c r="D82" s="11" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E82" s="8" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F82" s="8" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G82" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H82" s="3" t="e">
-        <v>#N/A</v>
+      <c r="D82" s="28" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E82" s="22" t="s">
+        <v>2690</v>
+      </c>
+      <c r="F82" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G82" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H82" s="13" t="s">
+        <v>2691</v>
       </c>
       <c r="I82" t="e">
         <v>#N/A</v>
@@ -11061,7 +11799,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="83" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:11" ht="51.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A83" s="4" t="s">
         <v>1634</v>
       </c>
@@ -11071,20 +11809,20 @@
       <c r="C83" s="6" t="s">
         <v>236</v>
       </c>
-      <c r="D83" s="11" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E83" s="8" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F83" s="8" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G83" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H83" s="3" t="e">
-        <v>#N/A</v>
+      <c r="D83" s="28" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E83" s="22" t="s">
+        <v>2692</v>
+      </c>
+      <c r="F83" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G83" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H83" s="13" t="s">
+        <v>2693</v>
       </c>
       <c r="I83" t="e">
         <v>#N/A</v>
@@ -11096,7 +11834,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="84" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:11" ht="120.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A84" s="4" t="s">
         <v>1634</v>
       </c>
@@ -11106,20 +11844,20 @@
       <c r="C84" s="6" t="s">
         <v>237</v>
       </c>
-      <c r="D84" s="11" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E84" s="21" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F84" s="8" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G84" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H84" s="3" t="e">
-        <v>#N/A</v>
+      <c r="D84" s="28" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E84" s="15" t="s">
+        <v>2694</v>
+      </c>
+      <c r="F84" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G84" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H84" s="13" t="s">
+        <v>2695</v>
       </c>
       <c r="I84" t="e">
         <v>#N/A</v>
@@ -11131,30 +11869,30 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:11" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A85" s="4" t="s">
         <v>1634</v>
       </c>
-      <c r="B85" s="12" t="s">
+      <c r="B85" s="10" t="s">
         <v>1718</v>
       </c>
       <c r="C85" s="6" t="s">
         <v>238</v>
       </c>
-      <c r="D85" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E85" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F85" s="8" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G85" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H85" s="3" t="e">
-        <v>#N/A</v>
+      <c r="D85" s="22" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E85" s="15" t="s">
+        <v>2696</v>
+      </c>
+      <c r="F85" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G85" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H85" s="13" t="s">
+        <v>2697</v>
       </c>
       <c r="I85" t="e">
         <v>#N/A</v>
@@ -11166,30 +11904,30 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="86" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:11" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A86" s="4" t="s">
         <v>1634</v>
       </c>
-      <c r="B86" s="12" t="s">
+      <c r="B86" s="10" t="s">
         <v>1719</v>
       </c>
       <c r="C86" s="6" t="s">
         <v>239</v>
       </c>
-      <c r="D86" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E86" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F86" s="8" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G86" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H86" s="3" t="e">
-        <v>#N/A</v>
+      <c r="D86" s="22" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E86" s="15" t="s">
+        <v>2698</v>
+      </c>
+      <c r="F86" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G86" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H86" s="13" t="s">
+        <v>2699</v>
       </c>
       <c r="I86" t="e">
         <v>#N/A</v>
@@ -11201,30 +11939,30 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:11" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A87" s="4" t="s">
         <v>1634</v>
       </c>
-      <c r="B87" s="12" t="s">
+      <c r="B87" s="10" t="s">
         <v>1720</v>
       </c>
       <c r="C87" s="6" t="s">
         <v>240</v>
       </c>
-      <c r="D87" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E87" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F87" s="8" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G87" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H87" s="3" t="e">
-        <v>#N/A</v>
+      <c r="D87" s="22" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E87" s="15" t="s">
+        <v>2700</v>
+      </c>
+      <c r="F87" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G87" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H87" s="13" t="s">
+        <v>2701</v>
       </c>
       <c r="I87" t="e">
         <v>#N/A</v>
@@ -11236,7 +11974,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:11" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A88" s="4" t="s">
         <v>1634</v>
       </c>
@@ -11246,20 +11984,20 @@
       <c r="C88" s="6" t="s">
         <v>241</v>
       </c>
-      <c r="D88" s="14" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E88" s="21" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F88" s="8" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G88" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H88" s="3" t="e">
-        <v>#N/A</v>
+      <c r="D88" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E88" s="15" t="s">
+        <v>2702</v>
+      </c>
+      <c r="F88" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G88" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H88" s="13" t="s">
+        <v>2703</v>
       </c>
       <c r="I88" t="e">
         <v>#N/A</v>
@@ -11271,7 +12009,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:11" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A89" s="4" t="s">
         <v>1634</v>
       </c>
@@ -11281,20 +12019,20 @@
       <c r="C89" s="6" t="s">
         <v>242</v>
       </c>
-      <c r="D89" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E89" s="21" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F89" s="8" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G89" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H89" s="3" t="e">
-        <v>#N/A</v>
+      <c r="D89" s="22" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E89" s="15" t="s">
+        <v>2704</v>
+      </c>
+      <c r="F89" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G89" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H89" s="13" t="s">
+        <v>2705</v>
       </c>
       <c r="I89" t="e">
         <v>#N/A</v>
@@ -11306,7 +12044,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="90" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:11" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A90" s="4" t="s">
         <v>1634</v>
       </c>
@@ -11316,20 +12054,20 @@
       <c r="C90" s="6" t="s">
         <v>243</v>
       </c>
-      <c r="D90" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E90" s="21" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F90" s="8" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G90" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H90" s="3" t="e">
-        <v>#N/A</v>
+      <c r="D90" s="22" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E90" s="15" t="s">
+        <v>2706</v>
+      </c>
+      <c r="F90" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G90" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H90" s="13" t="s">
+        <v>2707</v>
       </c>
       <c r="I90" t="e">
         <v>#N/A</v>
@@ -11341,7 +12079,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="91" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:11" ht="120.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A91" s="4" t="s">
         <v>1634</v>
       </c>
@@ -11351,20 +12089,20 @@
       <c r="C91" s="6" t="s">
         <v>244</v>
       </c>
-      <c r="D91" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E91" s="21" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F91" s="8" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G91" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H91" s="3" t="e">
-        <v>#N/A</v>
+      <c r="D91" s="22" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E91" s="15" t="s">
+        <v>2708</v>
+      </c>
+      <c r="F91" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G91" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H91" s="13" t="s">
+        <v>2709</v>
       </c>
       <c r="I91" t="e">
         <v>#N/A</v>
@@ -11376,7 +12114,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:11" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A92" s="4" t="s">
         <v>1634</v>
       </c>
@@ -11386,20 +12124,20 @@
       <c r="C92" s="6" t="s">
         <v>245</v>
       </c>
-      <c r="D92" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E92" s="21" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F92" s="8" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G92" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H92" s="3" t="e">
-        <v>#N/A</v>
+      <c r="D92" s="22" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E92" s="15" t="s">
+        <v>2710</v>
+      </c>
+      <c r="F92" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G92" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H92" s="13" t="s">
+        <v>2711</v>
       </c>
       <c r="I92" t="e">
         <v>#N/A</v>
@@ -11411,7 +12149,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="93" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:11" ht="150.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A93" s="4" t="s">
         <v>1634</v>
       </c>
@@ -11421,20 +12159,20 @@
       <c r="C93" s="6" t="s">
         <v>246</v>
       </c>
-      <c r="D93" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E93" s="21" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F93" s="8" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G93" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H93" s="3" t="e">
-        <v>#N/A</v>
+      <c r="D93" s="22" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E93" s="15" t="s">
+        <v>2712</v>
+      </c>
+      <c r="F93" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G93" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H93" s="13" t="s">
+        <v>2713</v>
       </c>
       <c r="I93" t="e">
         <v>#N/A</v>
@@ -11446,7 +12184,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:11" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A94" s="4" t="s">
         <v>1634</v>
       </c>
@@ -11456,20 +12194,20 @@
       <c r="C94" s="6" t="s">
         <v>247</v>
       </c>
-      <c r="D94" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E94" s="21" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F94" s="8" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G94" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H94" s="3" t="e">
-        <v>#N/A</v>
+      <c r="D94" s="22" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E94" s="15" t="s">
+        <v>2714</v>
+      </c>
+      <c r="F94" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G94" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H94" s="13" t="s">
+        <v>2715</v>
       </c>
       <c r="I94" t="e">
         <v>#N/A</v>
@@ -11481,7 +12219,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:11" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A95" s="4" t="s">
         <v>1634</v>
       </c>
@@ -11491,20 +12229,20 @@
       <c r="C95" s="6" t="s">
         <v>248</v>
       </c>
-      <c r="D95" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E95" s="21" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F95" s="8" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G95" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H95" s="3" t="e">
-        <v>#N/A</v>
+      <c r="D95" s="22" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E95" s="15" t="s">
+        <v>2716</v>
+      </c>
+      <c r="F95" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G95" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H95" s="13" t="s">
+        <v>2717</v>
       </c>
       <c r="I95" t="e">
         <v>#N/A</v>
@@ -11516,7 +12254,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="96" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:11" ht="165.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A96" s="4" t="s">
         <v>1634</v>
       </c>
@@ -11526,20 +12264,20 @@
       <c r="C96" s="6" t="s">
         <v>249</v>
       </c>
-      <c r="D96" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E96" s="21" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F96" s="8" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G96" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H96" s="3" t="e">
-        <v>#N/A</v>
+      <c r="D96" s="22" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E96" s="15" t="s">
+        <v>2718</v>
+      </c>
+      <c r="F96" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G96" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H96" s="13" t="s">
+        <v>2719</v>
       </c>
       <c r="I96" t="e">
         <v>#N/A</v>
@@ -11551,7 +12289,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:11" ht="375.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A97" s="4" t="s">
         <v>1634</v>
       </c>
@@ -11561,20 +12299,20 @@
       <c r="C97" s="6" t="s">
         <v>250</v>
       </c>
-      <c r="D97" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E97" s="21" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F97" s="8" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G97" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H97" s="3" t="e">
-        <v>#N/A</v>
+      <c r="D97" s="22" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E97" s="15" t="s">
+        <v>2720</v>
+      </c>
+      <c r="F97" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G97" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H97" s="13" t="s">
+        <v>2721</v>
       </c>
       <c r="I97" t="e">
         <v>#N/A</v>
@@ -11586,7 +12324,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="98" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:11" ht="375.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A98" s="4" t="s">
         <v>1634</v>
       </c>
@@ -11596,20 +12334,20 @@
       <c r="C98" s="6" t="s">
         <v>251</v>
       </c>
-      <c r="D98" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E98" s="21" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F98" s="8" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G98" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H98" s="3" t="e">
-        <v>#N/A</v>
+      <c r="D98" s="22" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E98" s="15" t="s">
+        <v>2722</v>
+      </c>
+      <c r="F98" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G98" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H98" s="13" t="s">
+        <v>2723</v>
       </c>
       <c r="I98" t="e">
         <v>#N/A</v>
@@ -11621,7 +12359,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="99" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:11" ht="409.6" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A99" s="4" t="s">
         <v>1634</v>
       </c>
@@ -11631,20 +12369,20 @@
       <c r="C99" s="6" t="s">
         <v>252</v>
       </c>
-      <c r="D99" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E99" s="21" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F99" s="8" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G99" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H99" s="3" t="e">
-        <v>#N/A</v>
+      <c r="D99" s="22" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E99" s="15" t="s">
+        <v>2724</v>
+      </c>
+      <c r="F99" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G99" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H99" s="13" t="s">
+        <v>2725</v>
       </c>
       <c r="I99" t="e">
         <v>#N/A</v>
@@ -11656,7 +12394,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:11" ht="225.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A100" s="4" t="s">
         <v>1634</v>
       </c>
@@ -11666,20 +12404,20 @@
       <c r="C100" s="6" t="s">
         <v>253</v>
       </c>
-      <c r="D100" s="7" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E100" s="21" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F100" s="8" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G100" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H100" s="3" t="e">
-        <v>#N/A</v>
+      <c r="D100" s="21" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E100" s="15" t="s">
+        <v>2726</v>
+      </c>
+      <c r="F100" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G100" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H100" s="13" t="s">
+        <v>2727</v>
       </c>
       <c r="I100" t="e">
         <v>#N/A</v>
@@ -11691,7 +12429,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:11" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A101" s="4" t="s">
         <v>1634</v>
       </c>
@@ -11701,20 +12439,20 @@
       <c r="C101" s="6" t="s">
         <v>254</v>
       </c>
-      <c r="D101" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E101" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F101" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G101" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H101" s="3" t="e">
-        <v>#N/A</v>
+      <c r="D101" s="15" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E101" s="15" t="s">
+        <v>2728</v>
+      </c>
+      <c r="F101" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G101" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H101" s="13" t="s">
+        <v>2729</v>
       </c>
       <c r="I101" t="e">
         <v>#N/A</v>
@@ -11726,7 +12464,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="102" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:11" ht="120.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A102" s="4" t="s">
         <v>1634</v>
       </c>
@@ -11736,20 +12474,20 @@
       <c r="C102" s="6" t="s">
         <v>255</v>
       </c>
-      <c r="D102" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E102" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F102" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G102" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H102" s="3" t="e">
-        <v>#N/A</v>
+      <c r="D102" s="15" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E102" s="15" t="s">
+        <v>2730</v>
+      </c>
+      <c r="F102" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G102" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H102" s="13" t="s">
+        <v>2731</v>
       </c>
       <c r="I102" t="e">
         <v>#N/A</v>
@@ -11761,7 +12499,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:11" ht="120.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A103" s="4" t="s">
         <v>1634</v>
       </c>
@@ -11771,20 +12509,20 @@
       <c r="C103" s="6" t="s">
         <v>256</v>
       </c>
-      <c r="D103" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E103" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F103" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G103" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H103" s="3" t="e">
-        <v>#N/A</v>
+      <c r="D103" s="15" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E103" s="15" t="s">
+        <v>2732</v>
+      </c>
+      <c r="F103" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G103" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H103" s="13" t="s">
+        <v>2733</v>
       </c>
       <c r="I103" t="e">
         <v>#N/A</v>
@@ -11796,7 +12534,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:11" ht="135.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A104" s="4" t="s">
         <v>1634</v>
       </c>
@@ -11806,20 +12544,20 @@
       <c r="C104" s="6" t="s">
         <v>257</v>
       </c>
-      <c r="D104" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E104" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F104" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G104" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H104" s="3" t="e">
-        <v>#N/A</v>
+      <c r="D104" s="15" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E104" s="15" t="s">
+        <v>2734</v>
+      </c>
+      <c r="F104" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G104" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H104" s="13" t="s">
+        <v>2735</v>
       </c>
       <c r="I104" t="e">
         <v>#N/A</v>
@@ -11831,7 +12569,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="105" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:11" ht="300.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A105" s="4" t="s">
         <v>1634</v>
       </c>
@@ -11841,20 +12579,20 @@
       <c r="C105" s="6" t="s">
         <v>258</v>
       </c>
-      <c r="D105" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E105" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F105" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G105" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H105" s="3" t="e">
-        <v>#N/A</v>
+      <c r="D105" s="15" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E105" s="15" t="s">
+        <v>2736</v>
+      </c>
+      <c r="F105" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G105" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H105" s="13" t="s">
+        <v>2737</v>
       </c>
       <c r="I105" t="e">
         <v>#N/A</v>
@@ -11866,7 +12604,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:11" ht="165.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A106" s="4" t="s">
         <v>1634</v>
       </c>
@@ -11876,20 +12614,20 @@
       <c r="C106" s="6" t="s">
         <v>259</v>
       </c>
-      <c r="D106" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E106" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F106" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G106" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H106" s="3" t="e">
-        <v>#N/A</v>
+      <c r="D106" s="15" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E106" s="15" t="s">
+        <v>2738</v>
+      </c>
+      <c r="F106" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G106" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H106" s="13" t="s">
+        <v>2739</v>
       </c>
       <c r="I106" t="e">
         <v>#N/A</v>
@@ -11901,7 +12639,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="107" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:11" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A107" s="4" t="s">
         <v>1634</v>
       </c>
@@ -11911,20 +12649,20 @@
       <c r="C107" s="6" t="s">
         <v>260</v>
       </c>
-      <c r="D107" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E107" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F107" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G107" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H107" s="3" t="e">
-        <v>#N/A</v>
+      <c r="D107" s="15" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E107" s="15" t="s">
+        <v>2740</v>
+      </c>
+      <c r="F107" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G107" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H107" s="13" t="s">
+        <v>2741</v>
       </c>
       <c r="I107" t="e">
         <v>#N/A</v>
@@ -11936,7 +12674,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="108" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:11" ht="330.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A108" s="4" t="s">
         <v>1634</v>
       </c>
@@ -11946,20 +12684,20 @@
       <c r="C108" s="6" t="s">
         <v>261</v>
       </c>
-      <c r="D108" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E108" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F108" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G108" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H108" s="3" t="e">
-        <v>#N/A</v>
+      <c r="D108" s="15" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E108" s="15" t="s">
+        <v>2742</v>
+      </c>
+      <c r="F108" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G108" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H108" s="13" t="s">
+        <v>2743</v>
       </c>
       <c r="I108" t="e">
         <v>#N/A</v>
@@ -11971,7 +12709,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="109" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:11" ht="405.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A109" s="4" t="s">
         <v>1634</v>
       </c>
@@ -11981,20 +12719,20 @@
       <c r="C109" s="6" t="s">
         <v>262</v>
       </c>
-      <c r="D109" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E109" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F109" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G109" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H109" s="3" t="e">
-        <v>#N/A</v>
+      <c r="D109" s="15" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E109" s="15" t="s">
+        <v>2744</v>
+      </c>
+      <c r="F109" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G109" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H109" s="13" t="s">
+        <v>2745</v>
       </c>
       <c r="I109" t="e">
         <v>#N/A</v>
@@ -12006,7 +12744,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="110" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:11" ht="195.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A110" s="4" t="s">
         <v>1634</v>
       </c>
@@ -12016,20 +12754,20 @@
       <c r="C110" s="6" t="s">
         <v>263</v>
       </c>
-      <c r="D110" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E110" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F110" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G110" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H110" s="3" t="e">
-        <v>#N/A</v>
+      <c r="D110" s="15" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E110" s="15" t="s">
+        <v>2746</v>
+      </c>
+      <c r="F110" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G110" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H110" s="13" t="s">
+        <v>2747</v>
       </c>
       <c r="I110" t="e">
         <v>#N/A</v>
@@ -12041,7 +12779,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="111" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:11" ht="270.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A111" s="4" t="s">
         <v>1634</v>
       </c>
@@ -12051,20 +12789,20 @@
       <c r="C111" s="6" t="s">
         <v>264</v>
       </c>
-      <c r="D111" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E111" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F111" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G111" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H111" s="3" t="e">
-        <v>#N/A</v>
+      <c r="D111" s="15" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E111" s="15" t="s">
+        <v>2748</v>
+      </c>
+      <c r="F111" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G111" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H111" s="13" t="s">
+        <v>2749</v>
       </c>
       <c r="I111" t="e">
         <v>#N/A</v>
@@ -12076,7 +12814,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="112" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:11" ht="180.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A112" s="4" t="s">
         <v>1634</v>
       </c>
@@ -12086,20 +12824,20 @@
       <c r="C112" s="6" t="s">
         <v>265</v>
       </c>
-      <c r="D112" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E112" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F112" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G112" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H112" s="3" t="e">
-        <v>#N/A</v>
+      <c r="D112" s="15" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E112" s="15" t="s">
+        <v>2750</v>
+      </c>
+      <c r="F112" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G112" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H112" s="13" t="s">
+        <v>2751</v>
       </c>
       <c r="I112" t="e">
         <v>#N/A</v>
@@ -12111,7 +12849,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="113" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:11" ht="240.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A113" s="4" t="s">
         <v>1634</v>
       </c>
@@ -12121,20 +12859,20 @@
       <c r="C113" s="6" t="s">
         <v>266</v>
       </c>
-      <c r="D113" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E113" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F113" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G113" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H113" s="3" t="e">
-        <v>#N/A</v>
+      <c r="D113" s="15" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E113" s="15" t="s">
+        <v>2752</v>
+      </c>
+      <c r="F113" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G113" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H113" s="13" t="s">
+        <v>2753</v>
       </c>
       <c r="I113" t="e">
         <v>#N/A</v>
@@ -12146,7 +12884,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="114" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:11" ht="150.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A114" s="4" t="s">
         <v>1634</v>
       </c>
@@ -12156,20 +12894,20 @@
       <c r="C114" s="6" t="s">
         <v>267</v>
       </c>
-      <c r="D114" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E114" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F114" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G114" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H114" s="3" t="e">
-        <v>#N/A</v>
+      <c r="D114" s="15" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E114" s="15" t="s">
+        <v>2754</v>
+      </c>
+      <c r="F114" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G114" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H114" s="13" t="s">
+        <v>2755</v>
       </c>
       <c r="I114" t="e">
         <v>#N/A</v>
@@ -12181,7 +12919,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="115" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:11" ht="240.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A115" s="4" t="s">
         <v>1634</v>
       </c>
@@ -12191,20 +12929,20 @@
       <c r="C115" s="6" t="s">
         <v>264</v>
       </c>
-      <c r="D115" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E115" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F115" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G115" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H115" s="3" t="e">
-        <v>#N/A</v>
+      <c r="D115" s="15" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E115" s="15" t="s">
+        <v>2756</v>
+      </c>
+      <c r="F115" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G115" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H115" s="13" t="s">
+        <v>2757</v>
       </c>
       <c r="I115" t="e">
         <v>#N/A</v>
@@ -12216,7 +12954,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="116" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:11" ht="120.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A116" s="4" t="s">
         <v>1634</v>
       </c>
@@ -12226,20 +12964,20 @@
       <c r="C116" s="6" t="s">
         <v>268</v>
       </c>
-      <c r="D116" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E116" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F116" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G116" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H116" s="3" t="e">
-        <v>#N/A</v>
+      <c r="D116" s="15" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E116" s="15" t="s">
+        <v>2758</v>
+      </c>
+      <c r="F116" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G116" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H116" s="13" t="s">
+        <v>2759</v>
       </c>
       <c r="I116" t="e">
         <v>#N/A</v>
@@ -12251,7 +12989,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="117" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:11" ht="240.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A117" s="4" t="s">
         <v>1634</v>
       </c>
@@ -12261,20 +12999,20 @@
       <c r="C117" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="D117" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E117" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F117" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G117" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H117" s="3" t="e">
-        <v>#N/A</v>
+      <c r="D117" s="15" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E117" s="15" t="s">
+        <v>2760</v>
+      </c>
+      <c r="F117" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G117" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H117" s="13" t="s">
+        <v>2761</v>
       </c>
       <c r="I117" t="e">
         <v>#N/A</v>
@@ -12286,7 +13024,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="118" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:11" ht="150.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A118" s="4" t="s">
         <v>1634</v>
       </c>
@@ -12296,20 +13034,20 @@
       <c r="C118" s="6" t="s">
         <v>270</v>
       </c>
-      <c r="D118" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E118" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F118" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G118" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H118" s="3" t="e">
-        <v>#N/A</v>
+      <c r="D118" s="15" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E118" s="15" t="s">
+        <v>2754</v>
+      </c>
+      <c r="F118" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G118" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H118" s="13" t="s">
+        <v>2755</v>
       </c>
       <c r="I118" t="e">
         <v>#N/A</v>
@@ -12321,7 +13059,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="119" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:11" ht="210.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A119" s="4" t="s">
         <v>1634</v>
       </c>
@@ -12331,20 +13069,20 @@
       <c r="C119" s="6" t="s">
         <v>264</v>
       </c>
-      <c r="D119" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E119" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F119" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G119" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H119" s="3" t="e">
-        <v>#N/A</v>
+      <c r="D119" s="15" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E119" s="15" t="s">
+        <v>2756</v>
+      </c>
+      <c r="F119" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G119" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H119" s="13" t="s">
+        <v>2762</v>
       </c>
       <c r="I119" t="e">
         <v>#N/A</v>
@@ -12356,7 +13094,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="120" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:11" ht="150.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A120" s="4" t="s">
         <v>1634</v>
       </c>
@@ -12366,20 +13104,20 @@
       <c r="C120" s="6" t="s">
         <v>271</v>
       </c>
-      <c r="D120" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E120" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F120" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G120" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H120" s="3" t="e">
-        <v>#N/A</v>
+      <c r="D120" s="15" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E120" s="15" t="s">
+        <v>2758</v>
+      </c>
+      <c r="F120" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G120" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H120" s="13" t="s">
+        <v>2763</v>
       </c>
       <c r="I120" t="e">
         <v>#N/A</v>
@@ -12391,7 +13129,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="121" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:11" ht="210.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A121" s="4" t="s">
         <v>1634</v>
       </c>
@@ -12401,20 +13139,20 @@
       <c r="C121" s="6" t="s">
         <v>272</v>
       </c>
-      <c r="D121" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E121" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F121" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G121" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H121" s="3" t="e">
-        <v>#N/A</v>
+      <c r="D121" s="15" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E121" s="15" t="s">
+        <v>2760</v>
+      </c>
+      <c r="F121" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G121" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H121" s="13" t="s">
+        <v>2764</v>
       </c>
       <c r="I121" t="e">
         <v>#N/A</v>
@@ -12426,7 +13164,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="122" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:11" ht="120.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A122" s="4" t="s">
         <v>1634</v>
       </c>
@@ -12436,20 +13174,20 @@
       <c r="C122" s="6" t="s">
         <v>273</v>
       </c>
-      <c r="D122" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E122" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F122" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G122" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H122" s="3" t="e">
-        <v>#N/A</v>
+      <c r="D122" s="15" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E122" s="15" t="s">
+        <v>2765</v>
+      </c>
+      <c r="F122" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G122" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H122" s="13" t="s">
+        <v>2766</v>
       </c>
       <c r="I122" t="e">
         <v>#N/A</v>
@@ -12461,7 +13199,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="123" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:11" ht="315.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A123" s="4" t="s">
         <v>1634</v>
       </c>
@@ -12471,20 +13209,20 @@
       <c r="C123" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="D123" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E123" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F123" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G123" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H123" s="3" t="e">
-        <v>#N/A</v>
+      <c r="D123" s="15" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E123" s="15" t="s">
+        <v>2767</v>
+      </c>
+      <c r="F123" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G123" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H123" s="13" t="s">
+        <v>2768</v>
       </c>
       <c r="I123" t="e">
         <v>#N/A</v>
@@ -20487,10 +21225,10 @@
         <v>497</v>
       </c>
       <c r="D352" s="2" t="s">
-        <v>2484</v>
+        <v>2482</v>
       </c>
       <c r="E352" s="2" t="s">
-        <v>2485</v>
+        <v>2483</v>
       </c>
       <c r="F352" t="s">
         <v>1586</v>
@@ -29377,10 +30115,10 @@
         <v>749</v>
       </c>
       <c r="D606" s="2" t="s">
-        <v>2516</v>
+        <v>2514</v>
       </c>
       <c r="E606" s="2" t="s">
-        <v>2517</v>
+        <v>2515</v>
       </c>
       <c r="F606" t="s">
         <v>1586</v>
@@ -30575,7 +31313,7 @@
         <v>783</v>
       </c>
       <c r="D641" s="2" t="s">
-        <v>2421</v>
+        <v>2419</v>
       </c>
       <c r="E641" s="2" t="s">
         <v>1849</v>
@@ -30735,7 +31473,7 @@
         <v>788</v>
       </c>
       <c r="D646" s="2" t="s">
-        <v>2489</v>
+        <v>2487</v>
       </c>
       <c r="E646" s="2" t="s">
         <v>1877</v>
@@ -30770,7 +31508,7 @@
         <v>789</v>
       </c>
       <c r="D647" s="2" t="s">
-        <v>2422</v>
+        <v>2420</v>
       </c>
       <c r="E647" s="2" t="s">
         <v>1882</v>
@@ -31014,7 +31752,7 @@
       <c r="C654" s="6" t="s">
         <v>791</v>
       </c>
-      <c r="D654" s="15" t="s">
+      <c r="D654" s="11" t="s">
         <v>2281</v>
       </c>
       <c r="E654" s="2" t="s">
@@ -31189,7 +31927,7 @@
       <c r="C659" s="2" t="s">
         <v>2286</v>
       </c>
-      <c r="D659" s="16" t="s">
+      <c r="D659" s="12" t="s">
         <v>2287</v>
       </c>
       <c r="E659" s="2" t="s">
@@ -31224,7 +31962,7 @@
       <c r="C660" s="6" t="s">
         <v>793</v>
       </c>
-      <c r="D660" s="16" t="s">
+      <c r="D660" s="12" t="s">
         <v>2288</v>
       </c>
       <c r="E660" s="2" t="s">
@@ -31329,7 +32067,7 @@
       <c r="C663" s="6" t="s">
         <v>794</v>
       </c>
-      <c r="D663" s="16" t="s">
+      <c r="D663" s="12" t="s">
         <v>2289</v>
       </c>
       <c r="E663" s="2" t="s">
@@ -31364,7 +32102,7 @@
       <c r="C664" s="6" t="s">
         <v>795</v>
       </c>
-      <c r="D664" s="16" t="s">
+      <c r="D664" s="12" t="s">
         <v>2290</v>
       </c>
       <c r="E664" s="2" t="s">
@@ -31399,7 +32137,7 @@
       <c r="C665" s="6" t="s">
         <v>796</v>
       </c>
-      <c r="D665" s="16" t="s">
+      <c r="D665" s="12" t="s">
         <v>2291</v>
       </c>
       <c r="E665" s="2" t="s">
@@ -31434,7 +32172,7 @@
       <c r="C666" s="6" t="s">
         <v>797</v>
       </c>
-      <c r="D666" s="16" t="s">
+      <c r="D666" s="12" t="s">
         <v>2292</v>
       </c>
       <c r="E666" s="2" t="s">
@@ -36860,10 +37598,10 @@
         <v>2360</v>
       </c>
       <c r="D821" s="2" t="s">
-        <v>2468</v>
+        <v>2466</v>
       </c>
       <c r="E821" s="2" t="s">
-        <v>2465</v>
+        <v>2463</v>
       </c>
       <c r="F821" t="s">
         <v>1586</v>
@@ -36895,10 +37633,10 @@
         <v>2328</v>
       </c>
       <c r="D822" s="2" t="s">
-        <v>2467</v>
+        <v>2465</v>
       </c>
       <c r="E822" s="2" t="s">
-        <v>2466</v>
+        <v>2464</v>
       </c>
       <c r="F822" t="s">
         <v>1586</v>
@@ -37595,10 +38333,10 @@
         <v>966</v>
       </c>
       <c r="D842" s="2" t="s">
-        <v>2471</v>
+        <v>2469</v>
       </c>
       <c r="E842" s="2" t="s">
-        <v>2470</v>
+        <v>2468</v>
       </c>
       <c r="F842" t="s">
         <v>105</v>
@@ -37630,10 +38368,10 @@
         <v>967</v>
       </c>
       <c r="D843" s="2" t="s">
-        <v>2473</v>
+        <v>2471</v>
       </c>
       <c r="E843" s="2" t="s">
-        <v>2472</v>
+        <v>2470</v>
       </c>
       <c r="F843" t="s">
         <v>1586</v>
@@ -37700,10 +38438,10 @@
         <v>969</v>
       </c>
       <c r="D845" s="2" t="s">
-        <v>2475</v>
+        <v>2473</v>
       </c>
       <c r="E845" s="2" t="s">
-        <v>2474</v>
+        <v>2472</v>
       </c>
       <c r="F845" t="s">
         <v>1586</v>
@@ -37735,10 +38473,10 @@
         <v>970</v>
       </c>
       <c r="D846" s="2" t="s">
-        <v>2476</v>
+        <v>2474</v>
       </c>
       <c r="E846" s="2" t="s">
-        <v>2477</v>
+        <v>2475</v>
       </c>
       <c r="F846" t="s">
         <v>1586</v>
@@ -37944,14 +38682,14 @@
       <c r="C852" s="6" t="s">
         <v>976</v>
       </c>
-      <c r="D852" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E852" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F852" t="e">
-        <v>#N/A</v>
+      <c r="D852" s="2" t="s">
+        <v>2543</v>
+      </c>
+      <c r="E852" s="2" t="s">
+        <v>2544</v>
+      </c>
+      <c r="F852" t="s">
+        <v>1586</v>
       </c>
       <c r="G852" t="e">
         <v>#N/A</v>
@@ -38333,7 +39071,7 @@
         <v>2355</v>
       </c>
       <c r="E863" s="2" t="s">
-        <v>2525</v>
+        <v>2523</v>
       </c>
       <c r="F863" t="s">
         <v>1586</v>
@@ -38645,10 +39383,10 @@
         <v>996</v>
       </c>
       <c r="D872" s="2" t="s">
+        <v>2528</v>
+      </c>
+      <c r="E872" s="2" t="s">
         <v>2531</v>
-      </c>
-      <c r="E872" s="2" t="s">
-        <v>2534</v>
       </c>
       <c r="F872" t="s">
         <v>1586</v>
@@ -38680,10 +39418,10 @@
         <v>997</v>
       </c>
       <c r="D873" s="2" t="s">
-        <v>2537</v>
+        <v>2539</v>
       </c>
       <c r="E873" s="2" t="s">
-        <v>2538</v>
+        <v>2534</v>
       </c>
       <c r="F873" t="s">
         <v>1586</v>
@@ -38715,10 +39453,10 @@
         <v>998</v>
       </c>
       <c r="D874" s="2" t="s">
-        <v>2536</v>
+        <v>2533</v>
       </c>
       <c r="E874" s="2" t="s">
-        <v>2535</v>
+        <v>2532</v>
       </c>
       <c r="F874" t="s">
         <v>1586</v>
@@ -38747,16 +39485,16 @@
         <v>47714</v>
       </c>
       <c r="C875" s="6" t="s">
-        <v>2540</v>
+        <v>2536</v>
       </c>
       <c r="D875" s="2" t="s">
-        <v>2542</v>
+        <v>2538</v>
       </c>
       <c r="E875" s="2" t="s">
-        <v>2541</v>
-      </c>
-      <c r="F875" t="e">
-        <v>#N/A</v>
+        <v>2537</v>
+      </c>
+      <c r="F875" t="s">
+        <v>1586</v>
       </c>
       <c r="G875" t="e">
         <v>#N/A</v>
@@ -38893,7 +39631,7 @@
         <v>2356</v>
       </c>
       <c r="E879" s="2" t="s">
-        <v>2526</v>
+        <v>2540</v>
       </c>
       <c r="F879" t="s">
         <v>1586</v>
@@ -39170,10 +39908,10 @@
         <v>1010</v>
       </c>
       <c r="D887" s="2" t="s">
-        <v>2539</v>
-      </c>
-      <c r="E887" s="2" t="e">
-        <v>#N/A</v>
+        <v>2535</v>
+      </c>
+      <c r="E887" s="2" t="s">
+        <v>2545</v>
       </c>
       <c r="F887" t="s">
         <v>1586</v>
@@ -39194,7 +39932,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="888" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="888" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A888" s="4" t="s">
         <v>1978</v>
       </c>
@@ -39204,14 +39942,14 @@
       <c r="C888" s="6" t="s">
         <v>1011</v>
       </c>
-      <c r="D888" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E888" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F888" t="e">
-        <v>#N/A</v>
+      <c r="D888" s="2" t="s">
+        <v>2546</v>
+      </c>
+      <c r="E888" s="2" t="s">
+        <v>2547</v>
+      </c>
+      <c r="F888" t="s">
+        <v>1586</v>
       </c>
       <c r="G888" t="e">
         <v>#N/A</v>
@@ -39239,14 +39977,14 @@
       <c r="C889" s="6" t="s">
         <v>1012</v>
       </c>
-      <c r="D889" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E889" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F889" t="e">
-        <v>#N/A</v>
+      <c r="D889" s="2" t="s">
+        <v>2542</v>
+      </c>
+      <c r="E889" s="2" t="s">
+        <v>2541</v>
+      </c>
+      <c r="F889" t="s">
+        <v>1586</v>
       </c>
       <c r="G889" t="e">
         <v>#N/A</v>
@@ -39870,7 +40608,7 @@
         <v>1030</v>
       </c>
       <c r="D907" s="2" t="s">
-        <v>2469</v>
+        <v>2467</v>
       </c>
       <c r="E907" s="2" t="s">
         <v>2333</v>
@@ -40007,13 +40745,13 @@
         <v>47781</v>
       </c>
       <c r="C911" s="6" t="s">
+        <v>2479</v>
+      </c>
+      <c r="D911" s="2" t="s">
+        <v>2480</v>
+      </c>
+      <c r="E911" s="2" t="s">
         <v>2481</v>
-      </c>
-      <c r="D911" s="2" t="s">
-        <v>2482</v>
-      </c>
-      <c r="E911" s="2" t="s">
-        <v>2483</v>
       </c>
       <c r="F911" t="s">
         <v>1586</v>
@@ -40535,10 +41273,10 @@
         <v>1048</v>
       </c>
       <c r="D926" s="2" t="s">
-        <v>2490</v>
+        <v>2488</v>
       </c>
       <c r="E926" s="2" t="s">
-        <v>2491</v>
+        <v>2489</v>
       </c>
       <c r="F926" t="s">
         <v>1586</v>
@@ -40570,10 +41308,10 @@
         <v>1049</v>
       </c>
       <c r="D927" s="2" t="s">
-        <v>2500</v>
+        <v>2498</v>
       </c>
       <c r="E927" s="2" t="s">
-        <v>2501</v>
+        <v>2499</v>
       </c>
       <c r="F927" t="s">
         <v>1586</v>
@@ -41305,10 +42043,10 @@
         <v>1070</v>
       </c>
       <c r="D948" s="2" t="s">
-        <v>2496</v>
+        <v>2494</v>
       </c>
       <c r="E948" s="2" t="s">
-        <v>2504</v>
+        <v>2502</v>
       </c>
       <c r="F948" t="s">
         <v>1586</v>
@@ -41340,10 +42078,10 @@
         <v>1071</v>
       </c>
       <c r="D949" s="2" t="s">
-        <v>2497</v>
+        <v>2495</v>
       </c>
       <c r="E949" s="2" t="s">
-        <v>2498</v>
+        <v>2496</v>
       </c>
       <c r="F949" t="s">
         <v>1586</v>
@@ -41442,7 +42180,7 @@
         <v>50111</v>
       </c>
       <c r="C952" s="6" t="s">
-        <v>2505</v>
+        <v>2503</v>
       </c>
       <c r="D952" s="2" t="e">
         <v>#N/A</v>
@@ -41547,7 +42285,7 @@
         <v>50114</v>
       </c>
       <c r="C955" s="6" t="s">
-        <v>2506</v>
+        <v>2504</v>
       </c>
       <c r="D955" s="2" t="e">
         <v>#N/A</v>
@@ -41862,7 +42600,7 @@
         <v>50131</v>
       </c>
       <c r="C964" s="6" t="s">
-        <v>2507</v>
+        <v>2505</v>
       </c>
       <c r="D964" s="2" t="e">
         <v>#N/A</v>
@@ -41932,7 +42670,7 @@
         <v>50133</v>
       </c>
       <c r="C966" s="6" t="s">
-        <v>2508</v>
+        <v>2506</v>
       </c>
       <c r="D966" s="2" t="e">
         <v>#N/A</v>
@@ -41967,7 +42705,7 @@
         <v>50134</v>
       </c>
       <c r="C967" s="6" t="s">
-        <v>2509</v>
+        <v>2507</v>
       </c>
       <c r="D967" s="2" t="e">
         <v>#N/A</v>
@@ -42107,7 +42845,7 @@
         <v>50142</v>
       </c>
       <c r="C971" s="6" t="s">
-        <v>2510</v>
+        <v>2508</v>
       </c>
       <c r="D971" s="2" t="e">
         <v>#N/A</v>
@@ -42142,7 +42880,7 @@
         <v>50143</v>
       </c>
       <c r="C972" s="6" t="s">
-        <v>2511</v>
+        <v>2509</v>
       </c>
       <c r="D972" s="2" t="e">
         <v>#N/A</v>
@@ -42177,7 +42915,7 @@
         <v>50144</v>
       </c>
       <c r="C973" s="6" t="s">
-        <v>2512</v>
+        <v>2510</v>
       </c>
       <c r="D973" s="2" t="e">
         <v>#N/A</v>
@@ -42212,7 +42950,7 @@
         <v>50145</v>
       </c>
       <c r="C974" s="6" t="s">
-        <v>2513</v>
+        <v>2511</v>
       </c>
       <c r="D974" s="2" t="e">
         <v>#N/A</v>
@@ -42282,7 +43020,7 @@
         <v>50211</v>
       </c>
       <c r="C976" s="6" t="s">
-        <v>2514</v>
+        <v>2512</v>
       </c>
       <c r="D976" s="2" t="e">
         <v>#N/A</v>
@@ -42317,7 +43055,7 @@
         <v>50212</v>
       </c>
       <c r="C977" s="6" t="s">
-        <v>2515</v>
+        <v>2513</v>
       </c>
       <c r="D977" s="2" t="e">
         <v>#N/A</v>
@@ -44105,10 +44843,10 @@
         <v>15</v>
       </c>
       <c r="D1028" s="2" t="s">
-        <v>2499</v>
+        <v>2497</v>
       </c>
       <c r="E1028" s="2" t="s">
-        <v>2527</v>
+        <v>2524</v>
       </c>
       <c r="F1028" t="s">
         <v>1586</v>
@@ -44411,7 +45149,7 @@
         <v>118</v>
       </c>
       <c r="E1037" s="2" t="s">
-        <v>2418</v>
+        <v>2416</v>
       </c>
       <c r="F1037" t="s">
         <v>105</v>
@@ -44667,10 +45405,10 @@
         <v>1147</v>
       </c>
       <c r="D1045" s="2" t="s">
-        <v>2522</v>
+        <v>2520</v>
       </c>
       <c r="E1045" s="2" t="s">
-        <v>2419</v>
+        <v>2417</v>
       </c>
       <c r="F1045" t="s">
         <v>1586</v>
@@ -44699,7 +45437,7 @@
         <v>1148</v>
       </c>
       <c r="D1046" s="2" t="s">
-        <v>2532</v>
+        <v>2529</v>
       </c>
       <c r="E1046" s="2" t="s">
         <v>2351</v>
@@ -44731,7 +45469,7 @@
         <v>1149</v>
       </c>
       <c r="D1047" s="2" t="s">
-        <v>2533</v>
+        <v>2530</v>
       </c>
       <c r="E1047" s="2" t="s">
         <v>2352</v>
@@ -44801,10 +45539,10 @@
         <v>1151</v>
       </c>
       <c r="D1049" s="2" t="s">
-        <v>2502</v>
+        <v>2500</v>
       </c>
       <c r="E1049" s="2" t="s">
-        <v>2503</v>
+        <v>2501</v>
       </c>
       <c r="F1049" t="s">
         <v>1586</v>
@@ -45186,10 +45924,10 @@
         <v>1161</v>
       </c>
       <c r="D1060" s="2" t="s">
-        <v>2519</v>
+        <v>2517</v>
       </c>
       <c r="E1060" s="2" t="s">
-        <v>2518</v>
+        <v>2516</v>
       </c>
       <c r="F1060" t="s">
         <v>1825</v>
@@ -45198,7 +45936,7 @@
         <v>2078</v>
       </c>
       <c r="H1060" s="3" t="s">
-        <v>2478</v>
+        <v>2476</v>
       </c>
       <c r="I1060" t="s">
         <v>2081</v>
@@ -45361,10 +46099,10 @@
         <v>2094</v>
       </c>
       <c r="D1065" s="2" t="s">
-        <v>2520</v>
+        <v>2518</v>
       </c>
       <c r="E1065" s="2" t="s">
-        <v>2521</v>
+        <v>2519</v>
       </c>
       <c r="F1065" t="s">
         <v>1586</v>
@@ -45606,7 +46344,7 @@
         <v>1165</v>
       </c>
       <c r="D1072" s="2" t="s">
-        <v>2480</v>
+        <v>2478</v>
       </c>
       <c r="E1072" s="2" t="s">
         <v>2027</v>
@@ -45933,7 +46671,7 @@
         <v>2078</v>
       </c>
       <c r="H1081" s="3" t="s">
-        <v>2479</v>
+        <v>2477</v>
       </c>
       <c r="I1081" t="s">
         <v>2141</v>
@@ -46271,10 +47009,10 @@
         <v>2158</v>
       </c>
       <c r="D1091" s="2" t="s">
-        <v>2487</v>
+        <v>2485</v>
       </c>
       <c r="E1091" s="2" t="s">
-        <v>2488</v>
+        <v>2486</v>
       </c>
       <c r="F1091" t="s">
         <v>1586</v>
@@ -47356,7 +48094,7 @@
       <c r="D1122" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="E1122" s="21" t="s">
+      <c r="E1122" s="16" t="s">
         <v>2323</v>
       </c>
       <c r="F1122" t="e">
@@ -47774,7 +48512,7 @@
         <v>1214</v>
       </c>
       <c r="D1134" s="2" t="s">
-        <v>2423</v>
+        <v>2421</v>
       </c>
       <c r="E1134" s="2" t="s">
         <v>2326</v>
@@ -47882,7 +48620,7 @@
         <v>2321</v>
       </c>
       <c r="E1137" s="2" t="s">
-        <v>2528</v>
+        <v>2525</v>
       </c>
       <c r="F1137" t="s">
         <v>1586</v>
@@ -48019,7 +48757,7 @@
         <v>1221</v>
       </c>
       <c r="D1141" s="2" t="s">
-        <v>2492</v>
+        <v>2490</v>
       </c>
       <c r="E1141" s="2" t="e">
         <v>#N/A</v>
@@ -50049,7 +50787,7 @@
         <v>1278</v>
       </c>
       <c r="D1199" s="2" t="s">
-        <v>2486</v>
+        <v>2484</v>
       </c>
       <c r="E1199" s="2" t="s">
         <v>2315</v>
@@ -50609,10 +51347,10 @@
         <v>1294</v>
       </c>
       <c r="D1215" s="2" t="s">
-        <v>2415</v>
+        <v>2413</v>
       </c>
       <c r="E1215" s="2" t="s">
-        <v>2414</v>
+        <v>2412</v>
       </c>
       <c r="F1215" t="s">
         <v>1586</v>
@@ -50641,13 +51379,13 @@
         <v>68112</v>
       </c>
       <c r="C1216" s="6" t="s">
-        <v>2416</v>
+        <v>2414</v>
       </c>
       <c r="D1216" s="2" t="s">
-        <v>2417</v>
+        <v>2415</v>
       </c>
       <c r="E1216" s="2" t="s">
-        <v>2420</v>
+        <v>2418</v>
       </c>
       <c r="F1216" t="s">
         <v>1586</v>
@@ -56092,7 +56830,7 @@
       <c r="A1372" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B1372" s="12">
+      <c r="B1372" s="10">
         <v>85101</v>
       </c>
       <c r="C1372" s="6" t="s">
@@ -56127,7 +56865,7 @@
       <c r="A1373" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B1373" s="12">
+      <c r="B1373" s="10">
         <v>85102</v>
       </c>
       <c r="C1373" s="6" t="s">
@@ -56162,7 +56900,7 @@
       <c r="A1374" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B1374" s="12">
+      <c r="B1374" s="10">
         <v>85103</v>
       </c>
       <c r="C1374" s="6" t="s">
@@ -56197,7 +56935,7 @@
       <c r="A1375" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B1375" s="12">
+      <c r="B1375" s="10">
         <v>85104</v>
       </c>
       <c r="C1375" s="6" t="s">
@@ -57149,7 +57887,7 @@
         <v>69</v>
       </c>
       <c r="D1402" s="2" t="s">
-        <v>2524</v>
+        <v>2522</v>
       </c>
       <c r="E1402" s="2" t="e">
         <v>#N/A</v>
@@ -57989,7 +58727,7 @@
         <v>78</v>
       </c>
       <c r="D1426" s="2" t="s">
-        <v>2523</v>
+        <v>2521</v>
       </c>
       <c r="E1426" s="2" t="e">
         <v>#N/A</v>
@@ -58759,7 +59497,7 @@
         <v>89</v>
       </c>
       <c r="D1448" s="2" t="s">
-        <v>2424</v>
+        <v>2422</v>
       </c>
       <c r="E1448" s="2" t="e">
         <v>#N/A</v>
@@ -59389,10 +60127,10 @@
         <v>90</v>
       </c>
       <c r="D1466" s="2" t="s">
-        <v>2437</v>
+        <v>2435</v>
       </c>
       <c r="E1466" s="2" t="s">
-        <v>2438</v>
+        <v>2436</v>
       </c>
       <c r="F1466" t="s">
         <v>105</v>
@@ -59692,7 +60430,7 @@
         <v>97</v>
       </c>
       <c r="D1475" s="2" t="s">
-        <v>2425</v>
+        <v>2423</v>
       </c>
       <c r="E1475" s="2" t="e">
         <v>#N/A</v>
@@ -59724,10 +60462,10 @@
         <v>98</v>
       </c>
       <c r="D1476" s="2" t="s">
-        <v>2529</v>
+        <v>2526</v>
       </c>
       <c r="E1476" s="2" t="s">
-        <v>2530</v>
+        <v>2527</v>
       </c>
       <c r="F1476" t="s">
         <v>1586</v>
@@ -61019,7 +61757,7 @@
         <v>1525</v>
       </c>
       <c r="D1513" s="2" t="s">
-        <v>2494</v>
+        <v>2492</v>
       </c>
       <c r="E1513" s="2" t="e">
         <v>#N/A</v>
@@ -61264,7 +62002,7 @@
         <v>1532</v>
       </c>
       <c r="D1520" s="2" t="s">
-        <v>2493</v>
+        <v>2491</v>
       </c>
       <c r="E1520" s="2" t="e">
         <v>#N/A</v>
@@ -61649,10 +62387,10 @@
         <v>1543</v>
       </c>
       <c r="D1531" s="2" t="s">
-        <v>2426</v>
+        <v>2424</v>
       </c>
       <c r="E1531" s="2" t="s">
-        <v>2431</v>
+        <v>2429</v>
       </c>
       <c r="F1531" t="s">
         <v>105</v>
@@ -61681,10 +62419,10 @@
         <v>1544</v>
       </c>
       <c r="D1532" s="2" t="s">
-        <v>2433</v>
+        <v>2431</v>
       </c>
       <c r="E1532" s="2" t="s">
-        <v>2432</v>
+        <v>2430</v>
       </c>
       <c r="F1532" t="s">
         <v>105</v>
@@ -61692,7 +62430,7 @@
       <c r="G1532">
         <v>0</v>
       </c>
-      <c r="H1532" s="2" t="s">
+      <c r="H1532" s="3" t="s">
         <v>1626</v>
       </c>
       <c r="K1532"/>
@@ -61708,7 +62446,7 @@
         <v>1545</v>
       </c>
       <c r="D1533" s="2" t="s">
-        <v>2434</v>
+        <v>2432</v>
       </c>
       <c r="E1533" s="2"/>
       <c r="F1533" t="s">
@@ -61727,10 +62465,10 @@
         <v>1546</v>
       </c>
       <c r="D1534" s="2" t="s">
-        <v>2440</v>
+        <v>2438</v>
       </c>
       <c r="E1534" s="2" t="s">
-        <v>2435</v>
+        <v>2433</v>
       </c>
       <c r="F1534" t="s">
         <v>105</v>
@@ -61748,10 +62486,10 @@
         <v>1547</v>
       </c>
       <c r="D1535" s="2" t="s">
-        <v>2439</v>
+        <v>2437</v>
       </c>
       <c r="E1535" s="2" t="s">
-        <v>2436</v>
+        <v>2434</v>
       </c>
       <c r="F1535" t="s">
         <v>105</v>
@@ -61769,7 +62507,7 @@
         <v>1548</v>
       </c>
       <c r="D1536" s="2" t="s">
-        <v>2427</v>
+        <v>2425</v>
       </c>
       <c r="E1536" s="2" t="s">
         <v>1627</v>
@@ -61780,7 +62518,7 @@
       <c r="G1536">
         <v>0</v>
       </c>
-      <c r="H1536" s="2" t="s">
+      <c r="H1536" s="3" t="s">
         <v>2224</v>
       </c>
       <c r="I1536" s="2" t="s">
@@ -61802,16 +62540,16 @@
         <v>1549</v>
       </c>
       <c r="D1537" s="2" t="s">
-        <v>2441</v>
+        <v>2439</v>
       </c>
       <c r="E1537" s="2" t="s">
-        <v>2442</v>
+        <v>2440</v>
       </c>
       <c r="F1537" s="2" t="s">
         <v>1586</v>
       </c>
       <c r="G1537" s="2"/>
-      <c r="H1537" s="2" t="s">
+      <c r="H1537" s="3" t="s">
         <v>2227</v>
       </c>
       <c r="I1537" s="2" t="s">
@@ -61833,10 +62571,10 @@
         <v>1550</v>
       </c>
       <c r="D1538" s="2" t="s">
-        <v>2444</v>
+        <v>2442</v>
       </c>
       <c r="E1538" s="2" t="s">
-        <v>2445</v>
+        <v>2443</v>
       </c>
       <c r="F1538" t="s">
         <v>1586</v>
@@ -61844,8 +62582,8 @@
       <c r="G1538" t="s">
         <v>2230</v>
       </c>
-      <c r="H1538" s="2" t="s">
-        <v>2443</v>
+      <c r="H1538" s="3" t="s">
+        <v>2441</v>
       </c>
       <c r="I1538" s="2" t="s">
         <v>2231</v>
@@ -61869,12 +62607,11 @@
         <v>2233</v>
       </c>
       <c r="E1539" s="2" t="s">
-        <v>2446</v>
+        <v>2444</v>
       </c>
       <c r="F1539" t="s">
         <v>1586</v>
       </c>
-      <c r="H1539" s="2"/>
       <c r="K1539"/>
     </row>
     <row r="1540" spans="1:11" ht="150" x14ac:dyDescent="0.25">
@@ -61888,7 +62625,7 @@
         <v>1552</v>
       </c>
       <c r="D1540" s="2" t="s">
-        <v>2447</v>
+        <v>2445</v>
       </c>
       <c r="E1540" s="2" t="s">
         <v>2234</v>
@@ -61896,7 +62633,7 @@
       <c r="F1540" t="s">
         <v>1586</v>
       </c>
-      <c r="H1540" s="2" t="s">
+      <c r="H1540" s="3" t="s">
         <v>2235</v>
       </c>
       <c r="I1540" s="2" t="s">
@@ -61921,12 +62658,12 @@
         <v>2238</v>
       </c>
       <c r="E1541" s="2" t="s">
-        <v>2448</v>
+        <v>2446</v>
       </c>
       <c r="F1541" t="s">
         <v>1586</v>
       </c>
-      <c r="H1541" s="2" t="s">
+      <c r="H1541" s="3" t="s">
         <v>2027</v>
       </c>
       <c r="I1541" s="2" t="s">
@@ -61951,12 +62688,12 @@
         <v>2240</v>
       </c>
       <c r="E1542" s="2" t="s">
-        <v>2449</v>
+        <v>2447</v>
       </c>
       <c r="F1542" t="s">
         <v>1586</v>
       </c>
-      <c r="H1542" s="2" t="s">
+      <c r="H1542" s="3" t="s">
         <v>2027</v>
       </c>
       <c r="I1542" s="2" t="s">
@@ -61978,10 +62715,10 @@
         <v>1554</v>
       </c>
       <c r="D1543" s="2" t="s">
-        <v>2450</v>
+        <v>2448</v>
       </c>
       <c r="E1543" s="2" t="s">
-        <v>2451</v>
+        <v>2449</v>
       </c>
       <c r="F1543" t="s">
         <v>1586</v>
@@ -61989,7 +62726,7 @@
       <c r="G1543">
         <v>0</v>
       </c>
-      <c r="H1543" s="2" t="s">
+      <c r="H1543" s="3" t="s">
         <v>2027</v>
       </c>
       <c r="I1543" s="2" t="s">
@@ -62013,7 +62750,7 @@
         <v>1555</v>
       </c>
       <c r="D1544" s="2" t="s">
-        <v>2428</v>
+        <v>2426</v>
       </c>
       <c r="E1544" s="2" t="s">
         <v>1628</v>
@@ -62021,11 +62758,11 @@
       <c r="F1544" t="s">
         <v>1586</v>
       </c>
-      <c r="H1544" s="2" t="s">
+      <c r="H1544" s="3" t="s">
         <v>2244</v>
       </c>
       <c r="I1544" s="2" t="s">
-        <v>2452</v>
+        <v>2450</v>
       </c>
       <c r="J1544" s="2"/>
       <c r="K1544" s="2" t="s">
@@ -62043,10 +62780,10 @@
         <v>2297</v>
       </c>
       <c r="D1545" s="2" t="s">
-        <v>2454</v>
+        <v>2452</v>
       </c>
       <c r="E1545" s="2" t="s">
-        <v>2453</v>
+        <v>2451</v>
       </c>
       <c r="F1545" t="s">
         <v>1586</v>
@@ -62054,7 +62791,7 @@
       <c r="G1545" t="e">
         <v>#N/A</v>
       </c>
-      <c r="H1545" s="2" t="s">
+      <c r="H1545" s="3" t="s">
         <v>2246</v>
       </c>
       <c r="I1545" s="2" t="s">
@@ -62067,7 +62804,7 @@
         <v>2248</v>
       </c>
     </row>
-    <row r="1546" spans="1:11" ht="195" x14ac:dyDescent="0.25">
+    <row r="1546" spans="1:11" ht="150" x14ac:dyDescent="0.25">
       <c r="A1546" s="4" t="s">
         <v>2223</v>
       </c>
@@ -62089,7 +62826,7 @@
       <c r="G1546">
         <v>0</v>
       </c>
-      <c r="H1546" s="2" t="s">
+      <c r="H1546" s="3" t="s">
         <v>2250</v>
       </c>
       <c r="I1546" s="2" t="s">
@@ -62124,7 +62861,7 @@
       <c r="G1547">
         <v>0</v>
       </c>
-      <c r="H1547" s="2" t="s">
+      <c r="H1547" s="3" t="s">
         <v>2254</v>
       </c>
       <c r="I1547" s="2" t="s">
@@ -62159,7 +62896,7 @@
       <c r="G1548">
         <v>0</v>
       </c>
-      <c r="H1548" s="2" t="s">
+      <c r="H1548" s="3" t="s">
         <v>2258</v>
       </c>
       <c r="I1548" s="2" t="s">
@@ -62199,10 +62936,10 @@
         <v>1560</v>
       </c>
       <c r="D1550" s="2" t="s">
-        <v>2456</v>
+        <v>2454</v>
       </c>
       <c r="E1550" s="2" t="s">
-        <v>2455</v>
+        <v>2453</v>
       </c>
       <c r="F1550" s="2" t="s">
         <v>1586</v>
@@ -62220,10 +62957,10 @@
         <v>1561</v>
       </c>
       <c r="D1551" s="2" t="s">
-        <v>2458</v>
+        <v>2456</v>
       </c>
       <c r="E1551" s="2" t="s">
-        <v>2457</v>
+        <v>2455</v>
       </c>
       <c r="F1551" s="2" t="s">
         <v>1586</v>
@@ -62241,10 +62978,10 @@
         <v>1562</v>
       </c>
       <c r="D1552" s="2" t="s">
-        <v>2459</v>
+        <v>2457</v>
       </c>
       <c r="E1552" s="2" t="s">
-        <v>2460</v>
+        <v>2458</v>
       </c>
       <c r="F1552" s="2" t="s">
         <v>1586</v>
@@ -62262,16 +62999,16 @@
         <v>1563</v>
       </c>
       <c r="D1553" s="2" t="s">
-        <v>2429</v>
-      </c>
-      <c r="E1553" s="15" t="s">
-        <v>2461</v>
+        <v>2427</v>
+      </c>
+      <c r="E1553" s="11" t="s">
+        <v>2459</v>
       </c>
       <c r="F1553" t="s">
         <v>1586</v>
       </c>
       <c r="G1553" t="s">
-        <v>2462</v>
+        <v>2460</v>
       </c>
       <c r="K1553"/>
     </row>
@@ -62286,10 +63023,10 @@
         <v>1564</v>
       </c>
       <c r="D1554" s="2" t="s">
-        <v>2463</v>
+        <v>2461</v>
       </c>
       <c r="E1554" s="2" t="s">
-        <v>2430</v>
+        <v>2428</v>
       </c>
       <c r="F1554" s="2" t="s">
         <v>1586</v>
@@ -62323,10 +63060,10 @@
         <v>104</v>
       </c>
       <c r="D1556" s="2" t="s">
-        <v>2495</v>
+        <v>2493</v>
       </c>
       <c r="E1556" s="2" t="s">
-        <v>2464</v>
+        <v>2462</v>
       </c>
       <c r="F1556" s="2" t="s">
         <v>1586</v>
@@ -62334,31 +63071,31 @@
       <c r="K1556"/>
     </row>
     <row r="1557" spans="1:11" ht="45" x14ac:dyDescent="0.25">
-      <c r="A1557" s="22" t="s">
+      <c r="A1557" s="17" t="s">
         <v>2261</v>
       </c>
-      <c r="B1557" s="23">
+      <c r="B1557" s="18">
         <v>97000</v>
       </c>
-      <c r="C1557" s="24" t="s">
+      <c r="C1557" s="19" t="s">
         <v>1566</v>
       </c>
-      <c r="D1557" s="25"/>
-      <c r="E1557" s="25"/>
+      <c r="D1557" s="20"/>
+      <c r="E1557" s="20"/>
       <c r="K1557"/>
     </row>
     <row r="1558" spans="1:11" ht="60" x14ac:dyDescent="0.25">
-      <c r="A1558" s="22" t="s">
+      <c r="A1558" s="17" t="s">
         <v>2261</v>
       </c>
-      <c r="B1558" s="23">
+      <c r="B1558" s="18">
         <v>98100</v>
       </c>
-      <c r="C1558" s="24" t="s">
+      <c r="C1558" s="19" t="s">
         <v>1567</v>
       </c>
-      <c r="D1558" s="25"/>
-      <c r="E1558" s="25" t="s">
+      <c r="D1558" s="20"/>
+      <c r="E1558" s="20" t="s">
         <v>2262</v>
       </c>
       <c r="F1558" t="e">
@@ -62381,17 +63118,17 @@
       </c>
     </row>
     <row r="1559" spans="1:11" ht="45" x14ac:dyDescent="0.25">
-      <c r="A1559" s="22" t="s">
+      <c r="A1559" s="17" t="s">
         <v>2261</v>
       </c>
-      <c r="B1559" s="23">
+      <c r="B1559" s="18">
         <v>98200</v>
       </c>
-      <c r="C1559" s="24" t="s">
+      <c r="C1559" s="19" t="s">
         <v>1568</v>
       </c>
-      <c r="D1559" s="25"/>
-      <c r="E1559" s="25" t="s">
+      <c r="D1559" s="20"/>
+      <c r="E1559" s="20" t="s">
         <v>2267</v>
       </c>
       <c r="F1559" t="e">
@@ -62450,10 +63187,7 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:K1560"/>
-  <hyperlinks>
-    <hyperlink ref="D14" r:id="rId1" display="Riau Pos, Tribun Pekanbaru, Goriau.co, Cakaplah.com"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId2"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/data/kbli_populer_riau2.xlsx
+++ b/data/kbli_populer_riau2.xlsx
@@ -7265,10 +7265,6 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">cabai; cabai besar; cabai rawit; cabai keriting; paprika; capsicum; menanam; membudidayakan; penyemaian; pascapanen; benih 
-</t>
-  </si>
-  <si>
     <t xml:space="preserve">ubi jalar; talas; ganyong; irut; gembili; iles-iles; porang; umbi-umbian; menanam; membudidayakan; pascapanen 
 </t>
   </si>
@@ -8414,6 +8410,10 @@
   </si>
   <si>
     <t>Kegiatan pertanian tanaman semusim lainnya yang belum terklasifikasi di tempat lain, serta kegiatan penanaman untuk menghasilkan benih berupa biji. Mencakup pengolahan lahan, penanaman, pemeliharaan, pemanenan, dan pascapanen sebagai satu kesatuan.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cabe; cabai; cabai besar; cabai rawit; cabai keriting; paprika; capsicum; menanam; membudidayakan; penyemaian; pascapanen; benih;  
+</t>
   </si>
 </sst>
 </file>
@@ -8992,7 +8992,7 @@
         <v>1586</v>
       </c>
       <c r="H2" s="15" t="s">
-        <v>2769</v>
+        <v>2768</v>
       </c>
       <c r="I2" t="e">
         <v>#N/A</v>
@@ -9047,7 +9047,7 @@
         <v>157</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>2548</v>
+        <v>2547</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>2394</v>
@@ -9082,10 +9082,10 @@
         <v>158</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>2549</v>
+        <v>2548</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>2411</v>
+        <v>2410</v>
       </c>
       <c r="F5" s="8" t="s">
         <v>1586</v>
@@ -9117,7 +9117,7 @@
         <v>159</v>
       </c>
       <c r="D6" s="22" t="s">
-        <v>2550</v>
+        <v>2549</v>
       </c>
       <c r="E6" s="13" t="s">
         <v>2395</v>
@@ -9152,7 +9152,7 @@
         <v>160</v>
       </c>
       <c r="D7" s="23" t="s">
-        <v>2551</v>
+        <v>2550</v>
       </c>
       <c r="E7" s="13" t="s">
         <v>2396</v>
@@ -9187,7 +9187,7 @@
         <v>161</v>
       </c>
       <c r="D8" s="22" t="s">
-        <v>2552</v>
+        <v>2551</v>
       </c>
       <c r="E8" s="13" t="s">
         <v>2397</v>
@@ -9222,7 +9222,7 @@
         <v>162</v>
       </c>
       <c r="D9" s="22" t="s">
-        <v>2553</v>
+        <v>2552</v>
       </c>
       <c r="E9" s="13" t="s">
         <v>2398</v>
@@ -9257,7 +9257,7 @@
         <v>163</v>
       </c>
       <c r="D10" s="22" t="s">
-        <v>2554</v>
+        <v>2553</v>
       </c>
       <c r="E10" s="13" t="s">
         <v>2399</v>
@@ -9292,7 +9292,7 @@
         <v>164</v>
       </c>
       <c r="D11" s="22" t="s">
-        <v>2555</v>
+        <v>2554</v>
       </c>
       <c r="E11" s="13" t="s">
         <v>2400</v>
@@ -9327,13 +9327,13 @@
         <v>165</v>
       </c>
       <c r="D12" s="22" t="s">
-        <v>2556</v>
+        <v>2555</v>
       </c>
       <c r="E12" s="15" t="s">
         <v>2401</v>
       </c>
       <c r="F12" s="24" t="s">
-        <v>2582</v>
+        <v>2581</v>
       </c>
       <c r="G12" t="e">
         <v>#N/A</v>
@@ -9362,13 +9362,13 @@
         <v>166</v>
       </c>
       <c r="D13" s="22" t="s">
-        <v>2557</v>
+        <v>2556</v>
       </c>
       <c r="E13" s="15" t="s">
         <v>2402</v>
       </c>
       <c r="F13" s="24" t="s">
-        <v>2582</v>
+        <v>2581</v>
       </c>
       <c r="G13" t="e">
         <v>#N/A</v>
@@ -9397,13 +9397,13 @@
         <v>167</v>
       </c>
       <c r="D14" s="22" t="s">
-        <v>2558</v>
+        <v>2557</v>
       </c>
       <c r="E14" s="15" t="s">
         <v>2403</v>
       </c>
       <c r="F14" s="24" t="s">
-        <v>2582</v>
+        <v>2581</v>
       </c>
       <c r="G14" t="e">
         <v>#N/A</v>
@@ -9432,13 +9432,13 @@
         <v>168</v>
       </c>
       <c r="D15" s="22" t="s">
-        <v>2559</v>
+        <v>2558</v>
       </c>
       <c r="E15" s="15" t="s">
         <v>2404</v>
       </c>
       <c r="F15" s="24" t="s">
-        <v>2582</v>
+        <v>2581</v>
       </c>
       <c r="G15" t="e">
         <v>#N/A</v>
@@ -9467,13 +9467,13 @@
         <v>169</v>
       </c>
       <c r="D16" s="22" t="s">
-        <v>2560</v>
+        <v>2559</v>
       </c>
       <c r="E16" s="15" t="s">
         <v>2405</v>
       </c>
       <c r="F16" s="24" t="s">
-        <v>2561</v>
+        <v>2560</v>
       </c>
       <c r="G16" t="e">
         <v>#N/A</v>
@@ -9502,7 +9502,7 @@
         <v>170</v>
       </c>
       <c r="D17" s="22" t="s">
-        <v>2562</v>
+        <v>2561</v>
       </c>
       <c r="E17" s="15" t="s">
         <v>2406</v>
@@ -9535,7 +9535,7 @@
         <v>171</v>
       </c>
       <c r="D18" s="22" t="s">
-        <v>2563</v>
+        <v>2562</v>
       </c>
       <c r="E18" s="15" t="s">
         <v>2407</v>
@@ -9570,13 +9570,13 @@
         <v>172</v>
       </c>
       <c r="D19" s="22" t="s">
-        <v>2564</v>
+        <v>2563</v>
       </c>
       <c r="E19" s="15" t="s">
-        <v>2408</v>
+        <v>2776</v>
       </c>
       <c r="F19" s="24" t="s">
-        <v>2582</v>
+        <v>2581</v>
       </c>
       <c r="G19" t="e">
         <v>#N/A</v>
@@ -9605,13 +9605,13 @@
         <v>173</v>
       </c>
       <c r="D20" s="22" t="s">
-        <v>2565</v>
+        <v>2564</v>
       </c>
       <c r="E20" s="15" t="s">
-        <v>2409</v>
+        <v>2408</v>
       </c>
       <c r="F20" s="24" t="s">
-        <v>2582</v>
+        <v>2581</v>
       </c>
       <c r="G20" t="e">
         <v>#N/A</v>
@@ -9640,13 +9640,13 @@
         <v>174</v>
       </c>
       <c r="D21" s="22" t="s">
-        <v>2566</v>
+        <v>2565</v>
       </c>
       <c r="E21" s="15" t="s">
-        <v>2410</v>
+        <v>2409</v>
       </c>
       <c r="F21" s="24" t="s">
-        <v>2582</v>
+        <v>2581</v>
       </c>
       <c r="G21" t="e">
         <v>#N/A</v>
@@ -9675,19 +9675,19 @@
         <v>175</v>
       </c>
       <c r="D22" s="22" t="s">
+        <v>2566</v>
+      </c>
+      <c r="E22" s="15" t="s">
         <v>2567</v>
       </c>
-      <c r="E22" s="15" t="s">
+      <c r="F22" s="24" t="s">
         <v>2568</v>
       </c>
-      <c r="F22" s="24" t="s">
-        <v>2569</v>
-      </c>
       <c r="G22" t="e">
         <v>#N/A</v>
       </c>
       <c r="H22" s="13" t="s">
-        <v>2770</v>
+        <v>2769</v>
       </c>
       <c r="I22" t="e">
         <v>#N/A</v>
@@ -9710,11 +9710,11 @@
         <v>176</v>
       </c>
       <c r="D23" s="22" t="s">
+        <v>2569</v>
+      </c>
+      <c r="E23" s="15" t="s">
         <v>2570</v>
       </c>
-      <c r="E23" s="15" t="s">
-        <v>2571</v>
-      </c>
       <c r="F23" s="24" t="e">
         <v>#N/A</v>
       </c>
@@ -9722,7 +9722,7 @@
         <v>#N/A</v>
       </c>
       <c r="H23" s="13" t="s">
-        <v>2771</v>
+        <v>2770</v>
       </c>
       <c r="I23" t="e">
         <v>#N/A</v>
@@ -9745,19 +9745,19 @@
         <v>177</v>
       </c>
       <c r="D24" s="22" t="s">
+        <v>2571</v>
+      </c>
+      <c r="E24" s="15" t="s">
         <v>2572</v>
       </c>
-      <c r="E24" s="15" t="s">
-        <v>2573</v>
-      </c>
       <c r="F24" s="24" t="s">
-        <v>2569</v>
+        <v>2568</v>
       </c>
       <c r="G24" t="e">
         <v>#N/A</v>
       </c>
       <c r="H24" s="13" t="s">
-        <v>2772</v>
+        <v>2771</v>
       </c>
       <c r="I24" t="e">
         <v>#N/A</v>
@@ -9780,11 +9780,11 @@
         <v>178</v>
       </c>
       <c r="D25" s="22" t="s">
+        <v>2573</v>
+      </c>
+      <c r="E25" s="15" t="s">
         <v>2574</v>
       </c>
-      <c r="E25" s="15" t="s">
-        <v>2575</v>
-      </c>
       <c r="F25" s="24" t="e">
         <v>#N/A</v>
       </c>
@@ -9792,7 +9792,7 @@
         <v>#N/A</v>
       </c>
       <c r="H25" s="13" t="s">
-        <v>2773</v>
+        <v>2772</v>
       </c>
       <c r="I25" t="e">
         <v>#N/A</v>
@@ -9815,19 +9815,19 @@
         <v>179</v>
       </c>
       <c r="D26" s="22" t="s">
+        <v>2575</v>
+      </c>
+      <c r="E26" s="15" t="s">
         <v>2576</v>
       </c>
-      <c r="E26" s="15" t="s">
-        <v>2577</v>
-      </c>
       <c r="F26" s="24" t="s">
-        <v>2582</v>
+        <v>2581</v>
       </c>
       <c r="G26" t="e">
         <v>#N/A</v>
       </c>
       <c r="H26" s="13" t="s">
-        <v>2774</v>
+        <v>2773</v>
       </c>
       <c r="I26" t="e">
         <v>#N/A</v>
@@ -9850,19 +9850,19 @@
         <v>180</v>
       </c>
       <c r="D27" s="22" t="s">
+        <v>2577</v>
+      </c>
+      <c r="E27" s="15" t="s">
         <v>2578</v>
       </c>
-      <c r="E27" s="15" t="s">
-        <v>2579</v>
-      </c>
       <c r="F27" s="24" t="s">
-        <v>2582</v>
+        <v>2581</v>
       </c>
       <c r="G27" t="e">
         <v>#N/A</v>
       </c>
       <c r="H27" s="13" t="s">
-        <v>2775</v>
+        <v>2774</v>
       </c>
       <c r="I27" t="e">
         <v>#N/A</v>
@@ -9885,19 +9885,19 @@
         <v>181</v>
       </c>
       <c r="D28" s="22" t="s">
+        <v>2579</v>
+      </c>
+      <c r="E28" s="15" t="s">
         <v>2580</v>
       </c>
-      <c r="E28" s="15" t="s">
-        <v>2581</v>
-      </c>
       <c r="F28" s="24" t="s">
-        <v>2569</v>
+        <v>2568</v>
       </c>
       <c r="G28" t="e">
         <v>#N/A</v>
       </c>
       <c r="H28" s="13" t="s">
-        <v>2776</v>
+        <v>2775</v>
       </c>
       <c r="I28" t="e">
         <v>#N/A</v>
@@ -9920,19 +9920,19 @@
         <v>182</v>
       </c>
       <c r="D29" s="22" t="s">
+        <v>2582</v>
+      </c>
+      <c r="E29" s="15" t="s">
         <v>2583</v>
       </c>
-      <c r="E29" s="15" t="s">
+      <c r="F29" s="24" t="s">
+        <v>2568</v>
+      </c>
+      <c r="G29" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H29" s="13" t="s">
         <v>2584</v>
-      </c>
-      <c r="F29" s="24" t="s">
-        <v>2569</v>
-      </c>
-      <c r="G29" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H29" s="13" t="s">
-        <v>2585</v>
       </c>
       <c r="I29" t="e">
         <v>#N/A</v>
@@ -9958,16 +9958,16 @@
         <v>#N/A</v>
       </c>
       <c r="E30" s="15" t="s">
+        <v>2585</v>
+      </c>
+      <c r="F30" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G30" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H30" s="13" t="s">
         <v>2586</v>
-      </c>
-      <c r="F30" s="24" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G30" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H30" s="13" t="s">
-        <v>2587</v>
       </c>
       <c r="I30" t="e">
         <v>#N/A</v>
@@ -9993,16 +9993,16 @@
         <v>#N/A</v>
       </c>
       <c r="E31" s="15" t="s">
+        <v>2587</v>
+      </c>
+      <c r="F31" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G31" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H31" s="13" t="s">
         <v>2588</v>
-      </c>
-      <c r="F31" s="24" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G31" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H31" s="13" t="s">
-        <v>2589</v>
       </c>
       <c r="I31" t="e">
         <v>#N/A</v>
@@ -10028,16 +10028,16 @@
         <v>#N/A</v>
       </c>
       <c r="E32" s="15" t="s">
+        <v>2589</v>
+      </c>
+      <c r="F32" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G32" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H32" s="13" t="s">
         <v>2590</v>
-      </c>
-      <c r="F32" s="24" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G32" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H32" s="13" t="s">
-        <v>2591</v>
       </c>
       <c r="I32" t="e">
         <v>#N/A</v>
@@ -10063,16 +10063,16 @@
         <v>#N/A</v>
       </c>
       <c r="E33" s="15" t="s">
+        <v>2591</v>
+      </c>
+      <c r="F33" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G33" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H33" s="13" t="s">
         <v>2592</v>
-      </c>
-      <c r="F33" s="24" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G33" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H33" s="13" t="s">
-        <v>2593</v>
       </c>
       <c r="I33" t="e">
         <v>#N/A</v>
@@ -10098,16 +10098,16 @@
         <v>#N/A</v>
       </c>
       <c r="E34" s="15" t="s">
+        <v>2593</v>
+      </c>
+      <c r="F34" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G34" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H34" s="13" t="s">
         <v>2594</v>
-      </c>
-      <c r="F34" s="24" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G34" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H34" s="13" t="s">
-        <v>2595</v>
       </c>
       <c r="I34" t="e">
         <v>#N/A</v>
@@ -10133,16 +10133,16 @@
         <v>#N/A</v>
       </c>
       <c r="E35" s="15" t="s">
+        <v>2595</v>
+      </c>
+      <c r="F35" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G35" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H35" s="13" t="s">
         <v>2596</v>
-      </c>
-      <c r="F35" s="24" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G35" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H35" s="13" t="s">
-        <v>2597</v>
       </c>
       <c r="I35" t="e">
         <v>#N/A</v>
@@ -10168,16 +10168,16 @@
         <v>#N/A</v>
       </c>
       <c r="E36" s="15" t="s">
+        <v>2597</v>
+      </c>
+      <c r="F36" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G36" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H36" s="13" t="s">
         <v>2598</v>
-      </c>
-      <c r="F36" s="24" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G36" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H36" s="13" t="s">
-        <v>2599</v>
       </c>
       <c r="I36" t="e">
         <v>#N/A</v>
@@ -10203,16 +10203,16 @@
         <v>#N/A</v>
       </c>
       <c r="E37" s="15" t="s">
+        <v>2599</v>
+      </c>
+      <c r="F37" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G37" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H37" s="13" t="s">
         <v>2600</v>
-      </c>
-      <c r="F37" s="24" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G37" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H37" s="13" t="s">
-        <v>2601</v>
       </c>
       <c r="I37" t="e">
         <v>#N/A</v>
@@ -10238,16 +10238,16 @@
         <v>#N/A</v>
       </c>
       <c r="E38" s="15" t="s">
+        <v>2601</v>
+      </c>
+      <c r="F38" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G38" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H38" s="13" t="s">
         <v>2602</v>
-      </c>
-      <c r="F38" s="24" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G38" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H38" s="13" t="s">
-        <v>2603</v>
       </c>
       <c r="I38" t="e">
         <v>#N/A</v>
@@ -10273,16 +10273,16 @@
         <v>#N/A</v>
       </c>
       <c r="E39" s="15" t="s">
+        <v>2603</v>
+      </c>
+      <c r="F39" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G39" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H39" s="13" t="s">
         <v>2604</v>
-      </c>
-      <c r="F39" s="24" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G39" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H39" s="13" t="s">
-        <v>2605</v>
       </c>
       <c r="I39" t="e">
         <v>#N/A</v>
@@ -10308,16 +10308,16 @@
         <v>#N/A</v>
       </c>
       <c r="E40" s="15" t="s">
+        <v>2605</v>
+      </c>
+      <c r="F40" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G40" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H40" s="13" t="s">
         <v>2606</v>
-      </c>
-      <c r="F40" s="24" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G40" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H40" s="13" t="s">
-        <v>2607</v>
       </c>
       <c r="I40" t="e">
         <v>#N/A</v>
@@ -10343,16 +10343,16 @@
         <v>#N/A</v>
       </c>
       <c r="E41" s="15" t="s">
+        <v>2607</v>
+      </c>
+      <c r="F41" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G41" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H41" s="13" t="s">
         <v>2608</v>
-      </c>
-      <c r="F41" s="24" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G41" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H41" s="13" t="s">
-        <v>2609</v>
       </c>
       <c r="I41" t="e">
         <v>#N/A</v>
@@ -10378,16 +10378,16 @@
         <v>#N/A</v>
       </c>
       <c r="E42" s="15" t="s">
+        <v>2609</v>
+      </c>
+      <c r="F42" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G42" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H42" s="13" t="s">
         <v>2610</v>
-      </c>
-      <c r="F42" s="24" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G42" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H42" s="13" t="s">
-        <v>2611</v>
       </c>
       <c r="I42" t="e">
         <v>#N/A</v>
@@ -10413,16 +10413,16 @@
         <v>#N/A</v>
       </c>
       <c r="E43" s="15" t="s">
+        <v>2611</v>
+      </c>
+      <c r="F43" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G43" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H43" s="13" t="s">
         <v>2612</v>
-      </c>
-      <c r="F43" s="24" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G43" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H43" s="13" t="s">
-        <v>2613</v>
       </c>
       <c r="I43" t="e">
         <v>#N/A</v>
@@ -10448,16 +10448,16 @@
         <v>#N/A</v>
       </c>
       <c r="E44" s="15" t="s">
+        <v>2613</v>
+      </c>
+      <c r="F44" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G44" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H44" s="13" t="s">
         <v>2614</v>
-      </c>
-      <c r="F44" s="24" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G44" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H44" s="13" t="s">
-        <v>2615</v>
       </c>
       <c r="I44" t="e">
         <v>#N/A</v>
@@ -10483,16 +10483,16 @@
         <v>#N/A</v>
       </c>
       <c r="E45" s="15" t="s">
+        <v>2615</v>
+      </c>
+      <c r="F45" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G45" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H45" s="13" t="s">
         <v>2616</v>
-      </c>
-      <c r="F45" s="24" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G45" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H45" s="13" t="s">
-        <v>2617</v>
       </c>
       <c r="I45" t="e">
         <v>#N/A</v>
@@ -10518,16 +10518,16 @@
         <v>#N/A</v>
       </c>
       <c r="E46" s="15" t="s">
+        <v>2617</v>
+      </c>
+      <c r="F46" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G46" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H46" s="13" t="s">
         <v>2618</v>
-      </c>
-      <c r="F46" s="24" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G46" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H46" s="13" t="s">
-        <v>2619</v>
       </c>
       <c r="I46" t="e">
         <v>#N/A</v>
@@ -10553,16 +10553,16 @@
         <v>#N/A</v>
       </c>
       <c r="E47" s="15" t="s">
+        <v>2619</v>
+      </c>
+      <c r="F47" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G47" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H47" s="13" t="s">
         <v>2620</v>
-      </c>
-      <c r="F47" s="24" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G47" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H47" s="13" t="s">
-        <v>2621</v>
       </c>
       <c r="I47" t="e">
         <v>#N/A</v>
@@ -10588,16 +10588,16 @@
         <v>#N/A</v>
       </c>
       <c r="E48" s="15" t="s">
+        <v>2621</v>
+      </c>
+      <c r="F48" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G48" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H48" s="13" t="s">
         <v>2622</v>
-      </c>
-      <c r="F48" s="24" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G48" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H48" s="13" t="s">
-        <v>2623</v>
       </c>
       <c r="I48" t="e">
         <v>#N/A</v>
@@ -10623,16 +10623,16 @@
         <v>#N/A</v>
       </c>
       <c r="E49" s="15" t="s">
+        <v>2623</v>
+      </c>
+      <c r="F49" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G49" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H49" s="13" t="s">
         <v>2624</v>
-      </c>
-      <c r="F49" s="24" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G49" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H49" s="13" t="s">
-        <v>2625</v>
       </c>
       <c r="I49" t="e">
         <v>#N/A</v>
@@ -10658,16 +10658,16 @@
         <v>#N/A</v>
       </c>
       <c r="E50" s="15" t="s">
+        <v>2625</v>
+      </c>
+      <c r="F50" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G50" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H50" s="13" t="s">
         <v>2626</v>
-      </c>
-      <c r="F50" s="24" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G50" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H50" s="13" t="s">
-        <v>2627</v>
       </c>
       <c r="I50" t="e">
         <v>#N/A</v>
@@ -10693,16 +10693,16 @@
         <v>#N/A</v>
       </c>
       <c r="E51" s="15" t="s">
+        <v>2627</v>
+      </c>
+      <c r="F51" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G51" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H51" s="13" t="s">
         <v>2628</v>
-      </c>
-      <c r="F51" s="24" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G51" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H51" s="13" t="s">
-        <v>2629</v>
       </c>
       <c r="I51" t="e">
         <v>#N/A</v>
@@ -10728,16 +10728,16 @@
         <v>#N/A</v>
       </c>
       <c r="E52" s="15" t="s">
+        <v>2629</v>
+      </c>
+      <c r="F52" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G52" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H52" s="13" t="s">
         <v>2630</v>
-      </c>
-      <c r="F52" s="24" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G52" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H52" s="13" t="s">
-        <v>2631</v>
       </c>
       <c r="I52" t="e">
         <v>#N/A</v>
@@ -10763,16 +10763,16 @@
         <v>#N/A</v>
       </c>
       <c r="E53" s="15" t="s">
+        <v>2631</v>
+      </c>
+      <c r="F53" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G53" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H53" s="13" t="s">
         <v>2632</v>
-      </c>
-      <c r="F53" s="24" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G53" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H53" s="13" t="s">
-        <v>2633</v>
       </c>
       <c r="I53" t="e">
         <v>#N/A</v>
@@ -10798,16 +10798,16 @@
         <v>#N/A</v>
       </c>
       <c r="E54" s="15" t="s">
+        <v>2633</v>
+      </c>
+      <c r="F54" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G54" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H54" s="13" t="s">
         <v>2634</v>
-      </c>
-      <c r="F54" s="24" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G54" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H54" s="13" t="s">
-        <v>2635</v>
       </c>
       <c r="I54" t="e">
         <v>#N/A</v>
@@ -10833,16 +10833,16 @@
         <v>#N/A</v>
       </c>
       <c r="E55" s="15" t="s">
+        <v>2635</v>
+      </c>
+      <c r="F55" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G55" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H55" s="13" t="s">
         <v>2636</v>
-      </c>
-      <c r="F55" s="24" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G55" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H55" s="13" t="s">
-        <v>2637</v>
       </c>
       <c r="I55" t="e">
         <v>#N/A</v>
@@ -10868,16 +10868,16 @@
         <v>#N/A</v>
       </c>
       <c r="E56" s="15" t="s">
+        <v>2637</v>
+      </c>
+      <c r="F56" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G56" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H56" s="13" t="s">
         <v>2638</v>
-      </c>
-      <c r="F56" s="24" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G56" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H56" s="13" t="s">
-        <v>2639</v>
       </c>
       <c r="I56" t="e">
         <v>#N/A</v>
@@ -10903,16 +10903,16 @@
         <v>#N/A</v>
       </c>
       <c r="E57" s="15" t="s">
+        <v>2639</v>
+      </c>
+      <c r="F57" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G57" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H57" s="13" t="s">
         <v>2640</v>
-      </c>
-      <c r="F57" s="24" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G57" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H57" s="13" t="s">
-        <v>2641</v>
       </c>
       <c r="I57" t="e">
         <v>#N/A</v>
@@ -10938,16 +10938,16 @@
         <v>#N/A</v>
       </c>
       <c r="E58" s="15" t="s">
+        <v>2641</v>
+      </c>
+      <c r="F58" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G58" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H58" s="13" t="s">
         <v>2642</v>
-      </c>
-      <c r="F58" s="24" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G58" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H58" s="13" t="s">
-        <v>2643</v>
       </c>
       <c r="I58" t="e">
         <v>#N/A</v>
@@ -10973,16 +10973,16 @@
         <v>#N/A</v>
       </c>
       <c r="E59" s="15" t="s">
+        <v>2643</v>
+      </c>
+      <c r="F59" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G59" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H59" s="13" t="s">
         <v>2644</v>
-      </c>
-      <c r="F59" s="24" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G59" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H59" s="13" t="s">
-        <v>2645</v>
       </c>
       <c r="I59" t="e">
         <v>#N/A</v>
@@ -11008,16 +11008,16 @@
         <v>#N/A</v>
       </c>
       <c r="E60" s="15" t="s">
+        <v>2645</v>
+      </c>
+      <c r="F60" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G60" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H60" s="13" t="s">
         <v>2646</v>
-      </c>
-      <c r="F60" s="24" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G60" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H60" s="13" t="s">
-        <v>2647</v>
       </c>
       <c r="I60" t="e">
         <v>#N/A</v>
@@ -11043,16 +11043,16 @@
         <v>#N/A</v>
       </c>
       <c r="E61" s="27" t="s">
+        <v>2647</v>
+      </c>
+      <c r="F61" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G61" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H61" s="13" t="s">
         <v>2648</v>
-      </c>
-      <c r="F61" s="24" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G61" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H61" s="13" t="s">
-        <v>2649</v>
       </c>
       <c r="I61" t="e">
         <v>#N/A</v>
@@ -11078,16 +11078,16 @@
         <v>#N/A</v>
       </c>
       <c r="E62" s="15" t="s">
+        <v>2649</v>
+      </c>
+      <c r="F62" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G62" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H62" s="13" t="s">
         <v>2650</v>
-      </c>
-      <c r="F62" s="24" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G62" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H62" s="13" t="s">
-        <v>2651</v>
       </c>
       <c r="I62" t="e">
         <v>#N/A</v>
@@ -11113,16 +11113,16 @@
         <v>#N/A</v>
       </c>
       <c r="E63" s="15" t="s">
+        <v>2651</v>
+      </c>
+      <c r="F63" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G63" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H63" s="13" t="s">
         <v>2652</v>
-      </c>
-      <c r="F63" s="24" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G63" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H63" s="13" t="s">
-        <v>2653</v>
       </c>
       <c r="I63" t="e">
         <v>#N/A</v>
@@ -11148,16 +11148,16 @@
         <v>#N/A</v>
       </c>
       <c r="E64" s="15" t="s">
+        <v>2653</v>
+      </c>
+      <c r="F64" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G64" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H64" s="13" t="s">
         <v>2654</v>
-      </c>
-      <c r="F64" s="24" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G64" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H64" s="13" t="s">
-        <v>2655</v>
       </c>
       <c r="I64" t="e">
         <v>#N/A</v>
@@ -11183,16 +11183,16 @@
         <v>#N/A</v>
       </c>
       <c r="E65" s="15" t="s">
+        <v>2655</v>
+      </c>
+      <c r="F65" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G65" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H65" s="13" t="s">
         <v>2656</v>
-      </c>
-      <c r="F65" s="24" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G65" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H65" s="13" t="s">
-        <v>2657</v>
       </c>
       <c r="I65" t="e">
         <v>#N/A</v>
@@ -11218,16 +11218,16 @@
         <v>#N/A</v>
       </c>
       <c r="E66" s="15" t="s">
+        <v>2657</v>
+      </c>
+      <c r="F66" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G66" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H66" s="13" t="s">
         <v>2658</v>
-      </c>
-      <c r="F66" s="24" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G66" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H66" s="13" t="s">
-        <v>2659</v>
       </c>
       <c r="I66" t="e">
         <v>#N/A</v>
@@ -11253,16 +11253,16 @@
         <v>#N/A</v>
       </c>
       <c r="E67" s="15" t="s">
+        <v>2659</v>
+      </c>
+      <c r="F67" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G67" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H67" s="13" t="s">
         <v>2660</v>
-      </c>
-      <c r="F67" s="24" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G67" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H67" s="13" t="s">
-        <v>2661</v>
       </c>
       <c r="I67" t="e">
         <v>#N/A</v>
@@ -11288,16 +11288,16 @@
         <v>#N/A</v>
       </c>
       <c r="E68" s="15" t="s">
+        <v>2661</v>
+      </c>
+      <c r="F68" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G68" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H68" s="13" t="s">
         <v>2662</v>
-      </c>
-      <c r="F68" s="24" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G68" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H68" s="13" t="s">
-        <v>2663</v>
       </c>
       <c r="I68" t="e">
         <v>#N/A</v>
@@ -11323,16 +11323,16 @@
         <v>#N/A</v>
       </c>
       <c r="E69" s="15" t="s">
+        <v>2663</v>
+      </c>
+      <c r="F69" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G69" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H69" s="13" t="s">
         <v>2664</v>
-      </c>
-      <c r="F69" s="24" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G69" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H69" s="13" t="s">
-        <v>2665</v>
       </c>
       <c r="I69" t="e">
         <v>#N/A</v>
@@ -11358,16 +11358,16 @@
         <v>#N/A</v>
       </c>
       <c r="E70" s="15" t="s">
+        <v>2665</v>
+      </c>
+      <c r="F70" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G70" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H70" s="13" t="s">
         <v>2666</v>
-      </c>
-      <c r="F70" s="24" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G70" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H70" s="13" t="s">
-        <v>2667</v>
       </c>
       <c r="I70" t="e">
         <v>#N/A</v>
@@ -11393,16 +11393,16 @@
         <v>#N/A</v>
       </c>
       <c r="E71" s="15" t="s">
+        <v>2667</v>
+      </c>
+      <c r="F71" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G71" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H71" s="13" t="s">
         <v>2668</v>
-      </c>
-      <c r="F71" s="24" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G71" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H71" s="13" t="s">
-        <v>2669</v>
       </c>
       <c r="I71" t="e">
         <v>#N/A</v>
@@ -11428,16 +11428,16 @@
         <v>#N/A</v>
       </c>
       <c r="E72" s="15" t="s">
+        <v>2669</v>
+      </c>
+      <c r="F72" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G72" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H72" s="13" t="s">
         <v>2670</v>
-      </c>
-      <c r="F72" s="24" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G72" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H72" s="13" t="s">
-        <v>2671</v>
       </c>
       <c r="I72" t="e">
         <v>#N/A</v>
@@ -11463,16 +11463,16 @@
         <v>#N/A</v>
       </c>
       <c r="E73" s="15" t="s">
+        <v>2671</v>
+      </c>
+      <c r="F73" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G73" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H73" s="13" t="s">
         <v>2672</v>
-      </c>
-      <c r="F73" s="24" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G73" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H73" s="13" t="s">
-        <v>2673</v>
       </c>
       <c r="I73" t="e">
         <v>#N/A</v>
@@ -11498,16 +11498,16 @@
         <v>#N/A</v>
       </c>
       <c r="E74" s="15" t="s">
+        <v>2673</v>
+      </c>
+      <c r="F74" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G74" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H74" s="13" t="s">
         <v>2674</v>
-      </c>
-      <c r="F74" s="24" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G74" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H74" s="13" t="s">
-        <v>2675</v>
       </c>
       <c r="I74" t="e">
         <v>#N/A</v>
@@ -11533,16 +11533,16 @@
         <v>#N/A</v>
       </c>
       <c r="E75" s="15" t="s">
+        <v>2675</v>
+      </c>
+      <c r="F75" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G75" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H75" s="13" t="s">
         <v>2676</v>
-      </c>
-      <c r="F75" s="24" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G75" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H75" s="13" t="s">
-        <v>2677</v>
       </c>
       <c r="I75" t="e">
         <v>#N/A</v>
@@ -11568,16 +11568,16 @@
         <v>#N/A</v>
       </c>
       <c r="E76" s="15" t="s">
+        <v>2677</v>
+      </c>
+      <c r="F76" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G76" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H76" s="13" t="s">
         <v>2678</v>
-      </c>
-      <c r="F76" s="24" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G76" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H76" s="13" t="s">
-        <v>2679</v>
       </c>
       <c r="I76" t="e">
         <v>#N/A</v>
@@ -11603,16 +11603,16 @@
         <v>#N/A</v>
       </c>
       <c r="E77" s="15" t="s">
+        <v>2679</v>
+      </c>
+      <c r="F77" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G77" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H77" s="13" t="s">
         <v>2680</v>
-      </c>
-      <c r="F77" s="24" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G77" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H77" s="13" t="s">
-        <v>2681</v>
       </c>
       <c r="I77" t="e">
         <v>#N/A</v>
@@ -11638,16 +11638,16 @@
         <v>#N/A</v>
       </c>
       <c r="E78" s="15" t="s">
+        <v>2681</v>
+      </c>
+      <c r="F78" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G78" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H78" s="13" t="s">
         <v>2682</v>
-      </c>
-      <c r="F78" s="24" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G78" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H78" s="13" t="s">
-        <v>2683</v>
       </c>
       <c r="I78" t="e">
         <v>#N/A</v>
@@ -11673,16 +11673,16 @@
         <v>#N/A</v>
       </c>
       <c r="E79" s="15" t="s">
+        <v>2683</v>
+      </c>
+      <c r="F79" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G79" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H79" s="13" t="s">
         <v>2684</v>
-      </c>
-      <c r="F79" s="24" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G79" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H79" s="13" t="s">
-        <v>2685</v>
       </c>
       <c r="I79" t="e">
         <v>#N/A</v>
@@ -11708,16 +11708,16 @@
         <v>#N/A</v>
       </c>
       <c r="E80" s="22" t="s">
+        <v>2685</v>
+      </c>
+      <c r="F80" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G80" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H80" s="13" t="s">
         <v>2686</v>
-      </c>
-      <c r="F80" s="24" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G80" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H80" s="13" t="s">
-        <v>2687</v>
       </c>
       <c r="I80" t="e">
         <v>#N/A</v>
@@ -11743,16 +11743,16 @@
         <v>#N/A</v>
       </c>
       <c r="E81" s="22" t="s">
+        <v>2687</v>
+      </c>
+      <c r="F81" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G81" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H81" s="13" t="s">
         <v>2688</v>
-      </c>
-      <c r="F81" s="24" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G81" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H81" s="13" t="s">
-        <v>2689</v>
       </c>
       <c r="I81" t="e">
         <v>#N/A</v>
@@ -11778,16 +11778,16 @@
         <v>#N/A</v>
       </c>
       <c r="E82" s="22" t="s">
+        <v>2689</v>
+      </c>
+      <c r="F82" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G82" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H82" s="13" t="s">
         <v>2690</v>
-      </c>
-      <c r="F82" s="24" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G82" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H82" s="13" t="s">
-        <v>2691</v>
       </c>
       <c r="I82" t="e">
         <v>#N/A</v>
@@ -11813,16 +11813,16 @@
         <v>#N/A</v>
       </c>
       <c r="E83" s="22" t="s">
+        <v>2691</v>
+      </c>
+      <c r="F83" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G83" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H83" s="13" t="s">
         <v>2692</v>
-      </c>
-      <c r="F83" s="24" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G83" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H83" s="13" t="s">
-        <v>2693</v>
       </c>
       <c r="I83" t="e">
         <v>#N/A</v>
@@ -11848,16 +11848,16 @@
         <v>#N/A</v>
       </c>
       <c r="E84" s="15" t="s">
+        <v>2693</v>
+      </c>
+      <c r="F84" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G84" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H84" s="13" t="s">
         <v>2694</v>
-      </c>
-      <c r="F84" s="24" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G84" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H84" s="13" t="s">
-        <v>2695</v>
       </c>
       <c r="I84" t="e">
         <v>#N/A</v>
@@ -11883,16 +11883,16 @@
         <v>#N/A</v>
       </c>
       <c r="E85" s="15" t="s">
+        <v>2695</v>
+      </c>
+      <c r="F85" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G85" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H85" s="13" t="s">
         <v>2696</v>
-      </c>
-      <c r="F85" s="24" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G85" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H85" s="13" t="s">
-        <v>2697</v>
       </c>
       <c r="I85" t="e">
         <v>#N/A</v>
@@ -11918,16 +11918,16 @@
         <v>#N/A</v>
       </c>
       <c r="E86" s="15" t="s">
+        <v>2697</v>
+      </c>
+      <c r="F86" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G86" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H86" s="13" t="s">
         <v>2698</v>
-      </c>
-      <c r="F86" s="24" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G86" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H86" s="13" t="s">
-        <v>2699</v>
       </c>
       <c r="I86" t="e">
         <v>#N/A</v>
@@ -11953,16 +11953,16 @@
         <v>#N/A</v>
       </c>
       <c r="E87" s="15" t="s">
+        <v>2699</v>
+      </c>
+      <c r="F87" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G87" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H87" s="13" t="s">
         <v>2700</v>
-      </c>
-      <c r="F87" s="24" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G87" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H87" s="13" t="s">
-        <v>2701</v>
       </c>
       <c r="I87" t="e">
         <v>#N/A</v>
@@ -11988,16 +11988,16 @@
         <v>#N/A</v>
       </c>
       <c r="E88" s="15" t="s">
+        <v>2701</v>
+      </c>
+      <c r="F88" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G88" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H88" s="13" t="s">
         <v>2702</v>
-      </c>
-      <c r="F88" s="24" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G88" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H88" s="13" t="s">
-        <v>2703</v>
       </c>
       <c r="I88" t="e">
         <v>#N/A</v>
@@ -12023,16 +12023,16 @@
         <v>#N/A</v>
       </c>
       <c r="E89" s="15" t="s">
+        <v>2703</v>
+      </c>
+      <c r="F89" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G89" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H89" s="13" t="s">
         <v>2704</v>
-      </c>
-      <c r="F89" s="24" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G89" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H89" s="13" t="s">
-        <v>2705</v>
       </c>
       <c r="I89" t="e">
         <v>#N/A</v>
@@ -12058,16 +12058,16 @@
         <v>#N/A</v>
       </c>
       <c r="E90" s="15" t="s">
+        <v>2705</v>
+      </c>
+      <c r="F90" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G90" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H90" s="13" t="s">
         <v>2706</v>
-      </c>
-      <c r="F90" s="24" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G90" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H90" s="13" t="s">
-        <v>2707</v>
       </c>
       <c r="I90" t="e">
         <v>#N/A</v>
@@ -12093,16 +12093,16 @@
         <v>#N/A</v>
       </c>
       <c r="E91" s="15" t="s">
+        <v>2707</v>
+      </c>
+      <c r="F91" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G91" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H91" s="13" t="s">
         <v>2708</v>
-      </c>
-      <c r="F91" s="24" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G91" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H91" s="13" t="s">
-        <v>2709</v>
       </c>
       <c r="I91" t="e">
         <v>#N/A</v>
@@ -12128,16 +12128,16 @@
         <v>#N/A</v>
       </c>
       <c r="E92" s="15" t="s">
+        <v>2709</v>
+      </c>
+      <c r="F92" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G92" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H92" s="13" t="s">
         <v>2710</v>
-      </c>
-      <c r="F92" s="24" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G92" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H92" s="13" t="s">
-        <v>2711</v>
       </c>
       <c r="I92" t="e">
         <v>#N/A</v>
@@ -12163,16 +12163,16 @@
         <v>#N/A</v>
       </c>
       <c r="E93" s="15" t="s">
+        <v>2711</v>
+      </c>
+      <c r="F93" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G93" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H93" s="13" t="s">
         <v>2712</v>
-      </c>
-      <c r="F93" s="24" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G93" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H93" s="13" t="s">
-        <v>2713</v>
       </c>
       <c r="I93" t="e">
         <v>#N/A</v>
@@ -12198,16 +12198,16 @@
         <v>#N/A</v>
       </c>
       <c r="E94" s="15" t="s">
+        <v>2713</v>
+      </c>
+      <c r="F94" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G94" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H94" s="13" t="s">
         <v>2714</v>
-      </c>
-      <c r="F94" s="24" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G94" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H94" s="13" t="s">
-        <v>2715</v>
       </c>
       <c r="I94" t="e">
         <v>#N/A</v>
@@ -12233,16 +12233,16 @@
         <v>#N/A</v>
       </c>
       <c r="E95" s="15" t="s">
+        <v>2715</v>
+      </c>
+      <c r="F95" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G95" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H95" s="13" t="s">
         <v>2716</v>
-      </c>
-      <c r="F95" s="24" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G95" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H95" s="13" t="s">
-        <v>2717</v>
       </c>
       <c r="I95" t="e">
         <v>#N/A</v>
@@ -12268,16 +12268,16 @@
         <v>#N/A</v>
       </c>
       <c r="E96" s="15" t="s">
+        <v>2717</v>
+      </c>
+      <c r="F96" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G96" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H96" s="13" t="s">
         <v>2718</v>
-      </c>
-      <c r="F96" s="24" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G96" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H96" s="13" t="s">
-        <v>2719</v>
       </c>
       <c r="I96" t="e">
         <v>#N/A</v>
@@ -12303,16 +12303,16 @@
         <v>#N/A</v>
       </c>
       <c r="E97" s="15" t="s">
+        <v>2719</v>
+      </c>
+      <c r="F97" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G97" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H97" s="13" t="s">
         <v>2720</v>
-      </c>
-      <c r="F97" s="24" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G97" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H97" s="13" t="s">
-        <v>2721</v>
       </c>
       <c r="I97" t="e">
         <v>#N/A</v>
@@ -12338,16 +12338,16 @@
         <v>#N/A</v>
       </c>
       <c r="E98" s="15" t="s">
+        <v>2721</v>
+      </c>
+      <c r="F98" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G98" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H98" s="13" t="s">
         <v>2722</v>
-      </c>
-      <c r="F98" s="24" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G98" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H98" s="13" t="s">
-        <v>2723</v>
       </c>
       <c r="I98" t="e">
         <v>#N/A</v>
@@ -12373,16 +12373,16 @@
         <v>#N/A</v>
       </c>
       <c r="E99" s="15" t="s">
+        <v>2723</v>
+      </c>
+      <c r="F99" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G99" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H99" s="13" t="s">
         <v>2724</v>
-      </c>
-      <c r="F99" s="24" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G99" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H99" s="13" t="s">
-        <v>2725</v>
       </c>
       <c r="I99" t="e">
         <v>#N/A</v>
@@ -12408,16 +12408,16 @@
         <v>#N/A</v>
       </c>
       <c r="E100" s="15" t="s">
+        <v>2725</v>
+      </c>
+      <c r="F100" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G100" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H100" s="13" t="s">
         <v>2726</v>
-      </c>
-      <c r="F100" s="24" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G100" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H100" s="13" t="s">
-        <v>2727</v>
       </c>
       <c r="I100" t="e">
         <v>#N/A</v>
@@ -12443,16 +12443,16 @@
         <v>#N/A</v>
       </c>
       <c r="E101" s="15" t="s">
+        <v>2727</v>
+      </c>
+      <c r="F101" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G101" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H101" s="13" t="s">
         <v>2728</v>
-      </c>
-      <c r="F101" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G101" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H101" s="13" t="s">
-        <v>2729</v>
       </c>
       <c r="I101" t="e">
         <v>#N/A</v>
@@ -12478,16 +12478,16 @@
         <v>#N/A</v>
       </c>
       <c r="E102" s="15" t="s">
+        <v>2729</v>
+      </c>
+      <c r="F102" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G102" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H102" s="13" t="s">
         <v>2730</v>
-      </c>
-      <c r="F102" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G102" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H102" s="13" t="s">
-        <v>2731</v>
       </c>
       <c r="I102" t="e">
         <v>#N/A</v>
@@ -12513,16 +12513,16 @@
         <v>#N/A</v>
       </c>
       <c r="E103" s="15" t="s">
+        <v>2731</v>
+      </c>
+      <c r="F103" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G103" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H103" s="13" t="s">
         <v>2732</v>
-      </c>
-      <c r="F103" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G103" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H103" s="13" t="s">
-        <v>2733</v>
       </c>
       <c r="I103" t="e">
         <v>#N/A</v>
@@ -12548,16 +12548,16 @@
         <v>#N/A</v>
       </c>
       <c r="E104" s="15" t="s">
+        <v>2733</v>
+      </c>
+      <c r="F104" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G104" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H104" s="13" t="s">
         <v>2734</v>
-      </c>
-      <c r="F104" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G104" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H104" s="13" t="s">
-        <v>2735</v>
       </c>
       <c r="I104" t="e">
         <v>#N/A</v>
@@ -12583,16 +12583,16 @@
         <v>#N/A</v>
       </c>
       <c r="E105" s="15" t="s">
+        <v>2735</v>
+      </c>
+      <c r="F105" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G105" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H105" s="13" t="s">
         <v>2736</v>
-      </c>
-      <c r="F105" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G105" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H105" s="13" t="s">
-        <v>2737</v>
       </c>
       <c r="I105" t="e">
         <v>#N/A</v>
@@ -12618,16 +12618,16 @@
         <v>#N/A</v>
       </c>
       <c r="E106" s="15" t="s">
+        <v>2737</v>
+      </c>
+      <c r="F106" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G106" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H106" s="13" t="s">
         <v>2738</v>
-      </c>
-      <c r="F106" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G106" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H106" s="13" t="s">
-        <v>2739</v>
       </c>
       <c r="I106" t="e">
         <v>#N/A</v>
@@ -12653,16 +12653,16 @@
         <v>#N/A</v>
       </c>
       <c r="E107" s="15" t="s">
+        <v>2739</v>
+      </c>
+      <c r="F107" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G107" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H107" s="13" t="s">
         <v>2740</v>
-      </c>
-      <c r="F107" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G107" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H107" s="13" t="s">
-        <v>2741</v>
       </c>
       <c r="I107" t="e">
         <v>#N/A</v>
@@ -12688,16 +12688,16 @@
         <v>#N/A</v>
       </c>
       <c r="E108" s="15" t="s">
+        <v>2741</v>
+      </c>
+      <c r="F108" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G108" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H108" s="13" t="s">
         <v>2742</v>
-      </c>
-      <c r="F108" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G108" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H108" s="13" t="s">
-        <v>2743</v>
       </c>
       <c r="I108" t="e">
         <v>#N/A</v>
@@ -12723,16 +12723,16 @@
         <v>#N/A</v>
       </c>
       <c r="E109" s="15" t="s">
+        <v>2743</v>
+      </c>
+      <c r="F109" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G109" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H109" s="13" t="s">
         <v>2744</v>
-      </c>
-      <c r="F109" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G109" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H109" s="13" t="s">
-        <v>2745</v>
       </c>
       <c r="I109" t="e">
         <v>#N/A</v>
@@ -12758,16 +12758,16 @@
         <v>#N/A</v>
       </c>
       <c r="E110" s="15" t="s">
+        <v>2745</v>
+      </c>
+      <c r="F110" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G110" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H110" s="13" t="s">
         <v>2746</v>
-      </c>
-      <c r="F110" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G110" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H110" s="13" t="s">
-        <v>2747</v>
       </c>
       <c r="I110" t="e">
         <v>#N/A</v>
@@ -12793,16 +12793,16 @@
         <v>#N/A</v>
       </c>
       <c r="E111" s="15" t="s">
+        <v>2747</v>
+      </c>
+      <c r="F111" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G111" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H111" s="13" t="s">
         <v>2748</v>
-      </c>
-      <c r="F111" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G111" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H111" s="13" t="s">
-        <v>2749</v>
       </c>
       <c r="I111" t="e">
         <v>#N/A</v>
@@ -12828,16 +12828,16 @@
         <v>#N/A</v>
       </c>
       <c r="E112" s="15" t="s">
+        <v>2749</v>
+      </c>
+      <c r="F112" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G112" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H112" s="13" t="s">
         <v>2750</v>
-      </c>
-      <c r="F112" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G112" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H112" s="13" t="s">
-        <v>2751</v>
       </c>
       <c r="I112" t="e">
         <v>#N/A</v>
@@ -12863,16 +12863,16 @@
         <v>#N/A</v>
       </c>
       <c r="E113" s="15" t="s">
+        <v>2751</v>
+      </c>
+      <c r="F113" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G113" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H113" s="13" t="s">
         <v>2752</v>
-      </c>
-      <c r="F113" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G113" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H113" s="13" t="s">
-        <v>2753</v>
       </c>
       <c r="I113" t="e">
         <v>#N/A</v>
@@ -12898,16 +12898,16 @@
         <v>#N/A</v>
       </c>
       <c r="E114" s="15" t="s">
+        <v>2753</v>
+      </c>
+      <c r="F114" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G114" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H114" s="13" t="s">
         <v>2754</v>
-      </c>
-      <c r="F114" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G114" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H114" s="13" t="s">
-        <v>2755</v>
       </c>
       <c r="I114" t="e">
         <v>#N/A</v>
@@ -12933,16 +12933,16 @@
         <v>#N/A</v>
       </c>
       <c r="E115" s="15" t="s">
+        <v>2755</v>
+      </c>
+      <c r="F115" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G115" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H115" s="13" t="s">
         <v>2756</v>
-      </c>
-      <c r="F115" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G115" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H115" s="13" t="s">
-        <v>2757</v>
       </c>
       <c r="I115" t="e">
         <v>#N/A</v>
@@ -12968,16 +12968,16 @@
         <v>#N/A</v>
       </c>
       <c r="E116" s="15" t="s">
+        <v>2757</v>
+      </c>
+      <c r="F116" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G116" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H116" s="13" t="s">
         <v>2758</v>
-      </c>
-      <c r="F116" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G116" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H116" s="13" t="s">
-        <v>2759</v>
       </c>
       <c r="I116" t="e">
         <v>#N/A</v>
@@ -13003,16 +13003,16 @@
         <v>#N/A</v>
       </c>
       <c r="E117" s="15" t="s">
+        <v>2759</v>
+      </c>
+      <c r="F117" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G117" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H117" s="13" t="s">
         <v>2760</v>
-      </c>
-      <c r="F117" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G117" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H117" s="13" t="s">
-        <v>2761</v>
       </c>
       <c r="I117" t="e">
         <v>#N/A</v>
@@ -13038,16 +13038,16 @@
         <v>#N/A</v>
       </c>
       <c r="E118" s="15" t="s">
+        <v>2753</v>
+      </c>
+      <c r="F118" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G118" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H118" s="13" t="s">
         <v>2754</v>
-      </c>
-      <c r="F118" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G118" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H118" s="13" t="s">
-        <v>2755</v>
       </c>
       <c r="I118" t="e">
         <v>#N/A</v>
@@ -13073,7 +13073,7 @@
         <v>#N/A</v>
       </c>
       <c r="E119" s="15" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="F119" s="13" t="e">
         <v>#N/A</v>
@@ -13082,7 +13082,7 @@
         <v>#N/A</v>
       </c>
       <c r="H119" s="13" t="s">
-        <v>2762</v>
+        <v>2761</v>
       </c>
       <c r="I119" t="e">
         <v>#N/A</v>
@@ -13108,7 +13108,7 @@
         <v>#N/A</v>
       </c>
       <c r="E120" s="15" t="s">
-        <v>2758</v>
+        <v>2757</v>
       </c>
       <c r="F120" s="13" t="e">
         <v>#N/A</v>
@@ -13117,7 +13117,7 @@
         <v>#N/A</v>
       </c>
       <c r="H120" s="13" t="s">
-        <v>2763</v>
+        <v>2762</v>
       </c>
       <c r="I120" t="e">
         <v>#N/A</v>
@@ -13143,7 +13143,7 @@
         <v>#N/A</v>
       </c>
       <c r="E121" s="15" t="s">
-        <v>2760</v>
+        <v>2759</v>
       </c>
       <c r="F121" s="13" t="e">
         <v>#N/A</v>
@@ -13152,7 +13152,7 @@
         <v>#N/A</v>
       </c>
       <c r="H121" s="13" t="s">
-        <v>2764</v>
+        <v>2763</v>
       </c>
       <c r="I121" t="e">
         <v>#N/A</v>
@@ -13178,16 +13178,16 @@
         <v>#N/A</v>
       </c>
       <c r="E122" s="15" t="s">
+        <v>2764</v>
+      </c>
+      <c r="F122" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G122" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H122" s="13" t="s">
         <v>2765</v>
-      </c>
-      <c r="F122" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G122" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H122" s="13" t="s">
-        <v>2766</v>
       </c>
       <c r="I122" t="e">
         <v>#N/A</v>
@@ -13213,16 +13213,16 @@
         <v>#N/A</v>
       </c>
       <c r="E123" s="15" t="s">
+        <v>2766</v>
+      </c>
+      <c r="F123" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G123" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H123" s="13" t="s">
         <v>2767</v>
-      </c>
-      <c r="F123" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G123" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H123" s="13" t="s">
-        <v>2768</v>
       </c>
       <c r="I123" t="e">
         <v>#N/A</v>
@@ -21225,10 +21225,10 @@
         <v>497</v>
       </c>
       <c r="D352" s="2" t="s">
+        <v>2481</v>
+      </c>
+      <c r="E352" s="2" t="s">
         <v>2482</v>
-      </c>
-      <c r="E352" s="2" t="s">
-        <v>2483</v>
       </c>
       <c r="F352" t="s">
         <v>1586</v>
@@ -30115,10 +30115,10 @@
         <v>749</v>
       </c>
       <c r="D606" s="2" t="s">
+        <v>2513</v>
+      </c>
+      <c r="E606" s="2" t="s">
         <v>2514</v>
-      </c>
-      <c r="E606" s="2" t="s">
-        <v>2515</v>
       </c>
       <c r="F606" t="s">
         <v>1586</v>
@@ -31313,7 +31313,7 @@
         <v>783</v>
       </c>
       <c r="D641" s="2" t="s">
-        <v>2419</v>
+        <v>2418</v>
       </c>
       <c r="E641" s="2" t="s">
         <v>1849</v>
@@ -31473,7 +31473,7 @@
         <v>788</v>
       </c>
       <c r="D646" s="2" t="s">
-        <v>2487</v>
+        <v>2486</v>
       </c>
       <c r="E646" s="2" t="s">
         <v>1877</v>
@@ -31508,7 +31508,7 @@
         <v>789</v>
       </c>
       <c r="D647" s="2" t="s">
-        <v>2420</v>
+        <v>2419</v>
       </c>
       <c r="E647" s="2" t="s">
         <v>1882</v>
@@ -37598,10 +37598,10 @@
         <v>2360</v>
       </c>
       <c r="D821" s="2" t="s">
-        <v>2466</v>
+        <v>2465</v>
       </c>
       <c r="E821" s="2" t="s">
-        <v>2463</v>
+        <v>2462</v>
       </c>
       <c r="F821" t="s">
         <v>1586</v>
@@ -37633,10 +37633,10 @@
         <v>2328</v>
       </c>
       <c r="D822" s="2" t="s">
-        <v>2465</v>
+        <v>2464</v>
       </c>
       <c r="E822" s="2" t="s">
-        <v>2464</v>
+        <v>2463</v>
       </c>
       <c r="F822" t="s">
         <v>1586</v>
@@ -38333,10 +38333,10 @@
         <v>966</v>
       </c>
       <c r="D842" s="2" t="s">
-        <v>2469</v>
+        <v>2468</v>
       </c>
       <c r="E842" s="2" t="s">
-        <v>2468</v>
+        <v>2467</v>
       </c>
       <c r="F842" t="s">
         <v>105</v>
@@ -38368,10 +38368,10 @@
         <v>967</v>
       </c>
       <c r="D843" s="2" t="s">
-        <v>2471</v>
+        <v>2470</v>
       </c>
       <c r="E843" s="2" t="s">
-        <v>2470</v>
+        <v>2469</v>
       </c>
       <c r="F843" t="s">
         <v>1586</v>
@@ -38438,10 +38438,10 @@
         <v>969</v>
       </c>
       <c r="D845" s="2" t="s">
-        <v>2473</v>
+        <v>2472</v>
       </c>
       <c r="E845" s="2" t="s">
-        <v>2472</v>
+        <v>2471</v>
       </c>
       <c r="F845" t="s">
         <v>1586</v>
@@ -38473,10 +38473,10 @@
         <v>970</v>
       </c>
       <c r="D846" s="2" t="s">
+        <v>2473</v>
+      </c>
+      <c r="E846" s="2" t="s">
         <v>2474</v>
-      </c>
-      <c r="E846" s="2" t="s">
-        <v>2475</v>
       </c>
       <c r="F846" t="s">
         <v>1586</v>
@@ -38683,10 +38683,10 @@
         <v>976</v>
       </c>
       <c r="D852" s="2" t="s">
+        <v>2542</v>
+      </c>
+      <c r="E852" s="2" t="s">
         <v>2543</v>
-      </c>
-      <c r="E852" s="2" t="s">
-        <v>2544</v>
       </c>
       <c r="F852" t="s">
         <v>1586</v>
@@ -39071,7 +39071,7 @@
         <v>2355</v>
       </c>
       <c r="E863" s="2" t="s">
-        <v>2523</v>
+        <v>2522</v>
       </c>
       <c r="F863" t="s">
         <v>1586</v>
@@ -39383,10 +39383,10 @@
         <v>996</v>
       </c>
       <c r="D872" s="2" t="s">
-        <v>2528</v>
+        <v>2527</v>
       </c>
       <c r="E872" s="2" t="s">
-        <v>2531</v>
+        <v>2530</v>
       </c>
       <c r="F872" t="s">
         <v>1586</v>
@@ -39418,10 +39418,10 @@
         <v>997</v>
       </c>
       <c r="D873" s="2" t="s">
-        <v>2539</v>
+        <v>2538</v>
       </c>
       <c r="E873" s="2" t="s">
-        <v>2534</v>
+        <v>2533</v>
       </c>
       <c r="F873" t="s">
         <v>1586</v>
@@ -39453,10 +39453,10 @@
         <v>998</v>
       </c>
       <c r="D874" s="2" t="s">
-        <v>2533</v>
+        <v>2532</v>
       </c>
       <c r="E874" s="2" t="s">
-        <v>2532</v>
+        <v>2531</v>
       </c>
       <c r="F874" t="s">
         <v>1586</v>
@@ -39485,13 +39485,13 @@
         <v>47714</v>
       </c>
       <c r="C875" s="6" t="s">
+        <v>2535</v>
+      </c>
+      <c r="D875" s="2" t="s">
+        <v>2537</v>
+      </c>
+      <c r="E875" s="2" t="s">
         <v>2536</v>
-      </c>
-      <c r="D875" s="2" t="s">
-        <v>2538</v>
-      </c>
-      <c r="E875" s="2" t="s">
-        <v>2537</v>
       </c>
       <c r="F875" t="s">
         <v>1586</v>
@@ -39631,7 +39631,7 @@
         <v>2356</v>
       </c>
       <c r="E879" s="2" t="s">
-        <v>2540</v>
+        <v>2539</v>
       </c>
       <c r="F879" t="s">
         <v>1586</v>
@@ -39908,10 +39908,10 @@
         <v>1010</v>
       </c>
       <c r="D887" s="2" t="s">
-        <v>2535</v>
+        <v>2534</v>
       </c>
       <c r="E887" s="2" t="s">
-        <v>2545</v>
+        <v>2544</v>
       </c>
       <c r="F887" t="s">
         <v>1586</v>
@@ -39943,10 +39943,10 @@
         <v>1011</v>
       </c>
       <c r="D888" s="2" t="s">
+        <v>2545</v>
+      </c>
+      <c r="E888" s="2" t="s">
         <v>2546</v>
-      </c>
-      <c r="E888" s="2" t="s">
-        <v>2547</v>
       </c>
       <c r="F888" t="s">
         <v>1586</v>
@@ -39978,10 +39978,10 @@
         <v>1012</v>
       </c>
       <c r="D889" s="2" t="s">
-        <v>2542</v>
+        <v>2541</v>
       </c>
       <c r="E889" s="2" t="s">
-        <v>2541</v>
+        <v>2540</v>
       </c>
       <c r="F889" t="s">
         <v>1586</v>
@@ -40608,7 +40608,7 @@
         <v>1030</v>
       </c>
       <c r="D907" s="2" t="s">
-        <v>2467</v>
+        <v>2466</v>
       </c>
       <c r="E907" s="2" t="s">
         <v>2333</v>
@@ -40745,13 +40745,13 @@
         <v>47781</v>
       </c>
       <c r="C911" s="6" t="s">
+        <v>2478</v>
+      </c>
+      <c r="D911" s="2" t="s">
         <v>2479</v>
       </c>
-      <c r="D911" s="2" t="s">
+      <c r="E911" s="2" t="s">
         <v>2480</v>
-      </c>
-      <c r="E911" s="2" t="s">
-        <v>2481</v>
       </c>
       <c r="F911" t="s">
         <v>1586</v>
@@ -41273,10 +41273,10 @@
         <v>1048</v>
       </c>
       <c r="D926" s="2" t="s">
+        <v>2487</v>
+      </c>
+      <c r="E926" s="2" t="s">
         <v>2488</v>
-      </c>
-      <c r="E926" s="2" t="s">
-        <v>2489</v>
       </c>
       <c r="F926" t="s">
         <v>1586</v>
@@ -41308,10 +41308,10 @@
         <v>1049</v>
       </c>
       <c r="D927" s="2" t="s">
+        <v>2497</v>
+      </c>
+      <c r="E927" s="2" t="s">
         <v>2498</v>
-      </c>
-      <c r="E927" s="2" t="s">
-        <v>2499</v>
       </c>
       <c r="F927" t="s">
         <v>1586</v>
@@ -42043,10 +42043,10 @@
         <v>1070</v>
       </c>
       <c r="D948" s="2" t="s">
-        <v>2494</v>
+        <v>2493</v>
       </c>
       <c r="E948" s="2" t="s">
-        <v>2502</v>
+        <v>2501</v>
       </c>
       <c r="F948" t="s">
         <v>1586</v>
@@ -42078,10 +42078,10 @@
         <v>1071</v>
       </c>
       <c r="D949" s="2" t="s">
+        <v>2494</v>
+      </c>
+      <c r="E949" s="2" t="s">
         <v>2495</v>
-      </c>
-      <c r="E949" s="2" t="s">
-        <v>2496</v>
       </c>
       <c r="F949" t="s">
         <v>1586</v>
@@ -42180,7 +42180,7 @@
         <v>50111</v>
       </c>
       <c r="C952" s="6" t="s">
-        <v>2503</v>
+        <v>2502</v>
       </c>
       <c r="D952" s="2" t="e">
         <v>#N/A</v>
@@ -42285,7 +42285,7 @@
         <v>50114</v>
       </c>
       <c r="C955" s="6" t="s">
-        <v>2504</v>
+        <v>2503</v>
       </c>
       <c r="D955" s="2" t="e">
         <v>#N/A</v>
@@ -42600,7 +42600,7 @@
         <v>50131</v>
       </c>
       <c r="C964" s="6" t="s">
-        <v>2505</v>
+        <v>2504</v>
       </c>
       <c r="D964" s="2" t="e">
         <v>#N/A</v>
@@ -42670,7 +42670,7 @@
         <v>50133</v>
       </c>
       <c r="C966" s="6" t="s">
-        <v>2506</v>
+        <v>2505</v>
       </c>
       <c r="D966" s="2" t="e">
         <v>#N/A</v>
@@ -42705,7 +42705,7 @@
         <v>50134</v>
       </c>
       <c r="C967" s="6" t="s">
-        <v>2507</v>
+        <v>2506</v>
       </c>
       <c r="D967" s="2" t="e">
         <v>#N/A</v>
@@ -42845,7 +42845,7 @@
         <v>50142</v>
       </c>
       <c r="C971" s="6" t="s">
-        <v>2508</v>
+        <v>2507</v>
       </c>
       <c r="D971" s="2" t="e">
         <v>#N/A</v>
@@ -42880,7 +42880,7 @@
         <v>50143</v>
       </c>
       <c r="C972" s="6" t="s">
-        <v>2509</v>
+        <v>2508</v>
       </c>
       <c r="D972" s="2" t="e">
         <v>#N/A</v>
@@ -42915,7 +42915,7 @@
         <v>50144</v>
       </c>
       <c r="C973" s="6" t="s">
-        <v>2510</v>
+        <v>2509</v>
       </c>
       <c r="D973" s="2" t="e">
         <v>#N/A</v>
@@ -42950,7 +42950,7 @@
         <v>50145</v>
       </c>
       <c r="C974" s="6" t="s">
-        <v>2511</v>
+        <v>2510</v>
       </c>
       <c r="D974" s="2" t="e">
         <v>#N/A</v>
@@ -43020,7 +43020,7 @@
         <v>50211</v>
       </c>
       <c r="C976" s="6" t="s">
-        <v>2512</v>
+        <v>2511</v>
       </c>
       <c r="D976" s="2" t="e">
         <v>#N/A</v>
@@ -43055,7 +43055,7 @@
         <v>50212</v>
       </c>
       <c r="C977" s="6" t="s">
-        <v>2513</v>
+        <v>2512</v>
       </c>
       <c r="D977" s="2" t="e">
         <v>#N/A</v>
@@ -44843,10 +44843,10 @@
         <v>15</v>
       </c>
       <c r="D1028" s="2" t="s">
-        <v>2497</v>
+        <v>2496</v>
       </c>
       <c r="E1028" s="2" t="s">
-        <v>2524</v>
+        <v>2523</v>
       </c>
       <c r="F1028" t="s">
         <v>1586</v>
@@ -45149,7 +45149,7 @@
         <v>118</v>
       </c>
       <c r="E1037" s="2" t="s">
-        <v>2416</v>
+        <v>2415</v>
       </c>
       <c r="F1037" t="s">
         <v>105</v>
@@ -45405,10 +45405,10 @@
         <v>1147</v>
       </c>
       <c r="D1045" s="2" t="s">
-        <v>2520</v>
+        <v>2519</v>
       </c>
       <c r="E1045" s="2" t="s">
-        <v>2417</v>
+        <v>2416</v>
       </c>
       <c r="F1045" t="s">
         <v>1586</v>
@@ -45437,7 +45437,7 @@
         <v>1148</v>
       </c>
       <c r="D1046" s="2" t="s">
-        <v>2529</v>
+        <v>2528</v>
       </c>
       <c r="E1046" s="2" t="s">
         <v>2351</v>
@@ -45469,7 +45469,7 @@
         <v>1149</v>
       </c>
       <c r="D1047" s="2" t="s">
-        <v>2530</v>
+        <v>2529</v>
       </c>
       <c r="E1047" s="2" t="s">
         <v>2352</v>
@@ -45539,10 +45539,10 @@
         <v>1151</v>
       </c>
       <c r="D1049" s="2" t="s">
+        <v>2499</v>
+      </c>
+      <c r="E1049" s="2" t="s">
         <v>2500</v>
-      </c>
-      <c r="E1049" s="2" t="s">
-        <v>2501</v>
       </c>
       <c r="F1049" t="s">
         <v>1586</v>
@@ -45924,10 +45924,10 @@
         <v>1161</v>
       </c>
       <c r="D1060" s="2" t="s">
-        <v>2517</v>
+        <v>2516</v>
       </c>
       <c r="E1060" s="2" t="s">
-        <v>2516</v>
+        <v>2515</v>
       </c>
       <c r="F1060" t="s">
         <v>1825</v>
@@ -45936,7 +45936,7 @@
         <v>2078</v>
       </c>
       <c r="H1060" s="3" t="s">
-        <v>2476</v>
+        <v>2475</v>
       </c>
       <c r="I1060" t="s">
         <v>2081</v>
@@ -46099,10 +46099,10 @@
         <v>2094</v>
       </c>
       <c r="D1065" s="2" t="s">
+        <v>2517</v>
+      </c>
+      <c r="E1065" s="2" t="s">
         <v>2518</v>
-      </c>
-      <c r="E1065" s="2" t="s">
-        <v>2519</v>
       </c>
       <c r="F1065" t="s">
         <v>1586</v>
@@ -46344,7 +46344,7 @@
         <v>1165</v>
       </c>
       <c r="D1072" s="2" t="s">
-        <v>2478</v>
+        <v>2477</v>
       </c>
       <c r="E1072" s="2" t="s">
         <v>2027</v>
@@ -46671,7 +46671,7 @@
         <v>2078</v>
       </c>
       <c r="H1081" s="3" t="s">
-        <v>2477</v>
+        <v>2476</v>
       </c>
       <c r="I1081" t="s">
         <v>2141</v>
@@ -47009,10 +47009,10 @@
         <v>2158</v>
       </c>
       <c r="D1091" s="2" t="s">
+        <v>2484</v>
+      </c>
+      <c r="E1091" s="2" t="s">
         <v>2485</v>
-      </c>
-      <c r="E1091" s="2" t="s">
-        <v>2486</v>
       </c>
       <c r="F1091" t="s">
         <v>1586</v>
@@ -48512,7 +48512,7 @@
         <v>1214</v>
       </c>
       <c r="D1134" s="2" t="s">
-        <v>2421</v>
+        <v>2420</v>
       </c>
       <c r="E1134" s="2" t="s">
         <v>2326</v>
@@ -48620,7 +48620,7 @@
         <v>2321</v>
       </c>
       <c r="E1137" s="2" t="s">
-        <v>2525</v>
+        <v>2524</v>
       </c>
       <c r="F1137" t="s">
         <v>1586</v>
@@ -48757,7 +48757,7 @@
         <v>1221</v>
       </c>
       <c r="D1141" s="2" t="s">
-        <v>2490</v>
+        <v>2489</v>
       </c>
       <c r="E1141" s="2" t="e">
         <v>#N/A</v>
@@ -50787,7 +50787,7 @@
         <v>1278</v>
       </c>
       <c r="D1199" s="2" t="s">
-        <v>2484</v>
+        <v>2483</v>
       </c>
       <c r="E1199" s="2" t="s">
         <v>2315</v>
@@ -51347,10 +51347,10 @@
         <v>1294</v>
       </c>
       <c r="D1215" s="2" t="s">
-        <v>2413</v>
+        <v>2412</v>
       </c>
       <c r="E1215" s="2" t="s">
-        <v>2412</v>
+        <v>2411</v>
       </c>
       <c r="F1215" t="s">
         <v>1586</v>
@@ -51379,13 +51379,13 @@
         <v>68112</v>
       </c>
       <c r="C1216" s="6" t="s">
+        <v>2413</v>
+      </c>
+      <c r="D1216" s="2" t="s">
         <v>2414</v>
       </c>
-      <c r="D1216" s="2" t="s">
-        <v>2415</v>
-      </c>
       <c r="E1216" s="2" t="s">
-        <v>2418</v>
+        <v>2417</v>
       </c>
       <c r="F1216" t="s">
         <v>1586</v>
@@ -57887,7 +57887,7 @@
         <v>69</v>
       </c>
       <c r="D1402" s="2" t="s">
-        <v>2522</v>
+        <v>2521</v>
       </c>
       <c r="E1402" s="2" t="e">
         <v>#N/A</v>
@@ -58727,7 +58727,7 @@
         <v>78</v>
       </c>
       <c r="D1426" s="2" t="s">
-        <v>2521</v>
+        <v>2520</v>
       </c>
       <c r="E1426" s="2" t="e">
         <v>#N/A</v>
@@ -59497,7 +59497,7 @@
         <v>89</v>
       </c>
       <c r="D1448" s="2" t="s">
-        <v>2422</v>
+        <v>2421</v>
       </c>
       <c r="E1448" s="2" t="e">
         <v>#N/A</v>
@@ -60127,10 +60127,10 @@
         <v>90</v>
       </c>
       <c r="D1466" s="2" t="s">
+        <v>2434</v>
+      </c>
+      <c r="E1466" s="2" t="s">
         <v>2435</v>
-      </c>
-      <c r="E1466" s="2" t="s">
-        <v>2436</v>
       </c>
       <c r="F1466" t="s">
         <v>105</v>
@@ -60430,7 +60430,7 @@
         <v>97</v>
       </c>
       <c r="D1475" s="2" t="s">
-        <v>2423</v>
+        <v>2422</v>
       </c>
       <c r="E1475" s="2" t="e">
         <v>#N/A</v>
@@ -60462,10 +60462,10 @@
         <v>98</v>
       </c>
       <c r="D1476" s="2" t="s">
+        <v>2525</v>
+      </c>
+      <c r="E1476" s="2" t="s">
         <v>2526</v>
-      </c>
-      <c r="E1476" s="2" t="s">
-        <v>2527</v>
       </c>
       <c r="F1476" t="s">
         <v>1586</v>
@@ -61757,7 +61757,7 @@
         <v>1525</v>
       </c>
       <c r="D1513" s="2" t="s">
-        <v>2492</v>
+        <v>2491</v>
       </c>
       <c r="E1513" s="2" t="e">
         <v>#N/A</v>
@@ -62002,7 +62002,7 @@
         <v>1532</v>
       </c>
       <c r="D1520" s="2" t="s">
-        <v>2491</v>
+        <v>2490</v>
       </c>
       <c r="E1520" s="2" t="e">
         <v>#N/A</v>
@@ -62387,10 +62387,10 @@
         <v>1543</v>
       </c>
       <c r="D1531" s="2" t="s">
-        <v>2424</v>
+        <v>2423</v>
       </c>
       <c r="E1531" s="2" t="s">
-        <v>2429</v>
+        <v>2428</v>
       </c>
       <c r="F1531" t="s">
         <v>105</v>
@@ -62419,10 +62419,10 @@
         <v>1544</v>
       </c>
       <c r="D1532" s="2" t="s">
-        <v>2431</v>
+        <v>2430</v>
       </c>
       <c r="E1532" s="2" t="s">
-        <v>2430</v>
+        <v>2429</v>
       </c>
       <c r="F1532" t="s">
         <v>105</v>
@@ -62446,7 +62446,7 @@
         <v>1545</v>
       </c>
       <c r="D1533" s="2" t="s">
-        <v>2432</v>
+        <v>2431</v>
       </c>
       <c r="E1533" s="2"/>
       <c r="F1533" t="s">
@@ -62465,10 +62465,10 @@
         <v>1546</v>
       </c>
       <c r="D1534" s="2" t="s">
-        <v>2438</v>
+        <v>2437</v>
       </c>
       <c r="E1534" s="2" t="s">
-        <v>2433</v>
+        <v>2432</v>
       </c>
       <c r="F1534" t="s">
         <v>105</v>
@@ -62486,10 +62486,10 @@
         <v>1547</v>
       </c>
       <c r="D1535" s="2" t="s">
-        <v>2437</v>
+        <v>2436</v>
       </c>
       <c r="E1535" s="2" t="s">
-        <v>2434</v>
+        <v>2433</v>
       </c>
       <c r="F1535" t="s">
         <v>105</v>
@@ -62507,7 +62507,7 @@
         <v>1548</v>
       </c>
       <c r="D1536" s="2" t="s">
-        <v>2425</v>
+        <v>2424</v>
       </c>
       <c r="E1536" s="2" t="s">
         <v>1627</v>
@@ -62540,10 +62540,10 @@
         <v>1549</v>
       </c>
       <c r="D1537" s="2" t="s">
+        <v>2438</v>
+      </c>
+      <c r="E1537" s="2" t="s">
         <v>2439</v>
-      </c>
-      <c r="E1537" s="2" t="s">
-        <v>2440</v>
       </c>
       <c r="F1537" s="2" t="s">
         <v>1586</v>
@@ -62571,10 +62571,10 @@
         <v>1550</v>
       </c>
       <c r="D1538" s="2" t="s">
+        <v>2441</v>
+      </c>
+      <c r="E1538" s="2" t="s">
         <v>2442</v>
-      </c>
-      <c r="E1538" s="2" t="s">
-        <v>2443</v>
       </c>
       <c r="F1538" t="s">
         <v>1586</v>
@@ -62583,7 +62583,7 @@
         <v>2230</v>
       </c>
       <c r="H1538" s="3" t="s">
-        <v>2441</v>
+        <v>2440</v>
       </c>
       <c r="I1538" s="2" t="s">
         <v>2231</v>
@@ -62607,7 +62607,7 @@
         <v>2233</v>
       </c>
       <c r="E1539" s="2" t="s">
-        <v>2444</v>
+        <v>2443</v>
       </c>
       <c r="F1539" t="s">
         <v>1586</v>
@@ -62625,7 +62625,7 @@
         <v>1552</v>
       </c>
       <c r="D1540" s="2" t="s">
-        <v>2445</v>
+        <v>2444</v>
       </c>
       <c r="E1540" s="2" t="s">
         <v>2234</v>
@@ -62658,7 +62658,7 @@
         <v>2238</v>
       </c>
       <c r="E1541" s="2" t="s">
-        <v>2446</v>
+        <v>2445</v>
       </c>
       <c r="F1541" t="s">
         <v>1586</v>
@@ -62688,7 +62688,7 @@
         <v>2240</v>
       </c>
       <c r="E1542" s="2" t="s">
-        <v>2447</v>
+        <v>2446</v>
       </c>
       <c r="F1542" t="s">
         <v>1586</v>
@@ -62715,10 +62715,10 @@
         <v>1554</v>
       </c>
       <c r="D1543" s="2" t="s">
+        <v>2447</v>
+      </c>
+      <c r="E1543" s="2" t="s">
         <v>2448</v>
-      </c>
-      <c r="E1543" s="2" t="s">
-        <v>2449</v>
       </c>
       <c r="F1543" t="s">
         <v>1586</v>
@@ -62750,7 +62750,7 @@
         <v>1555</v>
       </c>
       <c r="D1544" s="2" t="s">
-        <v>2426</v>
+        <v>2425</v>
       </c>
       <c r="E1544" s="2" t="s">
         <v>1628</v>
@@ -62762,7 +62762,7 @@
         <v>2244</v>
       </c>
       <c r="I1544" s="2" t="s">
-        <v>2450</v>
+        <v>2449</v>
       </c>
       <c r="J1544" s="2"/>
       <c r="K1544" s="2" t="s">
@@ -62780,10 +62780,10 @@
         <v>2297</v>
       </c>
       <c r="D1545" s="2" t="s">
-        <v>2452</v>
+        <v>2451</v>
       </c>
       <c r="E1545" s="2" t="s">
-        <v>2451</v>
+        <v>2450</v>
       </c>
       <c r="F1545" t="s">
         <v>1586</v>
@@ -62936,10 +62936,10 @@
         <v>1560</v>
       </c>
       <c r="D1550" s="2" t="s">
-        <v>2454</v>
+        <v>2453</v>
       </c>
       <c r="E1550" s="2" t="s">
-        <v>2453</v>
+        <v>2452</v>
       </c>
       <c r="F1550" s="2" t="s">
         <v>1586</v>
@@ -62957,10 +62957,10 @@
         <v>1561</v>
       </c>
       <c r="D1551" s="2" t="s">
-        <v>2456</v>
+        <v>2455</v>
       </c>
       <c r="E1551" s="2" t="s">
-        <v>2455</v>
+        <v>2454</v>
       </c>
       <c r="F1551" s="2" t="s">
         <v>1586</v>
@@ -62978,10 +62978,10 @@
         <v>1562</v>
       </c>
       <c r="D1552" s="2" t="s">
+        <v>2456</v>
+      </c>
+      <c r="E1552" s="2" t="s">
         <v>2457</v>
-      </c>
-      <c r="E1552" s="2" t="s">
-        <v>2458</v>
       </c>
       <c r="F1552" s="2" t="s">
         <v>1586</v>
@@ -62999,16 +62999,16 @@
         <v>1563</v>
       </c>
       <c r="D1553" s="2" t="s">
-        <v>2427</v>
+        <v>2426</v>
       </c>
       <c r="E1553" s="11" t="s">
-        <v>2459</v>
+        <v>2458</v>
       </c>
       <c r="F1553" t="s">
         <v>1586</v>
       </c>
       <c r="G1553" t="s">
-        <v>2460</v>
+        <v>2459</v>
       </c>
       <c r="K1553"/>
     </row>
@@ -63023,10 +63023,10 @@
         <v>1564</v>
       </c>
       <c r="D1554" s="2" t="s">
-        <v>2461</v>
+        <v>2460</v>
       </c>
       <c r="E1554" s="2" t="s">
-        <v>2428</v>
+        <v>2427</v>
       </c>
       <c r="F1554" s="2" t="s">
         <v>1586</v>
@@ -63060,10 +63060,10 @@
         <v>104</v>
       </c>
       <c r="D1556" s="2" t="s">
-        <v>2493</v>
+        <v>2492</v>
       </c>
       <c r="E1556" s="2" t="s">
-        <v>2462</v>
+        <v>2461</v>
       </c>
       <c r="F1556" s="2" t="s">
         <v>1586</v>
